--- a/data/finra-margin-statistics.xlsx
+++ b/data/finra-margin-statistics.xlsx
@@ -467,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D356"/>
+  <dimension ref="A1:D357"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" min="1" max="1" width="14.0625"/>
@@ -501,5209 +501,5225 @@
     <row outlineLevel="0" r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B2" s="5">
-        <v>1417225</v>
+        <v>1453832</v>
       </c>
       <c r="C2" s="5">
-        <v>205132</v>
+        <v>207641</v>
       </c>
       <c r="D2" s="5">
-        <v>217305</v>
+        <v>217499</v>
       </c>
     </row>
     <row outlineLevel="0" r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B3" s="5">
-        <v>1502072</v>
+        <v>1417225</v>
       </c>
       <c r="C3" s="5">
-        <v>217441</v>
+        <v>205132</v>
       </c>
       <c r="D3" s="5">
-        <v>223412</v>
+        <v>217305</v>
       </c>
     </row>
     <row outlineLevel="0" r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B4" s="5">
-        <v>1415557</v>
+        <v>1502072</v>
       </c>
       <c r="C4" s="5">
-        <v>206600</v>
+        <v>217441</v>
       </c>
       <c r="D4" s="5">
-        <v>217256</v>
+        <v>223412</v>
       </c>
     </row>
     <row outlineLevel="0" r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B5" s="5">
-        <v>1304281</v>
+        <v>1415557</v>
       </c>
       <c r="C5" s="5">
-        <v>217836</v>
+        <v>206600</v>
       </c>
       <c r="D5" s="5">
-        <v>215445</v>
+        <v>217256</v>
       </c>
     </row>
     <row outlineLevel="0" r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <v>1220922</v>
+        <v>1304281</v>
       </c>
       <c r="C6" s="5">
-        <v>221860</v>
+        <v>217836</v>
       </c>
       <c r="D6" s="5">
-        <v>205600</v>
+        <v>215445</v>
       </c>
     </row>
     <row outlineLevel="0" r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B7" s="5">
-        <v>1253192</v>
+        <v>1220922</v>
       </c>
       <c r="C7" s="5">
-        <v>205060</v>
+        <v>221860</v>
       </c>
       <c r="D7" s="5">
-        <v>200047</v>
+        <v>205600</v>
       </c>
     </row>
     <row outlineLevel="0" r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B8" s="5">
-        <v>1279042</v>
+        <v>1253192</v>
       </c>
       <c r="C8" s="5">
-        <v>203700</v>
+        <v>205060</v>
       </c>
       <c r="D8" s="5">
-        <v>196911</v>
+        <v>200047</v>
       </c>
     </row>
     <row outlineLevel="0" r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B9" s="5">
-        <v>1225597</v>
+        <v>1279042</v>
       </c>
       <c r="C9" s="5">
-        <v>211720</v>
+        <v>203700</v>
       </c>
       <c r="D9" s="5">
-        <v>199762</v>
+        <v>196911</v>
       </c>
     </row>
     <row outlineLevel="0" r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="B10" s="5">
-        <v>1214321</v>
+        <v>1225597</v>
       </c>
       <c r="C10" s="5">
-        <v>202131</v>
+        <v>211720</v>
       </c>
       <c r="D10" s="5">
-        <v>194418</v>
+        <v>199762</v>
       </c>
     </row>
     <row outlineLevel="0" r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B11" s="5">
-        <v>1183654</v>
+        <v>1214321</v>
       </c>
       <c r="C11" s="5">
-        <v>197923</v>
+        <v>202131</v>
       </c>
       <c r="D11" s="5">
-        <v>195376</v>
+        <v>194418</v>
       </c>
     </row>
     <row outlineLevel="0" r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B12" s="5">
-        <v>1126494</v>
+        <v>1183654</v>
       </c>
       <c r="C12" s="5">
-        <v>204106</v>
+        <v>197923</v>
       </c>
       <c r="D12" s="5">
-        <v>194884</v>
+        <v>195376</v>
       </c>
     </row>
     <row outlineLevel="0" r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B13" s="5">
-        <v>1059723</v>
+        <v>1126494</v>
       </c>
       <c r="C13" s="5">
-        <v>188221</v>
+        <v>204106</v>
       </c>
       <c r="D13" s="5">
-        <v>181563</v>
+        <v>194884</v>
       </c>
     </row>
     <row outlineLevel="0" r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B14" s="5">
-        <v>1022548</v>
+        <v>1059723</v>
       </c>
       <c r="C14" s="5">
-        <v>194712</v>
+        <v>188221</v>
       </c>
       <c r="D14" s="5">
-        <v>186672</v>
+        <v>181563</v>
       </c>
     </row>
     <row outlineLevel="0" r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B15" s="5">
-        <v>1007961</v>
+        <v>1022548</v>
       </c>
       <c r="C15" s="5">
-        <v>200573</v>
+        <v>194712</v>
       </c>
       <c r="D15" s="5">
-        <v>185584</v>
+        <v>186672</v>
       </c>
     </row>
     <row outlineLevel="0" r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B16" s="5">
-        <v>920960</v>
+        <v>1007961</v>
       </c>
       <c r="C16" s="5">
-        <v>187685</v>
+        <v>200573</v>
       </c>
       <c r="D16" s="5">
-        <v>176698</v>
+        <v>185584</v>
       </c>
     </row>
     <row outlineLevel="0" r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B17" s="5">
-        <v>850558</v>
+        <v>920960</v>
       </c>
       <c r="C17" s="5">
-        <v>187958</v>
+        <v>187685</v>
       </c>
       <c r="D17" s="5">
-        <v>175824</v>
+        <v>176698</v>
       </c>
     </row>
     <row outlineLevel="0" r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B18" s="5">
-        <v>880316</v>
+        <v>850558</v>
       </c>
       <c r="C18" s="5">
-        <v>189855</v>
+        <v>187958</v>
       </c>
       <c r="D18" s="5">
-        <v>176161</v>
+        <v>175824</v>
       </c>
     </row>
     <row outlineLevel="0" r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B19" s="5">
-        <v>918144</v>
+        <v>880316</v>
       </c>
       <c r="C19" s="5">
-        <v>183278</v>
+        <v>189855</v>
       </c>
       <c r="D19" s="5">
-        <v>176051</v>
+        <v>176161</v>
       </c>
     </row>
     <row outlineLevel="0" r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B20" s="5">
-        <v>937253</v>
+        <v>918144</v>
       </c>
       <c r="C20" s="5">
-        <v>178301</v>
+        <v>183278</v>
       </c>
       <c r="D20" s="5">
-        <v>166346</v>
+        <v>176051</v>
       </c>
     </row>
     <row outlineLevel="0" r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B21" s="5">
-        <v>899168</v>
+        <v>937253</v>
       </c>
       <c r="C21" s="5">
-        <v>181280</v>
+        <v>178301</v>
       </c>
       <c r="D21" s="5">
-        <v>175795</v>
+        <v>166346</v>
       </c>
     </row>
     <row outlineLevel="0" r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B22" s="5">
-        <v>890852</v>
+        <v>899168</v>
       </c>
       <c r="C22" s="5">
-        <v>170052</v>
+        <v>181280</v>
       </c>
       <c r="D22" s="5">
-        <v>167223</v>
+        <v>175795</v>
       </c>
     </row>
     <row outlineLevel="0" r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B23" s="5">
-        <v>815369</v>
+        <v>890852</v>
       </c>
       <c r="C23" s="5">
-        <v>173621</v>
+        <v>170052</v>
       </c>
       <c r="D23" s="5">
-        <v>164813</v>
+        <v>167223</v>
       </c>
     </row>
     <row outlineLevel="0" r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B24" s="5">
-        <v>813211</v>
+        <v>815369</v>
       </c>
       <c r="C24" s="5">
-        <v>167901</v>
+        <v>173621</v>
       </c>
       <c r="D24" s="5">
-        <v>158358</v>
+        <v>164813</v>
       </c>
     </row>
     <row outlineLevel="0" r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B25" s="5">
-        <v>797162</v>
+        <v>813211</v>
       </c>
       <c r="C25" s="5">
-        <v>148702</v>
+        <v>167901</v>
       </c>
       <c r="D25" s="5">
-        <v>152107</v>
+        <v>158358</v>
       </c>
     </row>
     <row outlineLevel="0" r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B26" s="5">
-        <v>810835</v>
+        <v>797162</v>
       </c>
       <c r="C26" s="5">
-        <v>154951</v>
+        <v>148702</v>
       </c>
       <c r="D26" s="5">
-        <v>150738</v>
+        <v>152107</v>
       </c>
     </row>
     <row outlineLevel="0" r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B27" s="5">
-        <v>809322</v>
+        <v>810835</v>
       </c>
       <c r="C27" s="5">
-        <v>157240</v>
+        <v>154951</v>
       </c>
       <c r="D27" s="5">
-        <v>149714</v>
+        <v>150738</v>
       </c>
     </row>
     <row outlineLevel="0" r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B28" s="5">
-        <v>809431</v>
+        <v>809322</v>
       </c>
       <c r="C28" s="5">
-        <v>155256</v>
+        <v>157240</v>
       </c>
       <c r="D28" s="5">
-        <v>145072</v>
+        <v>149714</v>
       </c>
     </row>
     <row outlineLevel="0" r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B29" s="5">
-        <v>775464</v>
+        <v>809431</v>
       </c>
       <c r="C29" s="5">
-        <v>161749</v>
+        <v>155256</v>
       </c>
       <c r="D29" s="5">
-        <v>149855</v>
+        <v>145072</v>
       </c>
     </row>
     <row outlineLevel="0" r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B30" s="5">
-        <v>784136</v>
+        <v>775464</v>
       </c>
       <c r="C30" s="5">
-        <v>166990</v>
+        <v>161749</v>
       </c>
       <c r="D30" s="5">
-        <v>151339</v>
+        <v>149855</v>
       </c>
     </row>
     <row outlineLevel="0" r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B31" s="5">
-        <v>742963</v>
+        <v>784136</v>
       </c>
       <c r="C31" s="5">
-        <v>166144</v>
+        <v>166990</v>
       </c>
       <c r="D31" s="5">
-        <v>150620</v>
+        <v>151339</v>
       </c>
     </row>
     <row outlineLevel="0" r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B32" s="5">
-        <v>701975</v>
+        <v>742963</v>
       </c>
       <c r="C32" s="5">
-        <v>165025</v>
+        <v>166144</v>
       </c>
       <c r="D32" s="5">
-        <v>144941</v>
+        <v>150620</v>
       </c>
     </row>
     <row outlineLevel="0" r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B33" s="5">
-        <v>700774</v>
+        <v>701975</v>
       </c>
       <c r="C33" s="5">
-        <v>161639</v>
+        <v>165025</v>
       </c>
       <c r="D33" s="5">
-        <v>147019</v>
+        <v>144941</v>
       </c>
     </row>
     <row outlineLevel="0" r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B34" s="5">
-        <v>660887</v>
+        <v>700774</v>
       </c>
       <c r="C34" s="5">
-        <v>171207</v>
+        <v>161639</v>
       </c>
       <c r="D34" s="5">
-        <v>146319</v>
+        <v>147019</v>
       </c>
     </row>
     <row outlineLevel="0" r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="B35" s="5">
-        <v>635276</v>
+        <v>660887</v>
       </c>
       <c r="C35" s="5">
-        <v>162865</v>
+        <v>171207</v>
       </c>
       <c r="D35" s="5">
-        <v>142117</v>
+        <v>146319</v>
       </c>
     </row>
     <row outlineLevel="0" r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B36" s="5">
-        <v>680846</v>
+        <v>635276</v>
       </c>
       <c r="C36" s="5">
-        <v>153918</v>
+        <v>162865</v>
       </c>
       <c r="D36" s="5">
-        <v>141751</v>
+        <v>142117</v>
       </c>
     </row>
     <row outlineLevel="0" r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2023-08</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="B37" s="5">
-        <v>689185</v>
+        <v>680846</v>
       </c>
       <c r="C37" s="5">
-        <v>177711</v>
+        <v>153918</v>
       </c>
       <c r="D37" s="5">
-        <v>145989</v>
+        <v>141751</v>
       </c>
     </row>
     <row outlineLevel="0" r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="B38" s="5">
-        <v>709834</v>
+        <v>689185</v>
       </c>
       <c r="C38" s="5">
-        <v>174804</v>
+        <v>177711</v>
       </c>
       <c r="D38" s="5">
-        <v>147921</v>
+        <v>145989</v>
       </c>
     </row>
     <row outlineLevel="0" r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="B39" s="5">
-        <v>681228</v>
+        <v>709834</v>
       </c>
       <c r="C39" s="5">
-        <v>181569</v>
+        <v>174804</v>
       </c>
       <c r="D39" s="5">
-        <v>145173</v>
+        <v>147921</v>
       </c>
     </row>
     <row outlineLevel="0" r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="B40" s="5">
-        <v>644170</v>
+        <v>681228</v>
       </c>
       <c r="C40" s="5">
-        <v>178576</v>
+        <v>181569</v>
       </c>
       <c r="D40" s="5">
-        <v>147377</v>
+        <v>145173</v>
       </c>
     </row>
     <row outlineLevel="0" r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2023-04</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="B41" s="5">
-        <v>631949</v>
+        <v>644170</v>
       </c>
       <c r="C41" s="5">
-        <v>175460</v>
+        <v>178576</v>
       </c>
       <c r="D41" s="5">
-        <v>145594</v>
+        <v>147377</v>
       </c>
     </row>
     <row outlineLevel="0" r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2023-04</t>
         </is>
       </c>
       <c r="B42" s="5">
-        <v>645429</v>
+        <v>631949</v>
       </c>
       <c r="C42" s="5">
-        <v>191618</v>
+        <v>175460</v>
       </c>
       <c r="D42" s="5">
-        <v>152014</v>
+        <v>145594</v>
       </c>
     </row>
     <row outlineLevel="0" r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2023-02</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="B43" s="5">
-        <v>624379</v>
+        <v>645429</v>
       </c>
       <c r="C43" s="5">
-        <v>198644</v>
+        <v>191618</v>
       </c>
       <c r="D43" s="5">
-        <v>159103</v>
+        <v>152014</v>
       </c>
     </row>
     <row outlineLevel="0" r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>2023-02</t>
         </is>
       </c>
       <c r="B44" s="5">
-        <v>641228</v>
+        <v>624379</v>
       </c>
       <c r="C44" s="5">
-        <v>208720</v>
+        <v>198644</v>
       </c>
       <c r="D44" s="5">
-        <v>161224</v>
+        <v>159103</v>
       </c>
     </row>
     <row outlineLevel="0" r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="B45" s="5">
-        <v>606659</v>
+        <v>641228</v>
       </c>
       <c r="C45" s="5">
-        <v>205902</v>
+        <v>208720</v>
       </c>
       <c r="D45" s="5">
-        <v>164065</v>
+        <v>161224</v>
       </c>
     </row>
     <row outlineLevel="0" r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2022-11</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="B46" s="5">
-        <v>643783</v>
+        <v>606659</v>
       </c>
       <c r="C46" s="5">
-        <v>205158</v>
+        <v>205902</v>
       </c>
       <c r="D46" s="5">
-        <v>165434</v>
+        <v>164065</v>
       </c>
     </row>
     <row outlineLevel="0" r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2022-11</t>
         </is>
       </c>
       <c r="B47" s="5">
-        <v>649618</v>
+        <v>643783</v>
       </c>
       <c r="C47" s="5">
-        <v>216057</v>
+        <v>205158</v>
       </c>
       <c r="D47" s="5">
-        <v>172976</v>
+        <v>165434</v>
       </c>
     </row>
     <row outlineLevel="0" r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="B48" s="5">
-        <v>664009</v>
+        <v>649618</v>
       </c>
       <c r="C48" s="5">
-        <v>223400</v>
+        <v>216057</v>
       </c>
       <c r="D48" s="5">
-        <v>173050</v>
+        <v>172976</v>
       </c>
     </row>
     <row outlineLevel="0" r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="B49" s="5">
-        <v>687787</v>
+        <v>664009</v>
       </c>
       <c r="C49" s="5">
-        <v>226182</v>
+        <v>223400</v>
       </c>
       <c r="D49" s="5">
-        <v>175974</v>
+        <v>173050</v>
       </c>
     </row>
     <row outlineLevel="0" r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2022-07</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="B50" s="5">
-        <v>696781</v>
+        <v>687787</v>
       </c>
       <c r="C50" s="5">
-        <v>232147</v>
+        <v>226182</v>
       </c>
       <c r="D50" s="5">
-        <v>177054</v>
+        <v>175974</v>
       </c>
     </row>
     <row outlineLevel="0" r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="B51" s="5">
-        <v>683445</v>
+        <v>696781</v>
       </c>
       <c r="C51" s="5">
-        <v>249399</v>
+        <v>232147</v>
       </c>
       <c r="D51" s="5">
-        <v>186931</v>
+        <v>177054</v>
       </c>
     </row>
     <row outlineLevel="0" r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2022-05</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="B52" s="5">
-        <v>752944</v>
+        <v>683445</v>
       </c>
       <c r="C52" s="5">
-        <v>244857</v>
+        <v>249399</v>
       </c>
       <c r="D52" s="5">
-        <v>184151</v>
+        <v>186931</v>
       </c>
     </row>
     <row outlineLevel="0" r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2022-04</t>
+          <t>2022-05</t>
         </is>
       </c>
       <c r="B53" s="5">
-        <v>772940</v>
+        <v>752944</v>
       </c>
       <c r="C53" s="5">
-        <v>242724</v>
+        <v>244857</v>
       </c>
       <c r="D53" s="5">
-        <v>188652</v>
+        <v>184151</v>
       </c>
     </row>
     <row outlineLevel="0" r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2022-04</t>
         </is>
       </c>
       <c r="B54" s="5">
-        <v>799660</v>
+        <v>772940</v>
       </c>
       <c r="C54" s="5">
-        <v>256076</v>
+        <v>242724</v>
       </c>
       <c r="D54" s="5">
-        <v>196008</v>
+        <v>188652</v>
       </c>
     </row>
     <row outlineLevel="0" r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2022-02</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="B55" s="5">
-        <v>835255</v>
+        <v>799660</v>
       </c>
       <c r="C55" s="5">
-        <v>250686</v>
+        <v>256076</v>
       </c>
       <c r="D55" s="5">
-        <v>195269</v>
+        <v>196008</v>
       </c>
     </row>
     <row outlineLevel="0" r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2022-01</t>
+          <t>2022-02</t>
         </is>
       </c>
       <c r="B56" s="5">
-        <v>829637</v>
+        <v>835255</v>
       </c>
       <c r="C56" s="5">
-        <v>247752</v>
+        <v>250686</v>
       </c>
       <c r="D56" s="5">
-        <v>194545</v>
+        <v>195269</v>
       </c>
     </row>
     <row outlineLevel="0" r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2021-12</t>
+          <t>2022-01</t>
         </is>
       </c>
       <c r="B57" s="5">
-        <v>910021</v>
+        <v>829637</v>
       </c>
       <c r="C57" s="5">
-        <v>250435</v>
+        <v>247752</v>
       </c>
       <c r="D57" s="5">
-        <v>215116</v>
+        <v>194545</v>
       </c>
     </row>
     <row outlineLevel="0" r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2021-11</t>
+          <t>2021-12</t>
         </is>
       </c>
       <c r="B58" s="5">
-        <v>918598</v>
+        <v>910021</v>
       </c>
       <c r="C58" s="5">
-        <v>235638</v>
+        <v>250435</v>
       </c>
       <c r="D58" s="5">
-        <v>211623</v>
+        <v>215116</v>
       </c>
     </row>
     <row outlineLevel="0" r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2021-10</t>
+          <t>2021-11</t>
         </is>
       </c>
       <c r="B59" s="5">
-        <v>935862</v>
+        <v>918598</v>
       </c>
       <c r="C59" s="5">
-        <v>226159</v>
+        <v>235638</v>
       </c>
       <c r="D59" s="5">
-        <v>200548</v>
+        <v>211623</v>
       </c>
     </row>
     <row outlineLevel="0" r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2021-09</t>
+          <t>2021-10</t>
         </is>
       </c>
       <c r="B60" s="5">
-        <v>903117</v>
+        <v>935862</v>
       </c>
       <c r="C60" s="5">
-        <v>229279</v>
+        <v>226159</v>
       </c>
       <c r="D60" s="5">
-        <v>205564</v>
+        <v>200548</v>
       </c>
     </row>
     <row outlineLevel="0" r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2021-09</t>
         </is>
       </c>
       <c r="B61" s="5">
-        <v>911545</v>
+        <v>903117</v>
       </c>
       <c r="C61" s="5">
-        <v>219365</v>
+        <v>229279</v>
       </c>
       <c r="D61" s="5">
-        <v>198913</v>
+        <v>205564</v>
       </c>
     </row>
     <row outlineLevel="0" r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2021-07</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="B62" s="5">
-        <v>844324</v>
+        <v>911545</v>
       </c>
       <c r="C62" s="5">
-        <v>215463</v>
+        <v>219365</v>
       </c>
       <c r="D62" s="5">
-        <v>195762</v>
+        <v>198913</v>
       </c>
     </row>
     <row outlineLevel="0" r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2021-06</t>
+          <t>2021-07</t>
         </is>
       </c>
       <c r="B63" s="5">
-        <v>882103</v>
+        <v>844324</v>
       </c>
       <c r="C63" s="5">
-        <v>221862</v>
+        <v>215463</v>
       </c>
       <c r="D63" s="5">
-        <v>239290</v>
+        <v>195762</v>
       </c>
     </row>
     <row outlineLevel="0" r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2021-05</t>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="B64" s="5">
-        <v>861626</v>
+        <v>882103</v>
       </c>
       <c r="C64" s="5">
-        <v>213356</v>
+        <v>221862</v>
       </c>
       <c r="D64" s="5">
-        <v>234992</v>
+        <v>239290</v>
       </c>
     </row>
     <row outlineLevel="0" r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2021-04</t>
+          <t>2021-05</t>
         </is>
       </c>
       <c r="B65" s="5">
-        <v>847186</v>
+        <v>861626</v>
       </c>
       <c r="C65" s="5">
-        <v>218132</v>
+        <v>213356</v>
       </c>
       <c r="D65" s="5">
-        <v>233145</v>
+        <v>234992</v>
       </c>
     </row>
     <row outlineLevel="0" r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2021-03</t>
+          <t>2021-04</t>
         </is>
       </c>
       <c r="B66" s="5">
-        <v>822551</v>
+        <v>847186</v>
       </c>
       <c r="C66" s="5">
-        <v>219522</v>
+        <v>218132</v>
       </c>
       <c r="D66" s="5">
-        <v>237154</v>
+        <v>233145</v>
       </c>
     </row>
     <row outlineLevel="0" r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2021-02</t>
+          <t>2021-03</t>
         </is>
       </c>
       <c r="B67" s="5">
-        <v>813680</v>
+        <v>822551</v>
       </c>
       <c r="C67" s="5">
-        <v>220840</v>
+        <v>219522</v>
       </c>
       <c r="D67" s="5">
-        <v>240481</v>
+        <v>237154</v>
       </c>
     </row>
     <row outlineLevel="0" r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2021-01</t>
+          <t>2021-02</t>
         </is>
       </c>
       <c r="B68" s="5">
-        <v>798605</v>
+        <v>813680</v>
       </c>
       <c r="C68" s="5">
-        <v>224133</v>
+        <v>220840</v>
       </c>
       <c r="D68" s="5">
-        <v>241220</v>
+        <v>240481</v>
       </c>
     </row>
     <row outlineLevel="0" r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2020-12</t>
+          <t>2021-01</t>
         </is>
       </c>
       <c r="B69" s="5">
-        <v>778037</v>
+        <v>798605</v>
       </c>
       <c r="C69" s="5">
-        <v>224987</v>
+        <v>224133</v>
       </c>
       <c r="D69" s="5">
-        <v>227127</v>
+        <v>241220</v>
       </c>
     </row>
     <row outlineLevel="0" r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2020-11</t>
+          <t>2020-12</t>
         </is>
       </c>
       <c r="B70" s="5">
-        <v>722118</v>
+        <v>778037</v>
       </c>
       <c r="C70" s="5">
-        <v>200723</v>
+        <v>224987</v>
       </c>
       <c r="D70" s="5">
-        <v>221567</v>
+        <v>227127</v>
       </c>
     </row>
     <row outlineLevel="0" r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2020-10</t>
+          <t>2020-11</t>
         </is>
       </c>
       <c r="B71" s="5">
-        <v>659313</v>
+        <v>722118</v>
       </c>
       <c r="C71" s="5">
-        <v>193293</v>
+        <v>200723</v>
       </c>
       <c r="D71" s="5">
-        <v>217739</v>
+        <v>221567</v>
       </c>
     </row>
     <row outlineLevel="0" r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2020-09</t>
+          <t>2020-10</t>
         </is>
       </c>
       <c r="B72" s="5">
-        <v>654324</v>
+        <v>659313</v>
       </c>
       <c r="C72" s="5">
-        <v>189462</v>
+        <v>193293</v>
       </c>
       <c r="D72" s="5">
-        <v>211547</v>
+        <v>217739</v>
       </c>
     </row>
     <row outlineLevel="0" r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2020-08</t>
+          <t>2020-09</t>
         </is>
       </c>
       <c r="B73" s="5">
-        <v>645547</v>
+        <v>654324</v>
       </c>
       <c r="C73" s="5">
-        <v>185113</v>
+        <v>189462</v>
       </c>
       <c r="D73" s="5">
-        <v>215042</v>
+        <v>211547</v>
       </c>
     </row>
     <row outlineLevel="0" r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2020-07</t>
+          <t>2020-08</t>
         </is>
       </c>
       <c r="B74" s="5">
-        <v>613830</v>
+        <v>645547</v>
       </c>
       <c r="C74" s="5">
-        <v>181420</v>
+        <v>185113</v>
       </c>
       <c r="D74" s="5">
-        <v>223768</v>
+        <v>215042</v>
       </c>
     </row>
     <row outlineLevel="0" r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2020-06</t>
+          <t>2020-07</t>
         </is>
       </c>
       <c r="B75" s="5">
-        <v>584676</v>
+        <v>613830</v>
       </c>
       <c r="C75" s="5">
-        <v>185497</v>
+        <v>181420</v>
       </c>
       <c r="D75" s="5">
-        <v>229078</v>
+        <v>223768</v>
       </c>
     </row>
     <row outlineLevel="0" r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2020-05</t>
+          <t>2020-06</t>
         </is>
       </c>
       <c r="B76" s="5">
-        <v>552543</v>
+        <v>584676</v>
       </c>
       <c r="C76" s="5">
-        <v>175794</v>
+        <v>185497</v>
       </c>
       <c r="D76" s="5">
-        <v>210935</v>
+        <v>229078</v>
       </c>
     </row>
     <row outlineLevel="0" r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2020-04</t>
+          <t>2020-05</t>
         </is>
       </c>
       <c r="B77" s="5">
-        <v>524696</v>
+        <v>552543</v>
       </c>
       <c r="C77" s="5">
-        <v>180942</v>
+        <v>175794</v>
       </c>
       <c r="D77" s="5">
-        <v>217187</v>
+        <v>210935</v>
       </c>
     </row>
     <row outlineLevel="0" r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2020-03</t>
+          <t>2020-04</t>
         </is>
       </c>
       <c r="B78" s="5">
-        <v>479291</v>
+        <v>524696</v>
       </c>
       <c r="C78" s="5">
-        <v>191046</v>
+        <v>180942</v>
       </c>
       <c r="D78" s="5">
-        <v>226202</v>
+        <v>217187</v>
       </c>
     </row>
     <row outlineLevel="0" r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2020-02</t>
+          <t>2020-03</t>
         </is>
       </c>
       <c r="B79" s="5">
-        <v>545127</v>
+        <v>479291</v>
       </c>
       <c r="C79" s="5">
-        <v>163001</v>
+        <v>191046</v>
       </c>
       <c r="D79" s="5">
-        <v>197716</v>
+        <v>226202</v>
       </c>
     </row>
     <row outlineLevel="0" r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2020-01</t>
+          <t>2020-02</t>
         </is>
       </c>
       <c r="B80" s="5">
-        <v>561812</v>
+        <v>545127</v>
       </c>
       <c r="C80" s="5">
-        <v>152854</v>
+        <v>163001</v>
       </c>
       <c r="D80" s="5">
-        <v>186847</v>
+        <v>197716</v>
       </c>
     </row>
     <row outlineLevel="0" r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2019-12</t>
+          <t>2020-01</t>
         </is>
       </c>
       <c r="B81" s="5">
-        <v>579221</v>
+        <v>561812</v>
       </c>
       <c r="C81" s="5">
-        <v>151543</v>
+        <v>152854</v>
       </c>
       <c r="D81" s="5">
-        <v>186315</v>
+        <v>186847</v>
       </c>
     </row>
     <row outlineLevel="0" r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2019-11</t>
+          <t>2019-12</t>
         </is>
       </c>
       <c r="B82" s="5">
-        <v>563482</v>
+        <v>579221</v>
       </c>
       <c r="C82" s="5">
-        <v>146935</v>
+        <v>151543</v>
       </c>
       <c r="D82" s="5">
-        <v>186866</v>
+        <v>186315</v>
       </c>
     </row>
     <row outlineLevel="0" r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2019-10</t>
+          <t>2019-11</t>
         </is>
       </c>
       <c r="B83" s="5">
-        <v>554604</v>
+        <v>563482</v>
       </c>
       <c r="C83" s="5">
-        <v>145650</v>
+        <v>146935</v>
       </c>
       <c r="D83" s="5">
-        <v>183966</v>
+        <v>186866</v>
       </c>
     </row>
     <row outlineLevel="0" r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2019-09</t>
+          <t>2019-10</t>
         </is>
       </c>
       <c r="B84" s="5">
-        <v>555910</v>
+        <v>554604</v>
       </c>
       <c r="C84" s="5">
-        <v>150648</v>
+        <v>145650</v>
       </c>
       <c r="D84" s="5">
-        <v>187887</v>
+        <v>183966</v>
       </c>
     </row>
     <row outlineLevel="0" r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2019-08</t>
+          <t>2019-09</t>
         </is>
       </c>
       <c r="B85" s="5">
-        <v>564894</v>
+        <v>555910</v>
       </c>
       <c r="C85" s="5">
-        <v>135567</v>
+        <v>150648</v>
       </c>
       <c r="D85" s="5">
-        <v>181451</v>
+        <v>187887</v>
       </c>
     </row>
     <row outlineLevel="0" r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2019-07</t>
+          <t>2019-08</t>
         </is>
       </c>
       <c r="B86" s="5">
-        <v>602139</v>
+        <v>564894</v>
       </c>
       <c r="C86" s="5">
-        <v>138703</v>
+        <v>135567</v>
       </c>
       <c r="D86" s="5">
-        <v>182613</v>
+        <v>181451</v>
       </c>
     </row>
     <row outlineLevel="0" r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2019-06</t>
+          <t>2019-07</t>
         </is>
       </c>
       <c r="B87" s="5">
-        <v>596304</v>
+        <v>602139</v>
       </c>
       <c r="C87" s="5">
-        <v>139826</v>
+        <v>138703</v>
       </c>
       <c r="D87" s="5">
-        <v>179542</v>
+        <v>182613</v>
       </c>
     </row>
     <row outlineLevel="0" r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2019-05</t>
+          <t>2019-06</t>
         </is>
       </c>
       <c r="B88" s="5">
-        <v>568751</v>
+        <v>596304</v>
       </c>
       <c r="C88" s="5">
-        <v>137489</v>
+        <v>139826</v>
       </c>
       <c r="D88" s="5">
-        <v>179019</v>
+        <v>179542</v>
       </c>
     </row>
     <row outlineLevel="0" r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2019-04</t>
+          <t>2019-05</t>
         </is>
       </c>
       <c r="B89" s="5">
-        <v>588721</v>
+        <v>568751</v>
       </c>
       <c r="C89" s="5">
-        <v>143802</v>
+        <v>137489</v>
       </c>
       <c r="D89" s="5">
-        <v>178523</v>
+        <v>179019</v>
       </c>
     </row>
     <row outlineLevel="0" r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2019-03</t>
+          <t>2019-04</t>
         </is>
       </c>
       <c r="B90" s="5">
-        <v>574013</v>
+        <v>588721</v>
       </c>
       <c r="C90" s="5">
-        <v>141074</v>
+        <v>143802</v>
       </c>
       <c r="D90" s="5">
-        <v>180765</v>
+        <v>178523</v>
       </c>
     </row>
     <row outlineLevel="0" r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2019-02</t>
+          <t>2019-03</t>
         </is>
       </c>
       <c r="B91" s="5">
-        <v>581205</v>
+        <v>574013</v>
       </c>
       <c r="C91" s="5">
-        <v>149686</v>
+        <v>141074</v>
       </c>
       <c r="D91" s="5">
-        <v>181955</v>
+        <v>180765</v>
       </c>
     </row>
     <row outlineLevel="0" r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2019-01</t>
+          <t>2019-02</t>
         </is>
       </c>
       <c r="B92" s="5">
-        <v>568433</v>
+        <v>581205</v>
       </c>
       <c r="C92" s="5">
-        <v>151804</v>
+        <v>149686</v>
       </c>
       <c r="D92" s="5">
-        <v>186050</v>
+        <v>181955</v>
       </c>
     </row>
     <row outlineLevel="0" r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2018-12</t>
+          <t>2019-01</t>
         </is>
       </c>
       <c r="B93" s="5">
-        <v>554285</v>
+        <v>568433</v>
       </c>
       <c r="C93" s="5">
-        <v>159572</v>
+        <v>151804</v>
       </c>
       <c r="D93" s="5">
-        <v>190743</v>
+        <v>186050</v>
       </c>
     </row>
     <row outlineLevel="0" r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2018-11</t>
+          <t>2018-12</t>
         </is>
       </c>
       <c r="B94" s="5">
-        <v>592593</v>
+        <v>554285</v>
       </c>
       <c r="C94" s="5">
-        <v>146452</v>
+        <v>159572</v>
       </c>
       <c r="D94" s="5">
-        <v>178810</v>
+        <v>190743</v>
       </c>
     </row>
     <row outlineLevel="0" r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2018-10</t>
+          <t>2018-11</t>
         </is>
       </c>
       <c r="B95" s="5">
-        <v>607645</v>
+        <v>592593</v>
       </c>
       <c r="C95" s="5">
-        <v>148037</v>
+        <v>146452</v>
       </c>
       <c r="D95" s="5">
-        <v>183432</v>
+        <v>178810</v>
       </c>
     </row>
     <row outlineLevel="0" r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>2018-09</t>
+          <t>2018-10</t>
         </is>
       </c>
       <c r="B96" s="5">
-        <v>648126</v>
+        <v>607645</v>
       </c>
       <c r="C96" s="5">
-        <v>151384</v>
+        <v>148037</v>
       </c>
       <c r="D96" s="5">
-        <v>188152</v>
+        <v>183432</v>
       </c>
     </row>
     <row outlineLevel="0" r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>2018-08</t>
+          <t>2018-09</t>
         </is>
       </c>
       <c r="B97" s="5">
-        <v>652395</v>
+        <v>648126</v>
       </c>
       <c r="C97" s="5">
-        <v>148873</v>
+        <v>151384</v>
       </c>
       <c r="D97" s="5">
-        <v>178601</v>
+        <v>188152</v>
       </c>
     </row>
     <row outlineLevel="0" r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>2018-07</t>
+          <t>2018-08</t>
         </is>
       </c>
       <c r="B98" s="5">
-        <v>652790</v>
+        <v>652395</v>
       </c>
       <c r="C98" s="5">
-        <v>148947</v>
+        <v>148873</v>
       </c>
       <c r="D98" s="5">
-        <v>178299</v>
+        <v>178601</v>
       </c>
     </row>
     <row outlineLevel="0" r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2018-06</t>
+          <t>2018-07</t>
         </is>
       </c>
       <c r="B99" s="5">
-        <v>646931</v>
+        <v>652790</v>
       </c>
       <c r="C99" s="5">
-        <v>157150</v>
+        <v>148947</v>
       </c>
       <c r="D99" s="5">
-        <v>179399</v>
+        <v>178299</v>
       </c>
     </row>
     <row outlineLevel="0" r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>2018-05</t>
+          <t>2018-06</t>
         </is>
       </c>
       <c r="B100" s="5">
-        <v>668940</v>
+        <v>646931</v>
       </c>
       <c r="C100" s="5">
-        <v>155344</v>
+        <v>157150</v>
       </c>
       <c r="D100" s="5">
-        <v>181890</v>
+        <v>179399</v>
       </c>
     </row>
     <row outlineLevel="0" r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2018-04</t>
+          <t>2018-05</t>
         </is>
       </c>
       <c r="B101" s="5">
-        <v>652303</v>
+        <v>668940</v>
       </c>
       <c r="C101" s="5">
-        <v>155989</v>
+        <v>155344</v>
       </c>
       <c r="D101" s="5">
-        <v>179410</v>
+        <v>181890</v>
       </c>
     </row>
     <row outlineLevel="0" r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2018-03</t>
+          <t>2018-04</t>
         </is>
       </c>
       <c r="B102" s="5">
-        <v>645235</v>
+        <v>652303</v>
       </c>
       <c r="C102" s="5">
-        <v>166148</v>
+        <v>155989</v>
       </c>
       <c r="D102" s="5">
-        <v>180751</v>
+        <v>179410</v>
       </c>
     </row>
     <row outlineLevel="0" r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2018-02</t>
+          <t>2018-03</t>
         </is>
       </c>
       <c r="B103" s="5">
-        <v>645064</v>
+        <v>645235</v>
       </c>
       <c r="C103" s="5">
-        <v>164657</v>
+        <v>166148</v>
       </c>
       <c r="D103" s="5">
-        <v>183267</v>
+        <v>180751</v>
       </c>
     </row>
     <row outlineLevel="0" r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2018-01</t>
+          <t>2018-02</t>
         </is>
       </c>
       <c r="B104" s="5">
-        <v>665716</v>
+        <v>645064</v>
       </c>
       <c r="C104" s="5">
-        <v>168450</v>
+        <v>164657</v>
       </c>
       <c r="D104" s="5">
-        <v>181763</v>
+        <v>183267</v>
       </c>
     </row>
     <row outlineLevel="0" r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2017-12</t>
+          <t>2018-01</t>
         </is>
       </c>
       <c r="B105" s="5">
-        <v>642798</v>
+        <v>665716</v>
       </c>
       <c r="C105" s="5">
-        <v>172999</v>
+        <v>168450</v>
       </c>
       <c r="D105" s="5">
-        <v>182773</v>
+        <v>181763</v>
       </c>
     </row>
     <row outlineLevel="0" r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>2017-11</t>
+          <t>2017-12</t>
         </is>
       </c>
       <c r="B106" s="5">
-        <v>627422</v>
+        <v>642798</v>
       </c>
       <c r="C106" s="5">
-        <v>170948</v>
+        <v>172999</v>
       </c>
       <c r="D106" s="5">
-        <v>185312</v>
+        <v>182773</v>
       </c>
     </row>
     <row outlineLevel="0" r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2017-10</t>
+          <t>2017-11</t>
         </is>
       </c>
       <c r="B107" s="5">
-        <v>607838</v>
+        <v>627422</v>
       </c>
       <c r="C107" s="5">
-        <v>169368</v>
+        <v>170948</v>
       </c>
       <c r="D107" s="5">
-        <v>184047</v>
+        <v>185312</v>
       </c>
     </row>
     <row outlineLevel="0" r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>2017-09</t>
+          <t>2017-10</t>
         </is>
       </c>
       <c r="B108" s="5">
-        <v>606334</v>
+        <v>607838</v>
       </c>
       <c r="C108" s="5">
-        <v>172872</v>
+        <v>169368</v>
       </c>
       <c r="D108" s="5">
-        <v>183599</v>
+        <v>184047</v>
       </c>
     </row>
     <row outlineLevel="0" r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2017-08</t>
+          <t>2017-09</t>
         </is>
       </c>
       <c r="B109" s="5">
-        <v>596567</v>
+        <v>606334</v>
       </c>
       <c r="C109" s="5">
-        <v>170524</v>
+        <v>172872</v>
       </c>
       <c r="D109" s="5">
-        <v>183744</v>
+        <v>183599</v>
       </c>
     </row>
     <row outlineLevel="0" r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>2017-07</t>
+          <t>2017-08</t>
         </is>
       </c>
       <c r="B110" s="5">
-        <v>594414</v>
+        <v>596567</v>
       </c>
       <c r="C110" s="5">
-        <v>173195</v>
+        <v>170524</v>
       </c>
       <c r="D110" s="5">
-        <v>184246</v>
+        <v>183744</v>
       </c>
     </row>
     <row outlineLevel="0" r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2017-06</t>
+          <t>2017-07</t>
         </is>
       </c>
       <c r="B111" s="5">
-        <v>584258</v>
+        <v>594414</v>
       </c>
       <c r="C111" s="5">
-        <v>176707</v>
+        <v>173195</v>
       </c>
       <c r="D111" s="5">
-        <v>187500</v>
+        <v>184246</v>
       </c>
     </row>
     <row outlineLevel="0" r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>2017-05</t>
+          <t>2017-06</t>
         </is>
       </c>
       <c r="B112" s="5">
-        <v>582764</v>
+        <v>584258</v>
       </c>
       <c r="C112" s="5">
-        <v>176970</v>
+        <v>176707</v>
       </c>
       <c r="D112" s="5">
-        <v>185463</v>
+        <v>187500</v>
       </c>
     </row>
     <row outlineLevel="0" r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>2017-04</t>
+          <t>2017-05</t>
         </is>
       </c>
       <c r="B113" s="5">
-        <v>590797</v>
+        <v>582764</v>
       </c>
       <c r="C113" s="5">
-        <v>180908</v>
+        <v>176970</v>
       </c>
       <c r="D113" s="5">
-        <v>184930</v>
+        <v>185463</v>
       </c>
     </row>
     <row outlineLevel="0" r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>2017-03</t>
+          <t>2017-04</t>
         </is>
       </c>
       <c r="B114" s="5">
-        <v>577674</v>
+        <v>590797</v>
       </c>
       <c r="C114" s="5">
-        <v>186892</v>
+        <v>180908</v>
       </c>
       <c r="D114" s="5">
-        <v>184977</v>
+        <v>184930</v>
       </c>
     </row>
     <row outlineLevel="0" r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>2017-02</t>
+          <t>2017-03</t>
         </is>
       </c>
       <c r="B115" s="5">
-        <v>568637</v>
+        <v>577674</v>
       </c>
       <c r="C115" s="5">
-        <v>185720</v>
+        <v>186892</v>
       </c>
       <c r="D115" s="5">
-        <v>184598</v>
+        <v>184977</v>
       </c>
     </row>
     <row outlineLevel="0" r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>2017-01</t>
+          <t>2017-02</t>
         </is>
       </c>
       <c r="B116" s="5">
-        <v>553557</v>
+        <v>568637</v>
       </c>
       <c r="C116" s="5">
-        <v>186301</v>
+        <v>185720</v>
       </c>
       <c r="D116" s="5">
-        <v>186029</v>
+        <v>184598</v>
       </c>
     </row>
     <row outlineLevel="0" r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>2016-12</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="B117" s="5">
-        <v>529372</v>
+        <v>553557</v>
       </c>
       <c r="C117" s="5">
-        <v>188062</v>
+        <v>186301</v>
       </c>
       <c r="D117" s="5">
-        <v>189979</v>
+        <v>186029</v>
       </c>
     </row>
     <row outlineLevel="0" r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>2016-11</t>
+          <t>2016-12</t>
         </is>
       </c>
       <c r="B118" s="5">
-        <v>539972</v>
+        <v>529372</v>
       </c>
       <c r="C118" s="5">
-        <v>179598</v>
+        <v>188062</v>
       </c>
       <c r="D118" s="5">
-        <v>187085</v>
+        <v>189979</v>
       </c>
     </row>
     <row outlineLevel="0" r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>2016-10</t>
+          <t>2016-11</t>
         </is>
       </c>
       <c r="B119" s="5">
-        <v>523760</v>
+        <v>539972</v>
       </c>
       <c r="C119" s="5">
-        <v>182051</v>
+        <v>179598</v>
       </c>
       <c r="D119" s="5">
-        <v>182986</v>
+        <v>187085</v>
       </c>
     </row>
     <row outlineLevel="0" r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>2016-09</t>
+          <t>2016-10</t>
         </is>
       </c>
       <c r="B120" s="5">
-        <v>540615</v>
+        <v>523760</v>
       </c>
       <c r="C120" s="5">
-        <v>184757</v>
+        <v>182051</v>
       </c>
       <c r="D120" s="5">
-        <v>182833</v>
+        <v>182986</v>
       </c>
     </row>
     <row outlineLevel="0" r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>2016-08</t>
+          <t>2016-09</t>
         </is>
       </c>
       <c r="B121" s="5">
-        <v>510157</v>
+        <v>540615</v>
       </c>
       <c r="C121" s="5">
-        <v>177764</v>
+        <v>184757</v>
       </c>
       <c r="D121" s="5">
-        <v>185695</v>
+        <v>182833</v>
       </c>
     </row>
     <row outlineLevel="0" r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>2016-07</t>
+          <t>2016-08</t>
         </is>
       </c>
       <c r="B122" s="5">
-        <v>513221</v>
+        <v>510157</v>
       </c>
       <c r="C122" s="5">
-        <v>183435</v>
+        <v>177764</v>
       </c>
       <c r="D122" s="5">
-        <v>188155</v>
+        <v>185695</v>
       </c>
     </row>
     <row outlineLevel="0" r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>2016-06</t>
+          <t>2016-07</t>
         </is>
       </c>
       <c r="B123" s="5">
-        <v>487636</v>
+        <v>513221</v>
       </c>
       <c r="C123" s="5">
-        <v>186233</v>
+        <v>183435</v>
       </c>
       <c r="D123" s="5">
-        <v>189585</v>
+        <v>188155</v>
       </c>
     </row>
     <row outlineLevel="0" r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>2016-05</t>
+          <t>2016-06</t>
         </is>
       </c>
       <c r="B124" s="5">
-        <v>489867</v>
+        <v>487636</v>
       </c>
       <c r="C124" s="5">
-        <v>177161</v>
+        <v>186233</v>
       </c>
       <c r="D124" s="5">
-        <v>187495</v>
+        <v>189585</v>
       </c>
     </row>
     <row outlineLevel="0" r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>2016-04</t>
+          <t>2016-05</t>
         </is>
       </c>
       <c r="B125" s="5">
-        <v>495178</v>
+        <v>489867</v>
       </c>
       <c r="C125" s="5">
-        <v>176016</v>
+        <v>177161</v>
       </c>
       <c r="D125" s="5">
-        <v>187000</v>
+        <v>187495</v>
       </c>
     </row>
     <row outlineLevel="0" r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>2016-03</t>
+          <t>2016-04</t>
         </is>
       </c>
       <c r="B126" s="5">
-        <v>483909</v>
+        <v>495178</v>
       </c>
       <c r="C126" s="5">
-        <v>182673</v>
+        <v>176016</v>
       </c>
       <c r="D126" s="5">
-        <v>172525</v>
+        <v>187000</v>
       </c>
     </row>
     <row outlineLevel="0" r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>2016-02</t>
+          <t>2016-03</t>
         </is>
       </c>
       <c r="B127" s="5">
-        <v>474156</v>
+        <v>483909</v>
       </c>
       <c r="C127" s="5">
-        <v>178989</v>
+        <v>182673</v>
       </c>
       <c r="D127" s="5">
-        <v>168308</v>
+        <v>172525</v>
       </c>
     </row>
     <row outlineLevel="0" r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>2016-01</t>
+          <t>2016-02</t>
         </is>
       </c>
       <c r="B128" s="5">
-        <v>487200</v>
+        <v>474156</v>
       </c>
       <c r="C128" s="5">
-        <v>180616</v>
+        <v>178989</v>
       </c>
       <c r="D128" s="5">
-        <v>162825</v>
+        <v>168308</v>
       </c>
     </row>
     <row outlineLevel="0" r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>2015-12</t>
+          <t>2016-01</t>
         </is>
       </c>
       <c r="B129" s="5">
-        <v>503444</v>
+        <v>487200</v>
       </c>
       <c r="C129" s="5">
-        <v>181812</v>
+        <v>180616</v>
       </c>
       <c r="D129" s="5">
-        <v>159677</v>
+        <v>162825</v>
       </c>
     </row>
     <row outlineLevel="0" r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>2015-11</t>
+          <t>2015-12</t>
         </is>
       </c>
       <c r="B130" s="5">
-        <v>515410</v>
+        <v>503444</v>
       </c>
       <c r="C130" s="5">
-        <v>174607</v>
+        <v>181812</v>
       </c>
       <c r="D130" s="5">
-        <v>165584</v>
+        <v>159677</v>
       </c>
     </row>
     <row outlineLevel="0" r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>2015-10</t>
+          <t>2015-11</t>
         </is>
       </c>
       <c r="B131" s="5">
-        <v>513941</v>
+        <v>515410</v>
       </c>
       <c r="C131" s="5">
-        <v>174437</v>
+        <v>174607</v>
       </c>
       <c r="D131" s="5">
-        <v>163210</v>
+        <v>165584</v>
       </c>
     </row>
     <row outlineLevel="0" r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>2015-09</t>
+          <t>2015-10</t>
         </is>
       </c>
       <c r="B132" s="5">
-        <v>497279</v>
+        <v>513941</v>
       </c>
       <c r="C132" s="5">
-        <v>173760</v>
+        <v>174437</v>
       </c>
       <c r="D132" s="5">
-        <v>167132</v>
+        <v>163210</v>
       </c>
     </row>
     <row outlineLevel="0" r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2015-09</t>
         </is>
       </c>
       <c r="B133" s="5">
-        <v>515960</v>
+        <v>497279</v>
       </c>
       <c r="C133" s="5">
-        <v>175647</v>
+        <v>173760</v>
       </c>
       <c r="D133" s="5">
-        <v>168692</v>
+        <v>167132</v>
       </c>
     </row>
     <row outlineLevel="0" r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>2015-07</t>
+          <t>2015-08</t>
         </is>
       </c>
       <c r="B134" s="5">
-        <v>530744</v>
+        <v>515960</v>
       </c>
       <c r="C134" s="5">
-        <v>168659</v>
+        <v>175647</v>
       </c>
       <c r="D134" s="5">
-        <v>169132</v>
+        <v>168692</v>
       </c>
     </row>
     <row outlineLevel="0" r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>2015-06</t>
+          <t>2015-07</t>
         </is>
       </c>
       <c r="B135" s="5">
-        <v>547957</v>
+        <v>530744</v>
       </c>
       <c r="C135" s="5">
-        <v>170614</v>
+        <v>168659</v>
       </c>
       <c r="D135" s="5">
-        <v>168441</v>
+        <v>169132</v>
       </c>
     </row>
     <row outlineLevel="0" r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>2015-05</t>
+          <t>2015-06</t>
         </is>
       </c>
       <c r="B136" s="5">
-        <v>541671</v>
+        <v>547957</v>
       </c>
       <c r="C136" s="5">
-        <v>166334</v>
+        <v>170614</v>
       </c>
       <c r="D136" s="5">
-        <v>169076</v>
+        <v>168441</v>
       </c>
     </row>
     <row outlineLevel="0" r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>2015-04</t>
+          <t>2015-05</t>
         </is>
       </c>
       <c r="B137" s="5">
-        <v>549964</v>
+        <v>541671</v>
       </c>
       <c r="C137" s="5">
-        <v>168430</v>
+        <v>166334</v>
       </c>
       <c r="D137" s="5">
-        <v>167073</v>
+        <v>169076</v>
       </c>
     </row>
     <row outlineLevel="0" r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>2015-03</t>
+          <t>2015-04</t>
         </is>
       </c>
       <c r="B138" s="5">
-        <v>518055</v>
+        <v>549964</v>
       </c>
       <c r="C138" s="5">
-        <v>171625</v>
+        <v>168430</v>
       </c>
       <c r="D138" s="5">
-        <v>170074</v>
+        <v>167073</v>
       </c>
     </row>
     <row outlineLevel="0" r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>2015-02</t>
+          <t>2015-03</t>
         </is>
       </c>
       <c r="B139" s="5">
-        <v>504923</v>
+        <v>518055</v>
       </c>
       <c r="C139" s="5">
-        <v>168371</v>
+        <v>171625</v>
       </c>
       <c r="D139" s="5">
-        <v>170930</v>
+        <v>170074</v>
       </c>
     </row>
     <row outlineLevel="0" r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2015-02</t>
         </is>
       </c>
       <c r="B140" s="5">
-        <v>485872</v>
+        <v>504923</v>
       </c>
       <c r="C140" s="5">
-        <v>163599</v>
+        <v>168371</v>
       </c>
       <c r="D140" s="5">
-        <v>178259</v>
+        <v>170930</v>
       </c>
     </row>
     <row outlineLevel="0" r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>2014-12</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="B141" s="5">
-        <v>495756</v>
+        <v>485872</v>
       </c>
       <c r="C141" s="5">
-        <v>169295</v>
+        <v>163599</v>
       </c>
       <c r="D141" s="5">
-        <v>181223</v>
+        <v>178259</v>
       </c>
     </row>
     <row outlineLevel="0" r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>2014-11</t>
+          <t>2014-12</t>
         </is>
       </c>
       <c r="B142" s="5">
-        <v>496341</v>
+        <v>495756</v>
       </c>
       <c r="C142" s="5">
-        <v>158420</v>
+        <v>169295</v>
       </c>
       <c r="D142" s="5">
-        <v>184227</v>
+        <v>181223</v>
       </c>
     </row>
     <row outlineLevel="0" r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>2014-10</t>
+          <t>2014-11</t>
         </is>
       </c>
       <c r="B143" s="5">
-        <v>492888</v>
+        <v>496341</v>
       </c>
       <c r="C143" s="5">
-        <v>158624</v>
+        <v>158420</v>
       </c>
       <c r="D143" s="5">
-        <v>185193</v>
+        <v>184227</v>
       </c>
     </row>
     <row outlineLevel="0" r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>2014-09</t>
+          <t>2014-10</t>
         </is>
       </c>
       <c r="B144" s="5">
-        <v>503901</v>
+        <v>492888</v>
       </c>
       <c r="C144" s="5">
-        <v>161621</v>
+        <v>158624</v>
       </c>
       <c r="D144" s="5">
-        <v>183243</v>
+        <v>185193</v>
       </c>
     </row>
     <row outlineLevel="0" r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2014-09</t>
         </is>
       </c>
       <c r="B145" s="5">
-        <v>501000</v>
+        <v>503901</v>
       </c>
       <c r="C145" s="5">
-        <v>155245</v>
+        <v>161621</v>
       </c>
       <c r="D145" s="5">
-        <v>180820</v>
+        <v>183243</v>
       </c>
     </row>
     <row outlineLevel="0" r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>2014-07</t>
+          <t>2014-08</t>
         </is>
       </c>
       <c r="B146" s="5">
-        <v>498671</v>
+        <v>501000</v>
       </c>
       <c r="C146" s="5">
-        <v>155931</v>
+        <v>155245</v>
       </c>
       <c r="D146" s="5">
-        <v>177981</v>
+        <v>180820</v>
       </c>
     </row>
     <row outlineLevel="0" r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>2014-06</t>
+          <t>2014-07</t>
         </is>
       </c>
       <c r="B147" s="5">
-        <v>502270</v>
+        <v>498671</v>
       </c>
       <c r="C147" s="5">
-        <v>160293</v>
+        <v>155931</v>
       </c>
       <c r="D147" s="5">
-        <v>184723</v>
+        <v>177981</v>
       </c>
     </row>
     <row outlineLevel="0" r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>2014-05</t>
+          <t>2014-06</t>
         </is>
       </c>
       <c r="B148" s="5">
-        <v>475362</v>
+        <v>502270</v>
       </c>
       <c r="C148" s="5">
-        <v>150474</v>
+        <v>160293</v>
       </c>
       <c r="D148" s="5">
-        <v>188551</v>
+        <v>184723</v>
       </c>
     </row>
     <row outlineLevel="0" r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>2014-04</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="B149" s="5">
-        <v>475195</v>
+        <v>475362</v>
       </c>
       <c r="C149" s="5">
-        <v>149801</v>
+        <v>150474</v>
       </c>
       <c r="D149" s="5">
-        <v>194679</v>
+        <v>188551</v>
       </c>
     </row>
     <row outlineLevel="0" r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>2014-03</t>
+          <t>2014-04</t>
         </is>
       </c>
       <c r="B150" s="5">
-        <v>487932</v>
+        <v>475195</v>
       </c>
       <c r="C150" s="5">
-        <v>156083</v>
+        <v>149801</v>
       </c>
       <c r="D150" s="5">
-        <v>194461</v>
+        <v>194679</v>
       </c>
     </row>
     <row outlineLevel="0" r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>2014-02</t>
+          <t>2014-03</t>
         </is>
       </c>
       <c r="B151" s="5">
-        <v>502093</v>
+        <v>487932</v>
       </c>
       <c r="C151" s="5">
-        <v>154049</v>
+        <v>156083</v>
       </c>
       <c r="D151" s="5">
-        <v>190312</v>
+        <v>194461</v>
       </c>
     </row>
     <row outlineLevel="0" r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>2014-01</t>
+          <t>2014-02</t>
         </is>
       </c>
       <c r="B152" s="5">
-        <v>487549</v>
+        <v>502093</v>
       </c>
       <c r="C152" s="5">
-        <v>151878</v>
+        <v>154049</v>
       </c>
       <c r="D152" s="5">
-        <v>195863</v>
+        <v>190312</v>
       </c>
     </row>
     <row outlineLevel="0" r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>2013-12</t>
+          <t>2014-01</t>
         </is>
       </c>
       <c r="B153" s="5">
-        <v>478502</v>
+        <v>487549</v>
       </c>
       <c r="C153" s="5">
-        <v>157000</v>
+        <v>151878</v>
       </c>
       <c r="D153" s="5">
-        <v>197521</v>
+        <v>195863</v>
       </c>
     </row>
     <row outlineLevel="0" r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>2013-11</t>
+          <t>2013-12</t>
         </is>
       </c>
       <c r="B154" s="5">
-        <v>456378</v>
+        <v>478502</v>
       </c>
       <c r="C154" s="5">
-        <v>150214</v>
+        <v>157000</v>
       </c>
       <c r="D154" s="5">
-        <v>199153</v>
+        <v>197521</v>
       </c>
     </row>
     <row outlineLevel="0" r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>2013-10</t>
+          <t>2013-11</t>
         </is>
       </c>
       <c r="B155" s="5">
-        <v>445022</v>
+        <v>456378</v>
       </c>
       <c r="C155" s="5">
-        <v>151494</v>
+        <v>150214</v>
       </c>
       <c r="D155" s="5">
-        <v>199889</v>
+        <v>199153</v>
       </c>
     </row>
     <row outlineLevel="0" r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>2013-09</t>
+          <t>2013-10</t>
         </is>
       </c>
       <c r="B156" s="5">
-        <v>432852</v>
+        <v>445022</v>
       </c>
       <c r="C156" s="5">
-        <v>149895</v>
+        <v>151494</v>
       </c>
       <c r="D156" s="5">
-        <v>197780</v>
+        <v>199889</v>
       </c>
     </row>
     <row outlineLevel="0" r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>2013-08</t>
+          <t>2013-09</t>
         </is>
       </c>
       <c r="B157" s="5">
-        <v>414442</v>
+        <v>432852</v>
       </c>
       <c r="C157" s="5">
-        <v>143808</v>
+        <v>149895</v>
       </c>
       <c r="D157" s="5">
-        <v>195181</v>
+        <v>197780</v>
       </c>
     </row>
     <row outlineLevel="0" r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>2013-07</t>
+          <t>2013-08</t>
         </is>
       </c>
       <c r="B158" s="5">
-        <v>412101</v>
+        <v>414442</v>
       </c>
       <c r="C158" s="5">
-        <v>144495</v>
+        <v>143808</v>
       </c>
       <c r="D158" s="5">
-        <v>194790</v>
+        <v>195181</v>
       </c>
     </row>
     <row outlineLevel="0" r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>2013-06</t>
+          <t>2013-07</t>
         </is>
       </c>
       <c r="B159" s="5">
-        <v>407681</v>
+        <v>412101</v>
       </c>
       <c r="C159" s="5">
-        <v>150093</v>
+        <v>144495</v>
       </c>
       <c r="D159" s="5">
-        <v>200308</v>
+        <v>194790</v>
       </c>
     </row>
     <row outlineLevel="0" r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>2013-05</t>
+          <t>2013-06</t>
         </is>
       </c>
       <c r="B160" s="5">
-        <v>401606</v>
+        <v>407681</v>
       </c>
       <c r="C160" s="5">
-        <v>146765</v>
+        <v>150093</v>
       </c>
       <c r="D160" s="5">
-        <v>199756</v>
+        <v>200308</v>
       </c>
     </row>
     <row outlineLevel="0" r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>2013-04</t>
+          <t>2013-05</t>
         </is>
       </c>
       <c r="B161" s="5">
-        <v>408677</v>
+        <v>401606</v>
       </c>
       <c r="C161" s="5">
-        <v>140706</v>
+        <v>146765</v>
       </c>
       <c r="D161" s="5">
-        <v>191719</v>
+        <v>199756</v>
       </c>
     </row>
     <row outlineLevel="0" r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>2013-03</t>
+          <t>2013-04</t>
         </is>
       </c>
       <c r="B162" s="5">
-        <v>403933</v>
+        <v>408677</v>
       </c>
       <c r="C162" s="5">
-        <v>144530</v>
+        <v>140706</v>
       </c>
       <c r="D162" s="5">
-        <v>197887</v>
+        <v>191719</v>
       </c>
     </row>
     <row outlineLevel="0" r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>2013-02</t>
+          <t>2013-03</t>
         </is>
       </c>
       <c r="B163" s="5">
-        <v>390351</v>
+        <v>403933</v>
       </c>
       <c r="C163" s="5">
-        <v>142123</v>
+        <v>144530</v>
       </c>
       <c r="D163" s="5">
-        <v>208682</v>
+        <v>197887</v>
       </c>
     </row>
     <row outlineLevel="0" r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>2013-01</t>
+          <t>2013-02</t>
         </is>
       </c>
       <c r="B164" s="5">
-        <v>388123</v>
+        <v>390351</v>
       </c>
       <c r="C164" s="5">
-        <v>142856</v>
+        <v>142123</v>
       </c>
       <c r="D164" s="5">
-        <v>199709</v>
+        <v>208682</v>
       </c>
     </row>
     <row outlineLevel="0" r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>2012-12</t>
+          <t>2013-01</t>
         </is>
       </c>
       <c r="B165" s="5">
-        <v>355009</v>
+        <v>388123</v>
       </c>
       <c r="C165" s="5">
-        <v>162206</v>
+        <v>142856</v>
       </c>
       <c r="D165" s="5">
-        <v>211576</v>
+        <v>199709</v>
       </c>
     </row>
     <row outlineLevel="0" r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>2012-11</t>
+          <t>2012-12</t>
         </is>
       </c>
       <c r="B166" s="5">
-        <v>351441</v>
+        <v>355009</v>
       </c>
       <c r="C166" s="5">
-        <v>135650</v>
+        <v>162206</v>
       </c>
       <c r="D166" s="5">
-        <v>202425</v>
+        <v>211576</v>
       </c>
     </row>
     <row outlineLevel="0" r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>2012-10</t>
+          <t>2012-11</t>
         </is>
       </c>
       <c r="B167" s="5">
-        <v>342325</v>
+        <v>351441</v>
       </c>
       <c r="C167" s="5">
-        <v>124800</v>
+        <v>135650</v>
       </c>
       <c r="D167" s="5">
-        <v>200406</v>
+        <v>202425</v>
       </c>
     </row>
     <row outlineLevel="0" r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>2012-09</t>
+          <t>2012-10</t>
         </is>
       </c>
       <c r="B168" s="5">
-        <v>339159</v>
+        <v>342325</v>
       </c>
       <c r="C168" s="5">
-        <v>129389</v>
+        <v>124800</v>
       </c>
       <c r="D168" s="5">
-        <v>205176</v>
+        <v>200406</v>
       </c>
     </row>
     <row outlineLevel="0" r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>2012-08</t>
+          <t>2012-09</t>
         </is>
       </c>
       <c r="B169" s="5">
-        <v>320395</v>
+        <v>339159</v>
       </c>
       <c r="C169" s="5">
-        <v>124276</v>
+        <v>129389</v>
       </c>
       <c r="D169" s="5">
-        <v>196786</v>
+        <v>205176</v>
       </c>
     </row>
     <row outlineLevel="0" r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>2012-07</t>
+          <t>2012-08</t>
         </is>
       </c>
       <c r="B170" s="5">
-        <v>313525</v>
+        <v>320395</v>
       </c>
       <c r="C170" s="5">
-        <v>124330</v>
+        <v>124276</v>
       </c>
       <c r="D170" s="5">
-        <v>194741</v>
+        <v>196786</v>
       </c>
     </row>
     <row outlineLevel="0" r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>2012-06</t>
+          <t>2012-07</t>
         </is>
       </c>
       <c r="B171" s="5">
-        <v>320952</v>
+        <v>313525</v>
       </c>
       <c r="C171" s="5">
-        <v>138937</v>
+        <v>124330</v>
       </c>
       <c r="D171" s="5">
-        <v>192149</v>
+        <v>194741</v>
       </c>
     </row>
     <row outlineLevel="0" r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>2012-05</t>
+          <t>2012-06</t>
         </is>
       </c>
       <c r="B172" s="5">
-        <v>315147</v>
+        <v>320952</v>
       </c>
       <c r="C172" s="5">
-        <v>139111</v>
+        <v>138937</v>
       </c>
       <c r="D172" s="5">
-        <v>187938</v>
+        <v>192149</v>
       </c>
     </row>
     <row outlineLevel="0" r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>2012-04</t>
+          <t>2012-05</t>
         </is>
       </c>
       <c r="B173" s="5">
-        <v>335154</v>
+        <v>315147</v>
       </c>
       <c r="C173" s="5">
-        <v>138909</v>
+        <v>139111</v>
       </c>
       <c r="D173" s="5">
-        <v>182021</v>
+        <v>187938</v>
       </c>
     </row>
     <row outlineLevel="0" r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>2012-03</t>
+          <t>2012-04</t>
         </is>
       </c>
       <c r="B174" s="5">
-        <v>330815</v>
+        <v>335154</v>
       </c>
       <c r="C174" s="5">
-        <v>142297</v>
+        <v>138909</v>
       </c>
       <c r="D174" s="5">
-        <v>182814</v>
+        <v>182021</v>
       </c>
     </row>
     <row outlineLevel="0" r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>2012-02</t>
+          <t>2012-03</t>
         </is>
       </c>
       <c r="B175" s="5">
-        <v>323021</v>
+        <v>330815</v>
       </c>
       <c r="C175" s="5">
-        <v>139609</v>
+        <v>142297</v>
       </c>
       <c r="D175" s="5">
-        <v>177639</v>
+        <v>182814</v>
       </c>
     </row>
     <row outlineLevel="0" r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>2012-01</t>
+          <t>2012-02</t>
         </is>
       </c>
       <c r="B176" s="5">
-        <v>309844</v>
+        <v>323021</v>
       </c>
       <c r="C176" s="5">
-        <v>137309</v>
+        <v>139609</v>
       </c>
       <c r="D176" s="5">
-        <v>174889</v>
+        <v>177639</v>
       </c>
     </row>
     <row outlineLevel="0" r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>2011-12</t>
+          <t>2012-01</t>
         </is>
       </c>
       <c r="B177" s="5">
-        <v>301616</v>
+        <v>309844</v>
       </c>
       <c r="C177" s="5">
-        <v>142533</v>
+        <v>137309</v>
       </c>
       <c r="D177" s="5">
-        <v>189143</v>
+        <v>174889</v>
       </c>
     </row>
     <row outlineLevel="0" r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>2011-11</t>
+          <t>2011-12</t>
         </is>
       </c>
       <c r="B178" s="5">
-        <v>303930</v>
+        <v>301616</v>
       </c>
       <c r="C178" s="5">
-        <v>132934</v>
+        <v>142533</v>
       </c>
       <c r="D178" s="5">
-        <v>188259</v>
+        <v>189143</v>
       </c>
     </row>
     <row outlineLevel="0" r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>2011-10</t>
+          <t>2011-11</t>
         </is>
       </c>
       <c r="B179" s="5">
-        <v>317028</v>
+        <v>303930</v>
       </c>
       <c r="C179" s="5">
-        <v>133639</v>
+        <v>132934</v>
       </c>
       <c r="D179" s="5">
-        <v>188141</v>
+        <v>188259</v>
       </c>
     </row>
     <row outlineLevel="0" r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>2011-09</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="B180" s="5">
-        <v>298277</v>
+        <v>317028</v>
       </c>
       <c r="C180" s="5">
-        <v>141806</v>
+        <v>133639</v>
       </c>
       <c r="D180" s="5">
-        <v>204307</v>
+        <v>188141</v>
       </c>
     </row>
     <row outlineLevel="0" r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>2011-08</t>
+          <t>2011-09</t>
         </is>
       </c>
       <c r="B181" s="5">
-        <v>308866</v>
+        <v>298277</v>
       </c>
       <c r="C181" s="5">
-        <v>135508</v>
+        <v>141806</v>
       </c>
       <c r="D181" s="5">
-        <v>193533</v>
+        <v>204307</v>
       </c>
     </row>
     <row outlineLevel="0" r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>2011-07</t>
+          <t>2011-08</t>
         </is>
       </c>
       <c r="B182" s="5">
-        <v>344572</v>
+        <v>308866</v>
       </c>
       <c r="C182" s="5">
-        <v>138316</v>
+        <v>135508</v>
       </c>
       <c r="D182" s="5">
-        <v>182957</v>
+        <v>193533</v>
       </c>
     </row>
     <row outlineLevel="0" r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>2011-06</t>
+          <t>2011-07</t>
         </is>
       </c>
       <c r="B183" s="5">
-        <v>345273</v>
+        <v>344572</v>
       </c>
       <c r="C183" s="5">
-        <v>139575</v>
+        <v>138316</v>
       </c>
       <c r="D183" s="5">
-        <v>183547</v>
+        <v>182957</v>
       </c>
     </row>
     <row outlineLevel="0" r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>2011-05</t>
+          <t>2011-06</t>
         </is>
       </c>
       <c r="B184" s="5">
-        <v>355736</v>
+        <v>345273</v>
       </c>
       <c r="C184" s="5">
-        <v>133727</v>
+        <v>139575</v>
       </c>
       <c r="D184" s="5">
-        <v>175508</v>
+        <v>183547</v>
       </c>
     </row>
     <row outlineLevel="0" r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>2011-04</t>
+          <t>2011-05</t>
         </is>
       </c>
       <c r="B185" s="5">
-        <v>360883</v>
+        <v>355736</v>
       </c>
       <c r="C185" s="5">
-        <v>133131</v>
+        <v>133727</v>
       </c>
       <c r="D185" s="5">
-        <v>175399</v>
+        <v>175508</v>
       </c>
     </row>
     <row outlineLevel="0" r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>2011-03</t>
+          <t>2011-04</t>
         </is>
       </c>
       <c r="B186" s="5">
-        <v>355413</v>
+        <v>360883</v>
       </c>
       <c r="C186" s="5">
-        <v>133386</v>
+        <v>133131</v>
       </c>
       <c r="D186" s="5">
-        <v>170139</v>
+        <v>175399</v>
       </c>
     </row>
     <row outlineLevel="0" r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>2011-02</t>
+          <t>2011-03</t>
         </is>
       </c>
       <c r="B187" s="5">
-        <v>348979</v>
+        <v>355413</v>
       </c>
       <c r="C187" s="5">
-        <v>135760</v>
+        <v>133386</v>
       </c>
       <c r="D187" s="5">
-        <v>179102</v>
+        <v>170139</v>
       </c>
     </row>
     <row outlineLevel="0" r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>2011-01</t>
+          <t>2011-02</t>
         </is>
       </c>
       <c r="B188" s="5">
-        <v>326868</v>
+        <v>348979</v>
       </c>
       <c r="C188" s="5">
-        <v>130894</v>
+        <v>135760</v>
       </c>
       <c r="D188" s="5">
-        <v>173545</v>
+        <v>179102</v>
       </c>
     </row>
     <row outlineLevel="0" r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>2010-12</t>
+          <t>2011-01</t>
         </is>
       </c>
       <c r="B189" s="5">
-        <v>313678</v>
+        <v>326868</v>
       </c>
       <c r="C189" s="5">
-        <v>126098</v>
+        <v>130894</v>
       </c>
       <c r="D189" s="5">
-        <v>182426</v>
+        <v>173545</v>
       </c>
     </row>
     <row outlineLevel="0" r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>2010-11</t>
+          <t>2010-12</t>
         </is>
       </c>
       <c r="B190" s="5">
-        <v>309340</v>
+        <v>313678</v>
       </c>
       <c r="C190" s="5">
-        <v>119305</v>
+        <v>126098</v>
       </c>
       <c r="D190" s="5">
-        <v>176805</v>
+        <v>182426</v>
       </c>
     </row>
     <row outlineLevel="0" r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>2010-10</t>
+          <t>2010-11</t>
         </is>
       </c>
       <c r="B191" s="5">
-        <v>303428</v>
+        <v>309340</v>
       </c>
       <c r="C191" s="5">
-        <v>114784</v>
+        <v>119305</v>
       </c>
       <c r="D191" s="5">
-        <v>176588</v>
+        <v>176805</v>
       </c>
     </row>
     <row outlineLevel="0" r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>2010-09</t>
+          <t>2010-10</t>
         </is>
       </c>
       <c r="B192" s="5">
-        <v>288540</v>
+        <v>303428</v>
       </c>
       <c r="C192" s="5">
-        <v>114321</v>
+        <v>114784</v>
       </c>
       <c r="D192" s="5">
-        <v>173544</v>
+        <v>176588</v>
       </c>
     </row>
     <row outlineLevel="0" r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>2010-08</t>
+          <t>2010-09</t>
         </is>
       </c>
       <c r="B193" s="5">
-        <v>268371</v>
+        <v>288540</v>
       </c>
       <c r="C193" s="5">
-        <v>106870</v>
+        <v>114321</v>
       </c>
       <c r="D193" s="5">
-        <v>174209</v>
+        <v>173544</v>
       </c>
     </row>
     <row outlineLevel="0" r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>2010-07</t>
+          <t>2010-08</t>
         </is>
       </c>
       <c r="B194" s="5">
-        <v>267468</v>
+        <v>268371</v>
       </c>
       <c r="C194" s="5">
-        <v>106290</v>
+        <v>106870</v>
       </c>
       <c r="D194" s="5">
-        <v>172179</v>
+        <v>174209</v>
       </c>
     </row>
     <row outlineLevel="0" r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>2010-06</t>
+          <t>2010-07</t>
         </is>
       </c>
       <c r="B195" s="5">
-        <v>263202</v>
+        <v>267468</v>
       </c>
       <c r="C195" s="5">
-        <v>114265</v>
+        <v>106290</v>
       </c>
       <c r="D195" s="5">
-        <v>172908</v>
+        <v>172179</v>
       </c>
     </row>
     <row outlineLevel="0" r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>2010-05</t>
+          <t>2010-06</t>
         </is>
       </c>
       <c r="B196" s="5">
-        <v>268566</v>
+        <v>263202</v>
       </c>
       <c r="C196" s="5">
-        <v>114051</v>
+        <v>114265</v>
       </c>
       <c r="D196" s="5">
-        <v>166706</v>
+        <v>172908</v>
       </c>
     </row>
     <row outlineLevel="0" r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>2010-04</t>
+          <t>2010-05</t>
         </is>
       </c>
       <c r="B197" s="5">
-        <v>295550</v>
+        <v>268566</v>
       </c>
       <c r="C197" s="5">
-        <v>111217</v>
+        <v>114051</v>
       </c>
       <c r="D197" s="5">
-        <v>160630</v>
+        <v>166706</v>
       </c>
     </row>
     <row outlineLevel="0" r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>2010-03</t>
+          <t>2010-04</t>
         </is>
       </c>
       <c r="B198" s="5">
-        <v>277798</v>
+        <v>295550</v>
       </c>
       <c r="C198" s="5">
-        <v>108908</v>
+        <v>111217</v>
       </c>
       <c r="D198" s="5">
-        <v>162169</v>
+        <v>160630</v>
       </c>
     </row>
     <row outlineLevel="0" r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>2010-02</t>
+          <t>2010-03</t>
         </is>
       </c>
       <c r="B199" s="5">
-        <v>263657</v>
+        <v>277798</v>
       </c>
       <c r="C199" s="5">
-        <v>106131</v>
+        <v>108908</v>
       </c>
       <c r="D199" s="5">
-        <v>164624</v>
+        <v>162169</v>
       </c>
     </row>
     <row outlineLevel="0" r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>2010-01</t>
+          <t>2010-02</t>
         </is>
       </c>
       <c r="B200" s="5">
-        <v>266455</v>
+        <v>263657</v>
       </c>
       <c r="C200" s="5">
-        <v>281035</v>
+        <v>106131</v>
+      </c>
+      <c r="D200" s="5">
+        <v>164624</v>
       </c>
     </row>
     <row outlineLevel="0" r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2010-01</t>
         </is>
       </c>
       <c r="B201" s="5">
-        <v>262399</v>
+        <v>266455</v>
       </c>
       <c r="C201" s="5">
-        <v>281043</v>
+        <v>281035</v>
       </c>
     </row>
     <row outlineLevel="0" r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-12</t>
         </is>
       </c>
       <c r="B202" s="5">
-        <v>250988</v>
+        <v>262399</v>
       </c>
       <c r="C202" s="5">
-        <v>284071</v>
+        <v>281043</v>
       </c>
     </row>
     <row outlineLevel="0" r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-11</t>
         </is>
       </c>
       <c r="B203" s="5">
-        <v>265404</v>
+        <v>250988</v>
       </c>
       <c r="C203" s="5">
-        <v>299858</v>
+        <v>284071</v>
       </c>
     </row>
     <row outlineLevel="0" r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-10</t>
         </is>
       </c>
       <c r="B204" s="5">
-        <v>254107</v>
+        <v>265404</v>
       </c>
       <c r="C204" s="5">
-        <v>287196</v>
+        <v>299858</v>
       </c>
     </row>
     <row outlineLevel="0" r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-09</t>
         </is>
       </c>
       <c r="B205" s="5">
-        <v>236251</v>
+        <v>254107</v>
       </c>
       <c r="C205" s="5">
-        <v>281989</v>
+        <v>287196</v>
       </c>
     </row>
     <row outlineLevel="0" r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-08</t>
         </is>
       </c>
       <c r="B206" s="5">
-        <v>228734</v>
+        <v>236251</v>
       </c>
       <c r="C206" s="5">
-        <v>277082</v>
+        <v>281989</v>
       </c>
     </row>
     <row outlineLevel="0" r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="B207" s="5">
-        <v>217140</v>
+        <v>228734</v>
       </c>
       <c r="C207" s="5">
-        <v>283874</v>
+        <v>277082</v>
       </c>
     </row>
     <row outlineLevel="0" r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="B208" s="5">
-        <v>214401</v>
+        <v>217140</v>
       </c>
       <c r="C208" s="5">
-        <v>275313</v>
+        <v>283874</v>
       </c>
     </row>
     <row outlineLevel="0" r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="B209" s="5">
-        <v>208010</v>
+        <v>214401</v>
       </c>
       <c r="C209" s="5">
-        <v>285658</v>
+        <v>275313</v>
       </c>
     </row>
     <row outlineLevel="0" r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="B210" s="5">
-        <v>203967</v>
+        <v>208010</v>
       </c>
       <c r="C210" s="5">
-        <v>291927</v>
+        <v>285658</v>
       </c>
     </row>
     <row outlineLevel="0" r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="B211" s="5">
-        <v>199655</v>
+        <v>203967</v>
       </c>
       <c r="C211" s="5">
-        <v>310503</v>
+        <v>291927</v>
       </c>
     </row>
     <row outlineLevel="0" r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="B212" s="5">
-        <v>205007</v>
+        <v>199655</v>
       </c>
       <c r="C212" s="5">
-        <v>316763</v>
+        <v>310503</v>
       </c>
     </row>
     <row outlineLevel="0" r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="B213" s="5">
-        <v>210185</v>
+        <v>205007</v>
       </c>
       <c r="C213" s="5">
-        <v>345713</v>
+        <v>316763</v>
       </c>
     </row>
     <row outlineLevel="0" r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="B214" s="5">
-        <v>227334</v>
+        <v>210185</v>
       </c>
       <c r="C214" s="5">
-        <v>364232</v>
+        <v>345713</v>
       </c>
     </row>
     <row outlineLevel="0" r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="B215" s="5">
-        <v>277568</v>
+        <v>227334</v>
       </c>
       <c r="C215" s="5">
-        <v>383429</v>
+        <v>364232</v>
       </c>
     </row>
     <row outlineLevel="0" r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="B216" s="5">
-        <v>345745</v>
+        <v>277568</v>
       </c>
       <c r="C216" s="5">
-        <v>381702</v>
+        <v>383429</v>
       </c>
     </row>
     <row outlineLevel="0" r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="B217" s="5">
-        <v>324814</v>
+        <v>345745</v>
       </c>
       <c r="C217" s="5">
-        <v>530042</v>
+        <v>381702</v>
       </c>
     </row>
     <row outlineLevel="0" r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="B218" s="5">
-        <v>343297</v>
+        <v>324814</v>
       </c>
       <c r="C218" s="5">
-        <v>519226</v>
+        <v>530042</v>
       </c>
     </row>
     <row outlineLevel="0" r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>2008-06</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="B219" s="5">
-        <v>346892</v>
+        <v>343297</v>
       </c>
       <c r="C219" s="5">
-        <v>499634</v>
+        <v>519226</v>
       </c>
     </row>
     <row outlineLevel="0" r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>2008-05</t>
+          <t>2008-06</t>
         </is>
       </c>
       <c r="B220" s="5">
-        <v>341610</v>
+        <v>346892</v>
       </c>
       <c r="C220" s="5">
-        <v>470188</v>
+        <v>499634</v>
       </c>
     </row>
     <row outlineLevel="0" r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>2008-04</t>
+          <t>2008-05</t>
         </is>
       </c>
       <c r="B221" s="5">
-        <v>332303</v>
+        <v>341610</v>
       </c>
       <c r="C221" s="5">
-        <v>472371</v>
+        <v>470188</v>
       </c>
     </row>
     <row outlineLevel="0" r="222">
       <c r="A222" s="4" t="inlineStr">
         <is>
-          <t>2008-03</t>
+          <t>2008-04</t>
         </is>
       </c>
       <c r="B222" s="5">
-        <v>349419</v>
+        <v>332303</v>
       </c>
       <c r="C222" s="5">
-        <v>488831</v>
+        <v>472371</v>
       </c>
     </row>
     <row outlineLevel="0" r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>2008-02</t>
+          <t>2008-03</t>
         </is>
       </c>
       <c r="B223" s="5">
-        <v>377088</v>
+        <v>349419</v>
       </c>
       <c r="C223" s="5">
-        <v>454785</v>
+        <v>488831</v>
       </c>
     </row>
     <row outlineLevel="0" r="224">
       <c r="A224" s="4" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2008-02</t>
         </is>
       </c>
       <c r="B224" s="5">
-        <v>365592</v>
+        <v>377088</v>
       </c>
       <c r="C224" s="5">
-        <v>474496</v>
+        <v>454785</v>
       </c>
     </row>
     <row outlineLevel="0" r="225">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>2007-12</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="B225" s="5">
-        <v>355292</v>
+        <v>365592</v>
       </c>
       <c r="C225" s="5">
-        <v>456353</v>
+        <v>474496</v>
       </c>
     </row>
     <row outlineLevel="0" r="226">
       <c r="A226" s="4" t="inlineStr">
         <is>
-          <t>2007-11</t>
+          <t>2007-12</t>
         </is>
       </c>
       <c r="B226" s="5">
-        <v>379593</v>
+        <v>355292</v>
       </c>
       <c r="C226" s="5">
-        <v>426721</v>
+        <v>456353</v>
       </c>
     </row>
     <row outlineLevel="0" r="227">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>2007-10</t>
+          <t>2007-11</t>
         </is>
       </c>
       <c r="B227" s="5">
-        <v>376979</v>
+        <v>379593</v>
       </c>
       <c r="C227" s="5">
-        <v>392543</v>
+        <v>426721</v>
       </c>
     </row>
     <row outlineLevel="0" r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
-          <t>2007-09</t>
+          <t>2007-10</t>
         </is>
       </c>
       <c r="B228" s="5">
-        <v>359104</v>
+        <v>376979</v>
       </c>
       <c r="C228" s="5">
-        <v>377364</v>
+        <v>392543</v>
       </c>
     </row>
     <row outlineLevel="0" r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>2007-08</t>
+          <t>2007-09</t>
         </is>
       </c>
       <c r="B229" s="5">
-        <v>362475</v>
+        <v>359104</v>
       </c>
       <c r="C229" s="5">
-        <v>381550</v>
+        <v>377364</v>
       </c>
     </row>
     <row outlineLevel="0" r="230">
       <c r="A230" s="4" t="inlineStr">
         <is>
-          <t>2007-07</t>
+          <t>2007-08</t>
         </is>
       </c>
       <c r="B230" s="5">
-        <v>416403</v>
+        <v>362475</v>
       </c>
       <c r="C230" s="5">
-        <v>380971</v>
+        <v>381550</v>
       </c>
     </row>
     <row outlineLevel="0" r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>2007-06</t>
+          <t>2007-07</t>
         </is>
       </c>
       <c r="B231" s="5">
-        <v>408444</v>
+        <v>416403</v>
       </c>
       <c r="C231" s="5">
-        <v>347617</v>
+        <v>380971</v>
       </c>
     </row>
     <row outlineLevel="0" r="232">
       <c r="A232" s="4" t="inlineStr">
         <is>
-          <t>2007-05</t>
+          <t>2007-06</t>
         </is>
       </c>
       <c r="B232" s="5">
-        <v>382312</v>
+        <v>408444</v>
       </c>
       <c r="C232" s="5">
-        <v>334359</v>
+        <v>347617</v>
       </c>
     </row>
     <row outlineLevel="0" r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>2007-04</t>
+          <t>2007-05</t>
         </is>
       </c>
       <c r="B233" s="5">
-        <v>342084</v>
+        <v>382312</v>
       </c>
       <c r="C233" s="5">
-        <v>314744</v>
+        <v>334359</v>
       </c>
     </row>
     <row outlineLevel="0" r="234">
       <c r="A234" s="4" t="inlineStr">
         <is>
-          <t>2007-03</t>
+          <t>2007-04</t>
         </is>
       </c>
       <c r="B234" s="5">
-        <v>317737</v>
+        <v>342084</v>
       </c>
       <c r="C234" s="5">
-        <v>305479</v>
+        <v>314744</v>
       </c>
     </row>
     <row outlineLevel="0" r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>2007-02</t>
+          <t>2007-03</t>
         </is>
       </c>
       <c r="B235" s="5">
-        <v>321171</v>
+        <v>317737</v>
       </c>
       <c r="C235" s="5">
-        <v>300072</v>
+        <v>305479</v>
       </c>
     </row>
     <row outlineLevel="0" r="236">
       <c r="A236" s="4" t="inlineStr">
         <is>
-          <t>2007-01</t>
+          <t>2007-02</t>
         </is>
       </c>
       <c r="B236" s="5">
-        <v>311506</v>
+        <v>321171</v>
       </c>
       <c r="C236" s="5">
-        <v>292521</v>
+        <v>300072</v>
       </c>
     </row>
     <row outlineLevel="0" r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>2006-12</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="B237" s="5">
-        <v>303288</v>
+        <v>311506</v>
       </c>
       <c r="C237" s="5">
-        <v>299023</v>
+        <v>292521</v>
       </c>
     </row>
     <row outlineLevel="0" r="238">
       <c r="A238" s="4" t="inlineStr">
         <is>
-          <t>2006-11</t>
+          <t>2006-12</t>
         </is>
       </c>
       <c r="B238" s="5">
-        <v>294899</v>
+        <v>303288</v>
       </c>
       <c r="C238" s="5">
-        <v>290910</v>
+        <v>299023</v>
       </c>
     </row>
     <row outlineLevel="0" r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>2006-10</t>
+          <t>2006-11</t>
         </is>
       </c>
       <c r="B239" s="5">
-        <v>267710</v>
+        <v>294899</v>
       </c>
       <c r="C239" s="5">
-        <v>267462</v>
+        <v>290910</v>
       </c>
     </row>
     <row outlineLevel="0" r="240">
       <c r="A240" s="4" t="inlineStr">
         <is>
-          <t>2006-09</t>
+          <t>2006-10</t>
         </is>
       </c>
       <c r="B240" s="5">
-        <v>261769</v>
+        <v>267710</v>
       </c>
       <c r="C240" s="5">
-        <v>268612</v>
+        <v>267462</v>
       </c>
     </row>
     <row outlineLevel="0" r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>2006-08</t>
+          <t>2006-09</t>
         </is>
       </c>
       <c r="B241" s="5">
-        <v>249368</v>
+        <v>261769</v>
       </c>
       <c r="C241" s="5">
-        <v>269423</v>
+        <v>268612</v>
       </c>
     </row>
     <row outlineLevel="0" r="242">
       <c r="A242" s="4" t="inlineStr">
         <is>
-          <t>2006-07</t>
+          <t>2006-08</t>
         </is>
       </c>
       <c r="B242" s="5">
-        <v>256016</v>
+        <v>249368</v>
       </c>
       <c r="C242" s="5">
-        <v>269376</v>
+        <v>269423</v>
       </c>
     </row>
     <row outlineLevel="0" r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>2006-06</t>
+          <t>2006-07</t>
         </is>
       </c>
       <c r="B243" s="5">
-        <v>251495</v>
+        <v>256016</v>
       </c>
       <c r="C243" s="5">
-        <v>280275</v>
+        <v>269376</v>
       </c>
     </row>
     <row outlineLevel="0" r="244">
       <c r="A244" s="4" t="inlineStr">
         <is>
-          <t>2006-05</t>
+          <t>2006-06</t>
         </is>
       </c>
       <c r="B244" s="5">
-        <v>255608</v>
+        <v>251495</v>
       </c>
       <c r="C244" s="5">
-        <v>264307</v>
+        <v>280275</v>
       </c>
     </row>
     <row outlineLevel="0" r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>2006-04</t>
+          <t>2006-05</t>
         </is>
       </c>
       <c r="B245" s="5">
-        <v>265164</v>
+        <v>255608</v>
       </c>
       <c r="C245" s="5">
-        <v>259342</v>
+        <v>264307</v>
       </c>
     </row>
     <row outlineLevel="0" r="246">
       <c r="A246" s="4" t="inlineStr">
         <is>
-          <t>2006-03</t>
+          <t>2006-04</t>
         </is>
       </c>
       <c r="B246" s="5">
-        <v>259370</v>
+        <v>265164</v>
       </c>
       <c r="C246" s="5">
-        <v>258928</v>
+        <v>259342</v>
       </c>
     </row>
     <row outlineLevel="0" r="247">
       <c r="A247" s="4" t="inlineStr">
         <is>
-          <t>2006-02</t>
+          <t>2006-03</t>
         </is>
       </c>
       <c r="B247" s="5">
-        <v>249609</v>
+        <v>259370</v>
       </c>
       <c r="C247" s="5">
-        <v>257573</v>
+        <v>258928</v>
       </c>
     </row>
     <row outlineLevel="0" r="248">
       <c r="A248" s="4" t="inlineStr">
         <is>
-          <t>2006-01</t>
+          <t>2006-02</t>
         </is>
       </c>
       <c r="B248" s="5">
-        <v>255795</v>
+        <v>249609</v>
       </c>
       <c r="C248" s="5">
-        <v>255819</v>
+        <v>257573</v>
       </c>
     </row>
     <row outlineLevel="0" r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>2005-12</t>
+          <t>2006-01</t>
         </is>
       </c>
       <c r="B249" s="5">
-        <v>244098</v>
+        <v>255795</v>
       </c>
       <c r="C249" s="5">
-        <v>263205</v>
+        <v>255819</v>
       </c>
     </row>
     <row outlineLevel="0" r="250">
       <c r="A250" s="4" t="inlineStr">
         <is>
-          <t>2005-11</t>
+          <t>2005-12</t>
         </is>
       </c>
       <c r="B250" s="5">
-        <v>242904</v>
+        <v>244098</v>
       </c>
       <c r="C250" s="5">
-        <v>241695</v>
+        <v>263205</v>
       </c>
     </row>
     <row outlineLevel="0" r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>2005-10</t>
+          <t>2005-11</t>
         </is>
       </c>
       <c r="B251" s="5">
-        <v>239868</v>
+        <v>242904</v>
       </c>
       <c r="C251" s="5">
-        <v>243174</v>
+        <v>241695</v>
       </c>
     </row>
     <row outlineLevel="0" r="252">
       <c r="A252" s="4" t="inlineStr">
         <is>
-          <t>2005-09</t>
+          <t>2005-10</t>
         </is>
       </c>
       <c r="B252" s="5">
-        <v>244669</v>
+        <v>239868</v>
       </c>
       <c r="C252" s="5">
-        <v>238929</v>
+        <v>243174</v>
       </c>
     </row>
     <row outlineLevel="0" r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>2005-08</t>
+          <t>2005-09</t>
         </is>
       </c>
       <c r="B253" s="5">
-        <v>231400</v>
+        <v>244669</v>
       </c>
       <c r="C253" s="5">
-        <v>225410</v>
+        <v>238929</v>
       </c>
     </row>
     <row outlineLevel="0" r="254">
       <c r="A254" s="4" t="inlineStr">
         <is>
-          <t>2005-07</t>
+          <t>2005-08</t>
         </is>
       </c>
       <c r="B254" s="5">
-        <v>233585</v>
+        <v>231400</v>
       </c>
       <c r="C254" s="5">
-        <v>224242</v>
+        <v>225410</v>
       </c>
     </row>
     <row outlineLevel="0" r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>2005-06</t>
+          <t>2005-07</t>
         </is>
       </c>
       <c r="B255" s="5">
-        <v>224153</v>
+        <v>233585</v>
       </c>
       <c r="C255" s="5">
-        <v>234352</v>
+        <v>224242</v>
       </c>
     </row>
     <row outlineLevel="0" r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>2005-05</t>
+          <t>2005-06</t>
         </is>
       </c>
       <c r="B256" s="5">
-        <v>219404</v>
+        <v>224153</v>
       </c>
       <c r="C256" s="5">
-        <v>224933</v>
+        <v>234352</v>
       </c>
     </row>
     <row outlineLevel="0" r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>2005-04</t>
+          <t>2005-05</t>
         </is>
       </c>
       <c r="B257" s="5">
-        <v>217447</v>
+        <v>219404</v>
       </c>
       <c r="C257" s="5">
-        <v>223839</v>
+        <v>224933</v>
       </c>
     </row>
     <row outlineLevel="0" r="258">
       <c r="A258" s="4" t="inlineStr">
         <is>
-          <t>2005-03</t>
+          <t>2005-04</t>
         </is>
       </c>
       <c r="B258" s="5">
-        <v>226876</v>
+        <v>217447</v>
       </c>
       <c r="C258" s="5">
-        <v>234533</v>
+        <v>223839</v>
       </c>
     </row>
     <row outlineLevel="0" r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>2005-02</t>
+          <t>2005-03</t>
         </is>
       </c>
       <c r="B259" s="5">
-        <v>223155</v>
+        <v>226876</v>
       </c>
       <c r="C259" s="5">
-        <v>224392</v>
+        <v>234533</v>
       </c>
     </row>
     <row outlineLevel="0" r="260">
       <c r="A260" s="4" t="inlineStr">
         <is>
-          <t>2005-01</t>
+          <t>2005-02</t>
         </is>
       </c>
       <c r="B260" s="5">
-        <v>220122</v>
+        <v>223155</v>
       </c>
       <c r="C260" s="5">
-        <v>230624</v>
+        <v>224392</v>
       </c>
     </row>
     <row outlineLevel="0" r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2005-01</t>
         </is>
       </c>
       <c r="B261" s="5">
-        <v>217573</v>
+        <v>220122</v>
       </c>
       <c r="C261" s="5">
-        <v>238192</v>
+        <v>230624</v>
       </c>
     </row>
     <row outlineLevel="0" r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>2004-11</t>
+          <t>2004-12</t>
         </is>
       </c>
       <c r="B262" s="5">
-        <v>211012</v>
+        <v>217573</v>
       </c>
       <c r="C262" s="5">
-        <v>223928</v>
+        <v>238192</v>
       </c>
     </row>
     <row outlineLevel="0" r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>2004-10</t>
+          <t>2004-11</t>
         </is>
       </c>
       <c r="B263" s="5">
-        <v>197999</v>
+        <v>211012</v>
       </c>
       <c r="C263" s="5">
-        <v>218090</v>
+        <v>223928</v>
       </c>
     </row>
     <row outlineLevel="0" r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>2004-09</t>
+          <t>2004-10</t>
         </is>
       </c>
       <c r="B264" s="5">
-        <v>193668</v>
+        <v>197999</v>
       </c>
       <c r="C264" s="5">
-        <v>220860</v>
+        <v>218090</v>
       </c>
     </row>
     <row outlineLevel="0" r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>2004-08</t>
+          <t>2004-09</t>
         </is>
       </c>
       <c r="B265" s="5">
-        <v>187828</v>
+        <v>193668</v>
       </c>
       <c r="C265" s="5">
-        <v>217945</v>
+        <v>220860</v>
       </c>
     </row>
     <row outlineLevel="0" r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>2004-07</t>
+          <t>2004-08</t>
         </is>
       </c>
       <c r="B266" s="5">
-        <v>187844</v>
+        <v>187828</v>
       </c>
       <c r="C266" s="5">
-        <v>220196</v>
+        <v>217945</v>
       </c>
     </row>
     <row outlineLevel="0" r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>2004-06</t>
+          <t>2004-07</t>
         </is>
       </c>
       <c r="B267" s="5">
-        <v>193993</v>
+        <v>187844</v>
       </c>
       <c r="C267" s="5">
-        <v>220781</v>
+        <v>220196</v>
       </c>
     </row>
     <row outlineLevel="0" r="268">
       <c r="A268" s="4" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="B268" s="5">
-        <v>193843</v>
+        <v>193993</v>
       </c>
       <c r="C268" s="5">
-        <v>219640</v>
+        <v>220781</v>
       </c>
     </row>
     <row outlineLevel="0" r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>2004-04</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="B269" s="5">
-        <v>198778</v>
+        <v>193843</v>
       </c>
       <c r="C269" s="5">
-        <v>217992</v>
+        <v>219640</v>
       </c>
     </row>
     <row outlineLevel="0" r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>2004-03</t>
+          <t>2004-04</t>
         </is>
       </c>
       <c r="B270" s="5">
-        <v>191451</v>
+        <v>198778</v>
       </c>
       <c r="C270" s="5">
-        <v>203953</v>
+        <v>217992</v>
       </c>
     </row>
     <row outlineLevel="0" r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>2004-02</t>
+          <t>2004-03</t>
         </is>
       </c>
       <c r="B271" s="5">
-        <v>190448</v>
+        <v>191451</v>
       </c>
       <c r="C271" s="5">
-        <v>200323</v>
+        <v>203953</v>
       </c>
     </row>
     <row outlineLevel="0" r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2004-02</t>
         </is>
       </c>
       <c r="B272" s="5">
-        <v>189429</v>
+        <v>190448</v>
       </c>
       <c r="C272" s="5">
-        <v>198628</v>
+        <v>200323</v>
       </c>
     </row>
     <row outlineLevel="0" r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>2003-12</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="B273" s="5">
-        <v>181459</v>
+        <v>189429</v>
       </c>
       <c r="C273" s="5">
-        <v>199297</v>
+        <v>198628</v>
       </c>
     </row>
     <row outlineLevel="0" r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>2003-11</t>
+          <t>2003-12</t>
         </is>
       </c>
       <c r="B274" s="5">
-        <v>182587</v>
+        <v>181459</v>
       </c>
       <c r="C274" s="5">
-        <v>184899</v>
+        <v>199297</v>
       </c>
     </row>
     <row outlineLevel="0" r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>2003-10</t>
+          <t>2003-11</t>
         </is>
       </c>
       <c r="B275" s="5">
-        <v>175428</v>
+        <v>182587</v>
       </c>
       <c r="C275" s="5">
-        <v>191554</v>
+        <v>184899</v>
       </c>
     </row>
     <row outlineLevel="0" r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>2003-09</t>
+          <t>2003-10</t>
         </is>
       </c>
       <c r="B276" s="5">
-        <v>171194</v>
+        <v>175428</v>
       </c>
       <c r="C276" s="5">
-        <v>189826</v>
+        <v>191554</v>
       </c>
     </row>
     <row outlineLevel="0" r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>2003-08</t>
+          <t>2003-09</t>
         </is>
       </c>
       <c r="B277" s="5">
-        <v>167200</v>
+        <v>171194</v>
       </c>
       <c r="C277" s="5">
-        <v>188112</v>
+        <v>189826</v>
       </c>
     </row>
     <row outlineLevel="0" r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>2003-07</t>
+          <t>2003-08</t>
         </is>
       </c>
       <c r="B278" s="5">
-        <v>174427</v>
+        <v>167200</v>
       </c>
       <c r="C278" s="5">
-        <v>199973</v>
+        <v>188112</v>
       </c>
     </row>
     <row outlineLevel="0" r="279">
       <c r="A279" s="4" t="inlineStr">
         <is>
-          <t>2003-06</t>
+          <t>2003-07</t>
         </is>
       </c>
       <c r="B279" s="5">
-        <v>168281</v>
+        <v>174427</v>
       </c>
       <c r="C279" s="5">
-        <v>190026</v>
+        <v>199973</v>
       </c>
     </row>
     <row outlineLevel="0" r="280">
       <c r="A280" s="4" t="inlineStr">
         <is>
-          <t>2003-05</t>
+          <t>2003-06</t>
         </is>
       </c>
       <c r="B280" s="5">
-        <v>153725</v>
+        <v>168281</v>
       </c>
       <c r="C280" s="5">
-        <v>178946</v>
+        <v>190026</v>
       </c>
     </row>
     <row outlineLevel="0" r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>2003-04</t>
+          <t>2003-05</t>
         </is>
       </c>
       <c r="B281" s="5">
-        <v>143237</v>
+        <v>153725</v>
       </c>
       <c r="C281" s="5">
-        <v>168756</v>
+        <v>178946</v>
       </c>
     </row>
     <row outlineLevel="0" r="282">
       <c r="A282" s="4" t="inlineStr">
         <is>
-          <t>2003-03</t>
+          <t>2003-04</t>
         </is>
       </c>
       <c r="B282" s="5">
-        <v>144267</v>
+        <v>143237</v>
       </c>
       <c r="C282" s="5">
-        <v>176955</v>
+        <v>168756</v>
       </c>
     </row>
     <row outlineLevel="0" r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>2003-02</t>
+          <t>2003-03</t>
         </is>
       </c>
       <c r="B283" s="5">
-        <v>140516</v>
+        <v>144267</v>
       </c>
       <c r="C283" s="5">
-        <v>179925</v>
+        <v>176955</v>
       </c>
     </row>
     <row outlineLevel="0" r="284">
       <c r="A284" s="4" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2003-02</t>
         </is>
       </c>
       <c r="B284" s="5">
-        <v>141391</v>
+        <v>140516</v>
       </c>
       <c r="C284" s="5">
-        <v>179528</v>
+        <v>179925</v>
       </c>
     </row>
     <row outlineLevel="0" r="285">
       <c r="A285" s="4" t="inlineStr">
         <is>
-          <t>2002-12</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="B285" s="5">
-        <v>139451</v>
+        <v>141391</v>
       </c>
       <c r="C285" s="5">
-        <v>184715</v>
+        <v>179528</v>
       </c>
     </row>
     <row outlineLevel="0" r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>2002-11</t>
+          <t>2002-12</t>
         </is>
       </c>
       <c r="B286" s="5">
-        <v>139472</v>
+        <v>139451</v>
       </c>
       <c r="C286" s="5">
-        <v>176062</v>
+        <v>184715</v>
       </c>
     </row>
     <row outlineLevel="0" r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>2002-10</t>
+          <t>2002-11</t>
         </is>
       </c>
       <c r="B287" s="5">
-        <v>138647</v>
+        <v>139472</v>
       </c>
       <c r="C287" s="5">
-        <v>181069</v>
+        <v>176062</v>
       </c>
     </row>
     <row outlineLevel="0" r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>2002-09</t>
+          <t>2002-10</t>
         </is>
       </c>
       <c r="B288" s="5">
-        <v>136107</v>
+        <v>138647</v>
       </c>
       <c r="C288" s="5">
-        <v>180997</v>
+        <v>181069</v>
       </c>
     </row>
     <row outlineLevel="0" r="289">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>2002-08</t>
+          <t>2002-09</t>
         </is>
       </c>
       <c r="B289" s="5">
-        <v>139146</v>
+        <v>136107</v>
       </c>
       <c r="C289" s="5">
-        <v>174995</v>
+        <v>180997</v>
       </c>
     </row>
     <row outlineLevel="0" r="290">
       <c r="A290" s="4" t="inlineStr">
         <is>
-          <t>2002-07</t>
+          <t>2002-08</t>
         </is>
       </c>
       <c r="B290" s="5">
-        <v>143905</v>
+        <v>139146</v>
       </c>
       <c r="C290" s="5">
-        <v>183326</v>
+        <v>174995</v>
       </c>
     </row>
     <row outlineLevel="0" r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>2002-06</t>
+          <t>2002-07</t>
         </is>
       </c>
       <c r="B291" s="5">
-        <v>153972</v>
+        <v>143905</v>
       </c>
       <c r="C291" s="5">
-        <v>178744</v>
+        <v>183326</v>
       </c>
     </row>
     <row outlineLevel="0" r="292">
       <c r="A292" s="4" t="inlineStr">
         <is>
-          <t>2002-05</t>
+          <t>2002-06</t>
         </is>
       </c>
       <c r="B292" s="5">
-        <v>157802</v>
+        <v>153972</v>
       </c>
       <c r="C292" s="5">
-        <v>173395</v>
+        <v>178744</v>
       </c>
     </row>
     <row outlineLevel="0" r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>2002-04</t>
+          <t>2002-05</t>
         </is>
       </c>
       <c r="B293" s="5">
-        <v>159072</v>
+        <v>157802</v>
       </c>
       <c r="C293" s="5">
-        <v>175730</v>
+        <v>173395</v>
       </c>
     </row>
     <row outlineLevel="0" r="294">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>2002-03</t>
+          <t>2002-04</t>
         </is>
       </c>
       <c r="B294" s="5">
-        <v>160089</v>
+        <v>159072</v>
       </c>
       <c r="C294" s="5">
-        <v>180578</v>
+        <v>175730</v>
       </c>
     </row>
     <row outlineLevel="0" r="295">
       <c r="A295" s="4" t="inlineStr">
         <is>
-          <t>2002-02</t>
+          <t>2002-03</t>
         </is>
       </c>
       <c r="B295" s="5">
-        <v>154931</v>
+        <v>160089</v>
       </c>
       <c r="C295" s="5">
-        <v>186919</v>
+        <v>180578</v>
       </c>
     </row>
     <row outlineLevel="0" r="296">
       <c r="A296" s="4" t="inlineStr">
         <is>
-          <t>2002-01</t>
+          <t>2002-02</t>
         </is>
       </c>
       <c r="B296" s="5">
-        <v>160906</v>
+        <v>154931</v>
       </c>
       <c r="C296" s="5">
-        <v>189841</v>
+        <v>186919</v>
       </c>
     </row>
     <row outlineLevel="0" r="297">
       <c r="A297" s="4" t="inlineStr">
         <is>
-          <t>2001-12</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="B297" s="5">
-        <v>160473</v>
+        <v>160906</v>
       </c>
       <c r="C297" s="5">
-        <v>197424</v>
+        <v>189841</v>
       </c>
     </row>
     <row outlineLevel="0" r="298">
       <c r="A298" s="4" t="inlineStr">
         <is>
-          <t>2001-11</t>
+          <t>2001-12</t>
         </is>
       </c>
       <c r="B298" s="5">
-        <v>159440</v>
+        <v>160473</v>
       </c>
       <c r="C298" s="5">
-        <v>188441</v>
+        <v>197424</v>
       </c>
     </row>
     <row outlineLevel="0" r="299">
       <c r="A299" s="4" t="inlineStr">
         <is>
-          <t>2001-10</t>
+          <t>2001-11</t>
         </is>
       </c>
       <c r="B299" s="5">
-        <v>152367</v>
+        <v>159440</v>
       </c>
       <c r="C299" s="5">
-        <v>187012</v>
+        <v>188441</v>
       </c>
     </row>
     <row outlineLevel="0" r="300">
       <c r="A300" s="4" t="inlineStr">
         <is>
-          <t>2001-09</t>
+          <t>2001-10</t>
         </is>
       </c>
       <c r="B300" s="5">
-        <v>157931</v>
+        <v>152367</v>
       </c>
       <c r="C300" s="5">
-        <v>211281</v>
+        <v>187012</v>
       </c>
     </row>
     <row outlineLevel="0" r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>2001-08</t>
+          <t>2001-09</t>
         </is>
       </c>
       <c r="B301" s="5">
-        <v>169316</v>
+        <v>157931</v>
       </c>
       <c r="C301" s="5">
-        <v>191219</v>
+        <v>211281</v>
       </c>
     </row>
     <row outlineLevel="0" r="302">
       <c r="A302" s="4" t="inlineStr">
         <is>
-          <t>2001-07</t>
+          <t>2001-08</t>
         </is>
       </c>
       <c r="B302" s="5">
-        <v>173680</v>
+        <v>169316</v>
       </c>
       <c r="C302" s="5">
-        <v>185100</v>
+        <v>191219</v>
       </c>
     </row>
     <row outlineLevel="0" r="303">
       <c r="A303" s="4" t="inlineStr">
         <is>
-          <t>2001-06</t>
+          <t>2001-07</t>
         </is>
       </c>
       <c r="B303" s="5">
-        <v>179585</v>
+        <v>173680</v>
       </c>
       <c r="C303" s="5">
-        <v>187602</v>
+        <v>185100</v>
       </c>
     </row>
     <row outlineLevel="0" r="304">
       <c r="A304" s="4" t="inlineStr">
         <is>
-          <t>2001-05</t>
+          <t>2001-06</t>
         </is>
       </c>
       <c r="B304" s="5">
-        <v>183041</v>
+        <v>179585</v>
       </c>
       <c r="C304" s="5">
-        <v>183493</v>
+        <v>187602</v>
       </c>
     </row>
     <row outlineLevel="0" r="305">
       <c r="A305" s="4" t="inlineStr">
         <is>
-          <t>2001-04</t>
+          <t>2001-05</t>
         </is>
       </c>
       <c r="B305" s="5">
-        <v>176096</v>
+        <v>183041</v>
       </c>
       <c r="C305" s="5">
-        <v>191145</v>
+        <v>183493</v>
       </c>
     </row>
     <row outlineLevel="0" r="306">
       <c r="A306" s="4" t="inlineStr">
         <is>
-          <t>2001-03</t>
+          <t>2001-04</t>
         </is>
       </c>
       <c r="B306" s="5">
-        <v>174797</v>
+        <v>176096</v>
       </c>
       <c r="C306" s="5">
-        <v>198581</v>
+        <v>191145</v>
       </c>
     </row>
     <row outlineLevel="0" r="307">
       <c r="A307" s="4" t="inlineStr">
         <is>
-          <t>2001-02</t>
+          <t>2001-03</t>
         </is>
       </c>
       <c r="B307" s="5">
-        <v>198887</v>
+        <v>174797</v>
       </c>
       <c r="C307" s="5">
-        <v>193266</v>
+        <v>198581</v>
       </c>
     </row>
     <row outlineLevel="0" r="308">
       <c r="A308" s="4" t="inlineStr">
         <is>
-          <t>2001-01</t>
+          <t>2001-02</t>
         </is>
       </c>
       <c r="B308" s="5">
-        <v>208687</v>
+        <v>198887</v>
       </c>
       <c r="C308" s="5">
-        <v>187225</v>
+        <v>193266</v>
       </c>
     </row>
     <row outlineLevel="0" r="309">
       <c r="A309" s="4" t="inlineStr">
         <is>
-          <t>2000-12</t>
+          <t>2001-01</t>
         </is>
       </c>
       <c r="B309" s="5">
-        <v>210385</v>
+        <v>208687</v>
       </c>
       <c r="C309" s="5">
-        <v>198179</v>
+        <v>187225</v>
       </c>
     </row>
     <row outlineLevel="0" r="310">
       <c r="A310" s="4" t="inlineStr">
         <is>
-          <t>2000-11</t>
+          <t>2000-12</t>
         </is>
       </c>
       <c r="B310" s="5">
-        <v>237913</v>
+        <v>210385</v>
       </c>
       <c r="C310" s="5">
-        <v>186459</v>
+        <v>198179</v>
       </c>
     </row>
     <row outlineLevel="0" r="311">
       <c r="A311" s="4" t="inlineStr">
         <is>
-          <t>2000-10</t>
+          <t>2000-11</t>
         </is>
       </c>
       <c r="B311" s="5">
-        <v>250965</v>
+        <v>237913</v>
       </c>
       <c r="C311" s="5">
-        <v>172738</v>
+        <v>186459</v>
       </c>
     </row>
     <row outlineLevel="0" r="312">
       <c r="A312" s="4" t="inlineStr">
         <is>
-          <t>2000-09</t>
+          <t>2000-10</t>
         </is>
       </c>
       <c r="B312" s="5">
-        <v>270208</v>
+        <v>250965</v>
       </c>
       <c r="C312" s="5">
-        <v>160964</v>
+        <v>172738</v>
       </c>
     </row>
     <row outlineLevel="0" r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>2000-08</t>
+          <t>2000-09</t>
         </is>
       </c>
       <c r="B313" s="5">
-        <v>265166</v>
+        <v>270208</v>
       </c>
       <c r="C313" s="5">
-        <v>156775</v>
+        <v>160964</v>
       </c>
     </row>
     <row outlineLevel="0" r="314">
       <c r="A314" s="4" t="inlineStr">
         <is>
-          <t>2000-07</t>
+          <t>2000-08</t>
         </is>
       </c>
       <c r="B314" s="5">
-        <v>263729</v>
+        <v>265166</v>
       </c>
       <c r="C314" s="5">
-        <v>163050</v>
+        <v>156775</v>
       </c>
     </row>
     <row outlineLevel="0" r="315">
       <c r="A315" s="4" t="inlineStr">
         <is>
-          <t>2000-06</t>
+          <t>2000-07</t>
         </is>
       </c>
       <c r="B315" s="5">
-        <v>264471</v>
+        <v>263729</v>
       </c>
       <c r="C315" s="5">
-        <v>153050</v>
+        <v>163050</v>
       </c>
     </row>
     <row outlineLevel="0" r="316">
       <c r="A316" s="4" t="inlineStr">
         <is>
-          <t>2000-05</t>
+          <t>2000-06</t>
         </is>
       </c>
       <c r="B316" s="5">
-        <v>256862</v>
+        <v>264471</v>
       </c>
       <c r="C316" s="5">
-        <v>153843</v>
+        <v>153050</v>
       </c>
     </row>
     <row outlineLevel="0" r="317">
       <c r="A317" s="4" t="inlineStr">
         <is>
-          <t>2000-04</t>
+          <t>2000-05</t>
         </is>
       </c>
       <c r="B317" s="5">
-        <v>268716</v>
+        <v>256862</v>
       </c>
       <c r="C317" s="5">
-        <v>156868</v>
+        <v>153843</v>
       </c>
     </row>
     <row outlineLevel="0" r="318">
       <c r="A318" s="4" t="inlineStr">
         <is>
-          <t>2000-03</t>
+          <t>2000-04</t>
         </is>
       </c>
       <c r="B318" s="5">
-        <v>299933</v>
+        <v>268716</v>
       </c>
       <c r="C318" s="5">
-        <v>168002</v>
+        <v>156868</v>
       </c>
     </row>
     <row outlineLevel="0" r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>2000-02</t>
+          <t>2000-03</t>
         </is>
       </c>
       <c r="B319" s="5">
-        <v>284206</v>
+        <v>299933</v>
       </c>
       <c r="C319" s="5">
-        <v>153540</v>
+        <v>168002</v>
       </c>
     </row>
     <row outlineLevel="0" r="320">
       <c r="A320" s="4" t="inlineStr">
         <is>
-          <t>2000-01</t>
+          <t>2000-02</t>
         </is>
       </c>
       <c r="B320" s="5">
-        <v>260409</v>
+        <v>284206</v>
       </c>
       <c r="C320" s="5">
-        <v>148567</v>
+        <v>153540</v>
       </c>
     </row>
     <row outlineLevel="0" r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>1999-12</t>
+          <t>2000-01</t>
         </is>
       </c>
       <c r="B321" s="5">
-        <v>241967</v>
+        <v>260409</v>
       </c>
       <c r="C321" s="5">
-        <v>146582</v>
+        <v>148567</v>
       </c>
     </row>
     <row outlineLevel="0" r="322">
       <c r="A322" s="4" t="inlineStr">
         <is>
-          <t>1999-11</t>
+          <t>1999-12</t>
         </is>
       </c>
       <c r="B322" s="5">
-        <v>218304</v>
+        <v>241967</v>
       </c>
       <c r="C322" s="5">
-        <v>131786</v>
+        <v>146582</v>
       </c>
     </row>
     <row outlineLevel="0" r="323">
       <c r="A323" s="4" t="inlineStr">
         <is>
-          <t>1999-10</t>
+          <t>1999-11</t>
         </is>
       </c>
       <c r="B323" s="5">
-        <v>194259</v>
+        <v>218304</v>
       </c>
       <c r="C323" s="5">
-        <v>123457</v>
+        <v>131786</v>
       </c>
     </row>
     <row outlineLevel="0" r="324">
       <c r="A324" s="4" t="inlineStr">
         <is>
-          <t>1999-09</t>
+          <t>1999-10</t>
         </is>
       </c>
       <c r="B324" s="5">
-        <v>189741</v>
+        <v>194259</v>
       </c>
       <c r="C324" s="5">
-        <v>121207</v>
+        <v>123457</v>
       </c>
     </row>
     <row outlineLevel="0" r="325">
       <c r="A325" s="4" t="inlineStr">
         <is>
-          <t>1999-08</t>
+          <t>1999-09</t>
         </is>
       </c>
       <c r="B325" s="5">
-        <v>187616</v>
+        <v>189741</v>
       </c>
       <c r="C325" s="5">
-        <v>117149</v>
+        <v>121207</v>
       </c>
     </row>
     <row outlineLevel="0" r="326">
       <c r="A326" s="4" t="inlineStr">
         <is>
-          <t>1999-07</t>
+          <t>1999-08</t>
         </is>
       </c>
       <c r="B326" s="5">
-        <v>189503</v>
+        <v>187616</v>
       </c>
       <c r="C326" s="5">
-        <v>115017</v>
+        <v>117149</v>
       </c>
     </row>
     <row outlineLevel="0" r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>1999-06</t>
+          <t>1999-07</t>
         </is>
       </c>
       <c r="B327" s="5">
-        <v>187695</v>
+        <v>189503</v>
       </c>
       <c r="C327" s="5">
-        <v>116982</v>
+        <v>115017</v>
       </c>
     </row>
     <row outlineLevel="0" r="328">
       <c r="A328" s="4" t="inlineStr">
         <is>
-          <t>1999-05</t>
+          <t>1999-06</t>
         </is>
       </c>
       <c r="B328" s="5">
-        <v>189950</v>
+        <v>187695</v>
       </c>
       <c r="C328" s="5">
-        <v>114271</v>
+        <v>116982</v>
       </c>
     </row>
     <row outlineLevel="0" r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>1999-04</t>
+          <t>1999-05</t>
         </is>
       </c>
       <c r="B329" s="5">
-        <v>184329</v>
+        <v>189950</v>
       </c>
       <c r="C329" s="5">
-        <v>112290</v>
+        <v>114271</v>
       </c>
     </row>
     <row outlineLevel="0" r="330">
       <c r="A330" s="4" t="inlineStr">
         <is>
-          <t>1999-03</t>
+          <t>1999-04</t>
         </is>
       </c>
       <c r="B330" s="5">
-        <v>166212</v>
+        <v>184329</v>
       </c>
       <c r="C330" s="5">
-        <v>109941</v>
+        <v>112290</v>
       </c>
     </row>
     <row outlineLevel="0" r="331">
       <c r="A331" s="4" t="inlineStr">
         <is>
-          <t>1999-02</t>
+          <t>1999-03</t>
         </is>
       </c>
       <c r="B331" s="5">
-        <v>162909</v>
+        <v>166212</v>
       </c>
       <c r="C331" s="5">
-        <v>109523</v>
+        <v>109941</v>
       </c>
     </row>
     <row outlineLevel="0" r="332">
       <c r="A332" s="4" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1999-02</t>
         </is>
       </c>
       <c r="B332" s="5">
-        <v>162322</v>
+        <v>162909</v>
       </c>
       <c r="C332" s="5">
-        <v>107200</v>
+        <v>109523</v>
       </c>
     </row>
     <row outlineLevel="0" r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>1998-12</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="B333" s="5">
-        <v>148674</v>
+        <v>162322</v>
       </c>
       <c r="C333" s="5">
-        <v>111507</v>
+        <v>107200</v>
       </c>
     </row>
     <row outlineLevel="0" r="334">
       <c r="A334" s="4" t="inlineStr">
         <is>
-          <t>1998-11</t>
+          <t>1998-12</t>
         </is>
       </c>
       <c r="B334" s="5">
-        <v>148697</v>
+        <v>148674</v>
       </c>
       <c r="C334" s="5">
-        <v>108032</v>
+        <v>111507</v>
       </c>
     </row>
     <row outlineLevel="0" r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>1998-10</t>
+          <t>1998-11</t>
         </is>
       </c>
       <c r="B335" s="5">
-        <v>138399</v>
+        <v>148697</v>
       </c>
       <c r="C335" s="5">
-        <v>108179</v>
+        <v>108032</v>
       </c>
     </row>
     <row outlineLevel="0" r="336">
       <c r="A336" s="4" t="inlineStr">
         <is>
-          <t>1998-09</t>
+          <t>1998-10</t>
         </is>
       </c>
       <c r="B336" s="5">
-        <v>144541</v>
+        <v>138399</v>
       </c>
       <c r="C336" s="5">
-        <v>103879</v>
+        <v>108179</v>
       </c>
     </row>
     <row outlineLevel="0" r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>1998-08</t>
+          <t>1998-09</t>
         </is>
       </c>
       <c r="B337" s="5">
-        <v>155879</v>
+        <v>144541</v>
       </c>
       <c r="C337" s="5">
-        <v>100093</v>
+        <v>103879</v>
       </c>
     </row>
     <row outlineLevel="0" r="338">
       <c r="A338" s="4" t="inlineStr">
         <is>
-          <t>1998-07</t>
+          <t>1998-08</t>
         </is>
       </c>
       <c r="B338" s="5">
-        <v>160980</v>
+        <v>155879</v>
       </c>
       <c r="C338" s="5">
-        <v>92687</v>
+        <v>100093</v>
       </c>
     </row>
     <row outlineLevel="0" r="339">
       <c r="A339" s="4" t="inlineStr">
         <is>
-          <t>1998-06</t>
+          <t>1998-07</t>
         </is>
       </c>
       <c r="B339" s="5">
-        <v>154357</v>
+        <v>160980</v>
       </c>
       <c r="C339" s="5">
-        <v>87891</v>
+        <v>92687</v>
       </c>
     </row>
     <row outlineLevel="0" r="340">
       <c r="A340" s="4" t="inlineStr">
         <is>
-          <t>1998-05</t>
+          <t>1998-06</t>
         </is>
       </c>
       <c r="B340" s="5">
-        <v>150293</v>
+        <v>154357</v>
       </c>
       <c r="C340" s="5">
-        <v>80174</v>
+        <v>87891</v>
       </c>
     </row>
     <row outlineLevel="0" r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>1998-04</t>
+          <t>1998-05</t>
         </is>
       </c>
       <c r="B341" s="5">
-        <v>146589</v>
+        <v>150293</v>
       </c>
       <c r="C341" s="5">
-        <v>85771</v>
+        <v>80174</v>
       </c>
     </row>
     <row outlineLevel="0" r="342">
       <c r="A342" s="4" t="inlineStr">
         <is>
-          <t>1998-03</t>
+          <t>1998-04</t>
         </is>
       </c>
       <c r="B342" s="5">
-        <v>146536</v>
+        <v>146589</v>
       </c>
       <c r="C342" s="5">
-        <v>85580</v>
+        <v>85771</v>
       </c>
     </row>
     <row outlineLevel="0" r="343">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>1998-02</t>
+          <t>1998-03</t>
         </is>
       </c>
       <c r="B343" s="5">
-        <v>141328</v>
+        <v>146536</v>
       </c>
       <c r="C343" s="5">
-        <v>81932</v>
+        <v>85580</v>
       </c>
     </row>
     <row outlineLevel="0" r="344">
       <c r="A344" s="4" t="inlineStr">
         <is>
-          <t>1998-01</t>
+          <t>1998-02</t>
         </is>
       </c>
       <c r="B344" s="5">
-        <v>132912</v>
+        <v>141328</v>
       </c>
       <c r="C344" s="5">
-        <v>83362</v>
+        <v>81932</v>
       </c>
     </row>
     <row outlineLevel="0" r="345">
       <c r="A345" s="4" t="inlineStr">
         <is>
-          <t>1997-12</t>
+          <t>1998-01</t>
         </is>
       </c>
       <c r="B345" s="5">
-        <v>131560</v>
+        <v>132912</v>
       </c>
       <c r="C345" s="5">
-        <v>88590</v>
+        <v>83362</v>
       </c>
     </row>
     <row outlineLevel="0" r="346">
       <c r="A346" s="4" t="inlineStr">
         <is>
-          <t>1997-11</t>
+          <t>1997-12</t>
         </is>
       </c>
       <c r="B346" s="5">
-        <v>132741</v>
+        <v>131560</v>
       </c>
       <c r="C346" s="5">
-        <v>77259</v>
+        <v>88590</v>
       </c>
     </row>
     <row outlineLevel="0" r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>1997-10</t>
+          <t>1997-11</t>
         </is>
       </c>
       <c r="B347" s="5">
-        <v>134491</v>
+        <v>132741</v>
       </c>
       <c r="C347" s="5">
-        <v>80287</v>
+        <v>77259</v>
       </c>
     </row>
     <row outlineLevel="0" r="348">
       <c r="A348" s="4" t="inlineStr">
         <is>
-          <t>1997-09</t>
+          <t>1997-10</t>
         </is>
       </c>
       <c r="B348" s="5">
-        <v>131962</v>
+        <v>134491</v>
       </c>
       <c r="C348" s="5">
-        <v>73087</v>
+        <v>80287</v>
       </c>
     </row>
     <row outlineLevel="0" r="349">
       <c r="A349" s="4" t="inlineStr">
         <is>
-          <t>1997-08</t>
+          <t>1997-09</t>
         </is>
       </c>
       <c r="B349" s="5">
-        <v>124404</v>
+        <v>131962</v>
       </c>
       <c r="C349" s="5">
-        <v>71211</v>
+        <v>73087</v>
       </c>
     </row>
     <row outlineLevel="0" r="350">
       <c r="A350" s="4" t="inlineStr">
         <is>
-          <t>1997-07</t>
+          <t>1997-08</t>
         </is>
       </c>
       <c r="B350" s="5">
-        <v>121090</v>
+        <v>124404</v>
       </c>
       <c r="C350" s="5">
-        <v>73714</v>
+        <v>71211</v>
       </c>
     </row>
     <row outlineLevel="0" r="351">
       <c r="A351" s="4" t="inlineStr">
         <is>
-          <t>1997-06</t>
+          <t>1997-07</t>
         </is>
       </c>
       <c r="B351" s="5">
-        <v>118843</v>
+        <v>121090</v>
       </c>
       <c r="C351" s="5">
-        <v>72422</v>
+        <v>73714</v>
       </c>
     </row>
     <row outlineLevel="0" r="352">
       <c r="A352" s="4" t="inlineStr">
         <is>
-          <t>1997-05</t>
+          <t>1997-06</t>
         </is>
       </c>
       <c r="B352" s="5">
-        <v>111097</v>
+        <v>118843</v>
       </c>
       <c r="C352" s="5">
-        <v>66879</v>
+        <v>72422</v>
       </c>
     </row>
     <row outlineLevel="0" r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>1997-04</t>
+          <t>1997-05</t>
         </is>
       </c>
       <c r="B353" s="5">
-        <v>102842</v>
+        <v>111097</v>
       </c>
       <c r="C353" s="5">
-        <v>64825</v>
+        <v>66879</v>
       </c>
     </row>
     <row outlineLevel="0" r="354">
       <c r="A354" s="4" t="inlineStr">
         <is>
-          <t>1997-03</t>
+          <t>1997-04</t>
         </is>
       </c>
       <c r="B354" s="5">
-        <v>104835</v>
+        <v>102842</v>
       </c>
       <c r="C354" s="5">
-        <v>69553</v>
+        <v>64825</v>
       </c>
     </row>
     <row outlineLevel="0" r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>1997-02</t>
+          <t>1997-03</t>
         </is>
       </c>
       <c r="B355" s="5">
-        <v>103886</v>
+        <v>104835</v>
       </c>
       <c r="C355" s="5">
-        <v>67058</v>
+        <v>69553</v>
       </c>
     </row>
     <row outlineLevel="0" r="356">
       <c r="A356" s="4" t="inlineStr">
         <is>
+          <t>1997-02</t>
+        </is>
+      </c>
+      <c r="B356" s="5">
+        <v>103886</v>
+      </c>
+      <c r="C356" s="5">
+        <v>67058</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="357">
+      <c r="A357" s="4" t="inlineStr">
+        <is>
           <t>1997-01</t>
         </is>
       </c>
-      <c r="B356" s="5">
+      <c r="B357" s="5">
         <v>103337</v>
       </c>
-      <c r="C356" s="5">
+      <c r="C357" s="5">
         <v>68856</v>
       </c>
     </row>

--- a/data/finra-margin-statistics.xlsx
+++ b/data/finra-margin-statistics.xlsx
@@ -467,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D357"/>
+  <dimension ref="A1:D358"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" min="1" max="1" width="14.0625"/>
@@ -501,5225 +501,5241 @@
     <row outlineLevel="0" r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B2" s="5">
-        <v>1453832</v>
+        <v>1480054</v>
       </c>
       <c r="C2" s="5">
-        <v>207641</v>
+        <v>215328</v>
       </c>
       <c r="D2" s="5">
-        <v>217499</v>
+        <v>218581</v>
       </c>
     </row>
     <row outlineLevel="0" r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B3" s="5">
-        <v>1417225</v>
+        <v>1453832</v>
       </c>
       <c r="C3" s="5">
-        <v>205132</v>
+        <v>207641</v>
       </c>
       <c r="D3" s="5">
-        <v>217305</v>
+        <v>217499</v>
       </c>
     </row>
     <row outlineLevel="0" r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B4" s="5">
-        <v>1502072</v>
+        <v>1417225</v>
       </c>
       <c r="C4" s="5">
-        <v>217441</v>
+        <v>205132</v>
       </c>
       <c r="D4" s="5">
-        <v>223412</v>
+        <v>217305</v>
       </c>
     </row>
     <row outlineLevel="0" r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B5" s="5">
-        <v>1415557</v>
+        <v>1502072</v>
       </c>
       <c r="C5" s="5">
-        <v>206600</v>
+        <v>217441</v>
       </c>
       <c r="D5" s="5">
-        <v>217256</v>
+        <v>223412</v>
       </c>
     </row>
     <row outlineLevel="0" r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <v>1304281</v>
+        <v>1415557</v>
       </c>
       <c r="C6" s="5">
-        <v>217836</v>
+        <v>206600</v>
       </c>
       <c r="D6" s="5">
-        <v>215445</v>
+        <v>217256</v>
       </c>
     </row>
     <row outlineLevel="0" r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B7" s="5">
-        <v>1220922</v>
+        <v>1304281</v>
       </c>
       <c r="C7" s="5">
-        <v>221860</v>
+        <v>217836</v>
       </c>
       <c r="D7" s="5">
-        <v>205600</v>
+        <v>215445</v>
       </c>
     </row>
     <row outlineLevel="0" r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B8" s="5">
-        <v>1253192</v>
+        <v>1220922</v>
       </c>
       <c r="C8" s="5">
-        <v>205060</v>
+        <v>221860</v>
       </c>
       <c r="D8" s="5">
-        <v>200047</v>
+        <v>205600</v>
       </c>
     </row>
     <row outlineLevel="0" r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B9" s="5">
-        <v>1279042</v>
+        <v>1253192</v>
       </c>
       <c r="C9" s="5">
-        <v>203700</v>
+        <v>205060</v>
       </c>
       <c r="D9" s="5">
-        <v>196911</v>
+        <v>200047</v>
       </c>
     </row>
     <row outlineLevel="0" r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B10" s="5">
-        <v>1225597</v>
+        <v>1279042</v>
       </c>
       <c r="C10" s="5">
-        <v>211720</v>
+        <v>203700</v>
       </c>
       <c r="D10" s="5">
-        <v>199762</v>
+        <v>196911</v>
       </c>
     </row>
     <row outlineLevel="0" r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="B11" s="5">
-        <v>1214321</v>
+        <v>1225597</v>
       </c>
       <c r="C11" s="5">
-        <v>202131</v>
+        <v>211720</v>
       </c>
       <c r="D11" s="5">
-        <v>194418</v>
+        <v>199762</v>
       </c>
     </row>
     <row outlineLevel="0" r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B12" s="5">
-        <v>1183654</v>
+        <v>1214321</v>
       </c>
       <c r="C12" s="5">
-        <v>197923</v>
+        <v>202131</v>
       </c>
       <c r="D12" s="5">
-        <v>195376</v>
+        <v>194418</v>
       </c>
     </row>
     <row outlineLevel="0" r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B13" s="5">
-        <v>1126494</v>
+        <v>1183654</v>
       </c>
       <c r="C13" s="5">
-        <v>204106</v>
+        <v>197923</v>
       </c>
       <c r="D13" s="5">
-        <v>194884</v>
+        <v>195376</v>
       </c>
     </row>
     <row outlineLevel="0" r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B14" s="5">
-        <v>1059723</v>
+        <v>1126494</v>
       </c>
       <c r="C14" s="5">
-        <v>188221</v>
+        <v>204106</v>
       </c>
       <c r="D14" s="5">
-        <v>181563</v>
+        <v>194884</v>
       </c>
     </row>
     <row outlineLevel="0" r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B15" s="5">
-        <v>1022548</v>
+        <v>1059723</v>
       </c>
       <c r="C15" s="5">
-        <v>194712</v>
+        <v>188221</v>
       </c>
       <c r="D15" s="5">
-        <v>186672</v>
+        <v>181563</v>
       </c>
     </row>
     <row outlineLevel="0" r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B16" s="5">
-        <v>1007961</v>
+        <v>1022548</v>
       </c>
       <c r="C16" s="5">
-        <v>200573</v>
+        <v>194712</v>
       </c>
       <c r="D16" s="5">
-        <v>185584</v>
+        <v>186672</v>
       </c>
     </row>
     <row outlineLevel="0" r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B17" s="5">
-        <v>920960</v>
+        <v>1007961</v>
       </c>
       <c r="C17" s="5">
-        <v>187685</v>
+        <v>200573</v>
       </c>
       <c r="D17" s="5">
-        <v>176698</v>
+        <v>185584</v>
       </c>
     </row>
     <row outlineLevel="0" r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B18" s="5">
-        <v>850558</v>
+        <v>920960</v>
       </c>
       <c r="C18" s="5">
-        <v>187958</v>
+        <v>187685</v>
       </c>
       <c r="D18" s="5">
-        <v>175824</v>
+        <v>176698</v>
       </c>
     </row>
     <row outlineLevel="0" r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B19" s="5">
-        <v>880316</v>
+        <v>850558</v>
       </c>
       <c r="C19" s="5">
-        <v>189855</v>
+        <v>187958</v>
       </c>
       <c r="D19" s="5">
-        <v>176161</v>
+        <v>175824</v>
       </c>
     </row>
     <row outlineLevel="0" r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B20" s="5">
-        <v>918144</v>
+        <v>880316</v>
       </c>
       <c r="C20" s="5">
-        <v>183278</v>
+        <v>189855</v>
       </c>
       <c r="D20" s="5">
-        <v>176051</v>
+        <v>176161</v>
       </c>
     </row>
     <row outlineLevel="0" r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B21" s="5">
-        <v>937253</v>
+        <v>918144</v>
       </c>
       <c r="C21" s="5">
-        <v>178301</v>
+        <v>183278</v>
       </c>
       <c r="D21" s="5">
-        <v>166346</v>
+        <v>176051</v>
       </c>
     </row>
     <row outlineLevel="0" r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B22" s="5">
-        <v>899168</v>
+        <v>937253</v>
       </c>
       <c r="C22" s="5">
-        <v>181280</v>
+        <v>178301</v>
       </c>
       <c r="D22" s="5">
-        <v>175795</v>
+        <v>166346</v>
       </c>
     </row>
     <row outlineLevel="0" r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B23" s="5">
-        <v>890852</v>
+        <v>899168</v>
       </c>
       <c r="C23" s="5">
-        <v>170052</v>
+        <v>181280</v>
       </c>
       <c r="D23" s="5">
-        <v>167223</v>
+        <v>175795</v>
       </c>
     </row>
     <row outlineLevel="0" r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B24" s="5">
-        <v>815369</v>
+        <v>890852</v>
       </c>
       <c r="C24" s="5">
-        <v>173621</v>
+        <v>170052</v>
       </c>
       <c r="D24" s="5">
-        <v>164813</v>
+        <v>167223</v>
       </c>
     </row>
     <row outlineLevel="0" r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B25" s="5">
-        <v>813211</v>
+        <v>815369</v>
       </c>
       <c r="C25" s="5">
-        <v>167901</v>
+        <v>173621</v>
       </c>
       <c r="D25" s="5">
-        <v>158358</v>
+        <v>164813</v>
       </c>
     </row>
     <row outlineLevel="0" r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B26" s="5">
-        <v>797162</v>
+        <v>813211</v>
       </c>
       <c r="C26" s="5">
-        <v>148702</v>
+        <v>167901</v>
       </c>
       <c r="D26" s="5">
-        <v>152107</v>
+        <v>158358</v>
       </c>
     </row>
     <row outlineLevel="0" r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B27" s="5">
-        <v>810835</v>
+        <v>797162</v>
       </c>
       <c r="C27" s="5">
-        <v>154951</v>
+        <v>148702</v>
       </c>
       <c r="D27" s="5">
-        <v>150738</v>
+        <v>152107</v>
       </c>
     </row>
     <row outlineLevel="0" r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B28" s="5">
-        <v>809322</v>
+        <v>810835</v>
       </c>
       <c r="C28" s="5">
-        <v>157240</v>
+        <v>154951</v>
       </c>
       <c r="D28" s="5">
-        <v>149714</v>
+        <v>150738</v>
       </c>
     </row>
     <row outlineLevel="0" r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B29" s="5">
-        <v>809431</v>
+        <v>809322</v>
       </c>
       <c r="C29" s="5">
-        <v>155256</v>
+        <v>157240</v>
       </c>
       <c r="D29" s="5">
-        <v>145072</v>
+        <v>149714</v>
       </c>
     </row>
     <row outlineLevel="0" r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B30" s="5">
-        <v>775464</v>
+        <v>809431</v>
       </c>
       <c r="C30" s="5">
-        <v>161749</v>
+        <v>155256</v>
       </c>
       <c r="D30" s="5">
-        <v>149855</v>
+        <v>145072</v>
       </c>
     </row>
     <row outlineLevel="0" r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B31" s="5">
-        <v>784136</v>
+        <v>775464</v>
       </c>
       <c r="C31" s="5">
-        <v>166990</v>
+        <v>161749</v>
       </c>
       <c r="D31" s="5">
-        <v>151339</v>
+        <v>149855</v>
       </c>
     </row>
     <row outlineLevel="0" r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B32" s="5">
-        <v>742963</v>
+        <v>784136</v>
       </c>
       <c r="C32" s="5">
-        <v>166144</v>
+        <v>166990</v>
       </c>
       <c r="D32" s="5">
-        <v>150620</v>
+        <v>151339</v>
       </c>
     </row>
     <row outlineLevel="0" r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B33" s="5">
-        <v>701975</v>
+        <v>742963</v>
       </c>
       <c r="C33" s="5">
-        <v>165025</v>
+        <v>166144</v>
       </c>
       <c r="D33" s="5">
-        <v>144941</v>
+        <v>150620</v>
       </c>
     </row>
     <row outlineLevel="0" r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B34" s="5">
-        <v>700774</v>
+        <v>701975</v>
       </c>
       <c r="C34" s="5">
-        <v>161639</v>
+        <v>165025</v>
       </c>
       <c r="D34" s="5">
-        <v>147019</v>
+        <v>144941</v>
       </c>
     </row>
     <row outlineLevel="0" r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B35" s="5">
-        <v>660887</v>
+        <v>700774</v>
       </c>
       <c r="C35" s="5">
-        <v>171207</v>
+        <v>161639</v>
       </c>
       <c r="D35" s="5">
-        <v>146319</v>
+        <v>147019</v>
       </c>
     </row>
     <row outlineLevel="0" r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="B36" s="5">
-        <v>635276</v>
+        <v>660887</v>
       </c>
       <c r="C36" s="5">
-        <v>162865</v>
+        <v>171207</v>
       </c>
       <c r="D36" s="5">
-        <v>142117</v>
+        <v>146319</v>
       </c>
     </row>
     <row outlineLevel="0" r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B37" s="5">
-        <v>680846</v>
+        <v>635276</v>
       </c>
       <c r="C37" s="5">
-        <v>153918</v>
+        <v>162865</v>
       </c>
       <c r="D37" s="5">
-        <v>141751</v>
+        <v>142117</v>
       </c>
     </row>
     <row outlineLevel="0" r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2023-08</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="B38" s="5">
-        <v>689185</v>
+        <v>680846</v>
       </c>
       <c r="C38" s="5">
-        <v>177711</v>
+        <v>153918</v>
       </c>
       <c r="D38" s="5">
-        <v>145989</v>
+        <v>141751</v>
       </c>
     </row>
     <row outlineLevel="0" r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="B39" s="5">
-        <v>709834</v>
+        <v>689185</v>
       </c>
       <c r="C39" s="5">
-        <v>174804</v>
+        <v>177711</v>
       </c>
       <c r="D39" s="5">
-        <v>147921</v>
+        <v>145989</v>
       </c>
     </row>
     <row outlineLevel="0" r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="B40" s="5">
-        <v>681228</v>
+        <v>709834</v>
       </c>
       <c r="C40" s="5">
-        <v>181569</v>
+        <v>174804</v>
       </c>
       <c r="D40" s="5">
-        <v>145173</v>
+        <v>147921</v>
       </c>
     </row>
     <row outlineLevel="0" r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="B41" s="5">
-        <v>644170</v>
+        <v>681228</v>
       </c>
       <c r="C41" s="5">
-        <v>178576</v>
+        <v>181569</v>
       </c>
       <c r="D41" s="5">
-        <v>147377</v>
+        <v>145173</v>
       </c>
     </row>
     <row outlineLevel="0" r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2023-04</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="B42" s="5">
-        <v>631949</v>
+        <v>644170</v>
       </c>
       <c r="C42" s="5">
-        <v>175460</v>
+        <v>178576</v>
       </c>
       <c r="D42" s="5">
-        <v>145594</v>
+        <v>147377</v>
       </c>
     </row>
     <row outlineLevel="0" r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2023-04</t>
         </is>
       </c>
       <c r="B43" s="5">
-        <v>645429</v>
+        <v>631949</v>
       </c>
       <c r="C43" s="5">
-        <v>191618</v>
+        <v>175460</v>
       </c>
       <c r="D43" s="5">
-        <v>152014</v>
+        <v>145594</v>
       </c>
     </row>
     <row outlineLevel="0" r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2023-02</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="B44" s="5">
-        <v>624379</v>
+        <v>645429</v>
       </c>
       <c r="C44" s="5">
-        <v>198644</v>
+        <v>191618</v>
       </c>
       <c r="D44" s="5">
-        <v>159103</v>
+        <v>152014</v>
       </c>
     </row>
     <row outlineLevel="0" r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>2023-02</t>
         </is>
       </c>
       <c r="B45" s="5">
-        <v>641228</v>
+        <v>624379</v>
       </c>
       <c r="C45" s="5">
-        <v>208720</v>
+        <v>198644</v>
       </c>
       <c r="D45" s="5">
-        <v>161224</v>
+        <v>159103</v>
       </c>
     </row>
     <row outlineLevel="0" r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="B46" s="5">
-        <v>606659</v>
+        <v>641228</v>
       </c>
       <c r="C46" s="5">
-        <v>205902</v>
+        <v>208720</v>
       </c>
       <c r="D46" s="5">
-        <v>164065</v>
+        <v>161224</v>
       </c>
     </row>
     <row outlineLevel="0" r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2022-11</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="B47" s="5">
-        <v>643783</v>
+        <v>606659</v>
       </c>
       <c r="C47" s="5">
-        <v>205158</v>
+        <v>205902</v>
       </c>
       <c r="D47" s="5">
-        <v>165434</v>
+        <v>164065</v>
       </c>
     </row>
     <row outlineLevel="0" r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2022-11</t>
         </is>
       </c>
       <c r="B48" s="5">
-        <v>649618</v>
+        <v>643783</v>
       </c>
       <c r="C48" s="5">
-        <v>216057</v>
+        <v>205158</v>
       </c>
       <c r="D48" s="5">
-        <v>172976</v>
+        <v>165434</v>
       </c>
     </row>
     <row outlineLevel="0" r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="B49" s="5">
-        <v>664009</v>
+        <v>649618</v>
       </c>
       <c r="C49" s="5">
-        <v>223400</v>
+        <v>216057</v>
       </c>
       <c r="D49" s="5">
-        <v>173050</v>
+        <v>172976</v>
       </c>
     </row>
     <row outlineLevel="0" r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="B50" s="5">
-        <v>687787</v>
+        <v>664009</v>
       </c>
       <c r="C50" s="5">
-        <v>226182</v>
+        <v>223400</v>
       </c>
       <c r="D50" s="5">
-        <v>175974</v>
+        <v>173050</v>
       </c>
     </row>
     <row outlineLevel="0" r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2022-07</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="B51" s="5">
-        <v>696781</v>
+        <v>687787</v>
       </c>
       <c r="C51" s="5">
-        <v>232147</v>
+        <v>226182</v>
       </c>
       <c r="D51" s="5">
-        <v>177054</v>
+        <v>175974</v>
       </c>
     </row>
     <row outlineLevel="0" r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="B52" s="5">
-        <v>683445</v>
+        <v>696781</v>
       </c>
       <c r="C52" s="5">
-        <v>249399</v>
+        <v>232147</v>
       </c>
       <c r="D52" s="5">
-        <v>186931</v>
+        <v>177054</v>
       </c>
     </row>
     <row outlineLevel="0" r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2022-05</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="B53" s="5">
-        <v>752944</v>
+        <v>683445</v>
       </c>
       <c r="C53" s="5">
-        <v>244857</v>
+        <v>249399</v>
       </c>
       <c r="D53" s="5">
-        <v>184151</v>
+        <v>186931</v>
       </c>
     </row>
     <row outlineLevel="0" r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2022-04</t>
+          <t>2022-05</t>
         </is>
       </c>
       <c r="B54" s="5">
-        <v>772940</v>
+        <v>752944</v>
       </c>
       <c r="C54" s="5">
-        <v>242724</v>
+        <v>244857</v>
       </c>
       <c r="D54" s="5">
-        <v>188652</v>
+        <v>184151</v>
       </c>
     </row>
     <row outlineLevel="0" r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2022-04</t>
         </is>
       </c>
       <c r="B55" s="5">
-        <v>799660</v>
+        <v>772940</v>
       </c>
       <c r="C55" s="5">
-        <v>256076</v>
+        <v>242724</v>
       </c>
       <c r="D55" s="5">
-        <v>196008</v>
+        <v>188652</v>
       </c>
     </row>
     <row outlineLevel="0" r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2022-02</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="B56" s="5">
-        <v>835255</v>
+        <v>799660</v>
       </c>
       <c r="C56" s="5">
-        <v>250686</v>
+        <v>256076</v>
       </c>
       <c r="D56" s="5">
-        <v>195269</v>
+        <v>196008</v>
       </c>
     </row>
     <row outlineLevel="0" r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2022-01</t>
+          <t>2022-02</t>
         </is>
       </c>
       <c r="B57" s="5">
-        <v>829637</v>
+        <v>835255</v>
       </c>
       <c r="C57" s="5">
-        <v>247752</v>
+        <v>250686</v>
       </c>
       <c r="D57" s="5">
-        <v>194545</v>
+        <v>195269</v>
       </c>
     </row>
     <row outlineLevel="0" r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2021-12</t>
+          <t>2022-01</t>
         </is>
       </c>
       <c r="B58" s="5">
-        <v>910021</v>
+        <v>829637</v>
       </c>
       <c r="C58" s="5">
-        <v>250435</v>
+        <v>247752</v>
       </c>
       <c r="D58" s="5">
-        <v>215116</v>
+        <v>194545</v>
       </c>
     </row>
     <row outlineLevel="0" r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2021-11</t>
+          <t>2021-12</t>
         </is>
       </c>
       <c r="B59" s="5">
-        <v>918598</v>
+        <v>910021</v>
       </c>
       <c r="C59" s="5">
-        <v>235638</v>
+        <v>250435</v>
       </c>
       <c r="D59" s="5">
-        <v>211623</v>
+        <v>215116</v>
       </c>
     </row>
     <row outlineLevel="0" r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2021-10</t>
+          <t>2021-11</t>
         </is>
       </c>
       <c r="B60" s="5">
-        <v>935862</v>
+        <v>918598</v>
       </c>
       <c r="C60" s="5">
-        <v>226159</v>
+        <v>235638</v>
       </c>
       <c r="D60" s="5">
-        <v>200548</v>
+        <v>211623</v>
       </c>
     </row>
     <row outlineLevel="0" r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2021-09</t>
+          <t>2021-10</t>
         </is>
       </c>
       <c r="B61" s="5">
-        <v>903117</v>
+        <v>935862</v>
       </c>
       <c r="C61" s="5">
-        <v>229279</v>
+        <v>226159</v>
       </c>
       <c r="D61" s="5">
-        <v>205564</v>
+        <v>200548</v>
       </c>
     </row>
     <row outlineLevel="0" r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2021-09</t>
         </is>
       </c>
       <c r="B62" s="5">
-        <v>911545</v>
+        <v>903117</v>
       </c>
       <c r="C62" s="5">
-        <v>219365</v>
+        <v>229279</v>
       </c>
       <c r="D62" s="5">
-        <v>198913</v>
+        <v>205564</v>
       </c>
     </row>
     <row outlineLevel="0" r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2021-07</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="B63" s="5">
-        <v>844324</v>
+        <v>911545</v>
       </c>
       <c r="C63" s="5">
-        <v>215463</v>
+        <v>219365</v>
       </c>
       <c r="D63" s="5">
-        <v>195762</v>
+        <v>198913</v>
       </c>
     </row>
     <row outlineLevel="0" r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2021-06</t>
+          <t>2021-07</t>
         </is>
       </c>
       <c r="B64" s="5">
-        <v>882103</v>
+        <v>844324</v>
       </c>
       <c r="C64" s="5">
-        <v>221862</v>
+        <v>215463</v>
       </c>
       <c r="D64" s="5">
-        <v>239290</v>
+        <v>195762</v>
       </c>
     </row>
     <row outlineLevel="0" r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2021-05</t>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="B65" s="5">
-        <v>861626</v>
+        <v>882103</v>
       </c>
       <c r="C65" s="5">
-        <v>213356</v>
+        <v>221862</v>
       </c>
       <c r="D65" s="5">
-        <v>234992</v>
+        <v>239290</v>
       </c>
     </row>
     <row outlineLevel="0" r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2021-04</t>
+          <t>2021-05</t>
         </is>
       </c>
       <c r="B66" s="5">
-        <v>847186</v>
+        <v>861626</v>
       </c>
       <c r="C66" s="5">
-        <v>218132</v>
+        <v>213356</v>
       </c>
       <c r="D66" s="5">
-        <v>233145</v>
+        <v>234992</v>
       </c>
     </row>
     <row outlineLevel="0" r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2021-03</t>
+          <t>2021-04</t>
         </is>
       </c>
       <c r="B67" s="5">
-        <v>822551</v>
+        <v>847186</v>
       </c>
       <c r="C67" s="5">
-        <v>219522</v>
+        <v>218132</v>
       </c>
       <c r="D67" s="5">
-        <v>237154</v>
+        <v>233145</v>
       </c>
     </row>
     <row outlineLevel="0" r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2021-02</t>
+          <t>2021-03</t>
         </is>
       </c>
       <c r="B68" s="5">
-        <v>813680</v>
+        <v>822551</v>
       </c>
       <c r="C68" s="5">
-        <v>220840</v>
+        <v>219522</v>
       </c>
       <c r="D68" s="5">
-        <v>240481</v>
+        <v>237154</v>
       </c>
     </row>
     <row outlineLevel="0" r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2021-01</t>
+          <t>2021-02</t>
         </is>
       </c>
       <c r="B69" s="5">
-        <v>798605</v>
+        <v>813680</v>
       </c>
       <c r="C69" s="5">
-        <v>224133</v>
+        <v>220840</v>
       </c>
       <c r="D69" s="5">
-        <v>241220</v>
+        <v>240481</v>
       </c>
     </row>
     <row outlineLevel="0" r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2020-12</t>
+          <t>2021-01</t>
         </is>
       </c>
       <c r="B70" s="5">
-        <v>778037</v>
+        <v>798605</v>
       </c>
       <c r="C70" s="5">
-        <v>224987</v>
+        <v>224133</v>
       </c>
       <c r="D70" s="5">
-        <v>227127</v>
+        <v>241220</v>
       </c>
     </row>
     <row outlineLevel="0" r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2020-11</t>
+          <t>2020-12</t>
         </is>
       </c>
       <c r="B71" s="5">
-        <v>722118</v>
+        <v>778037</v>
       </c>
       <c r="C71" s="5">
-        <v>200723</v>
+        <v>224987</v>
       </c>
       <c r="D71" s="5">
-        <v>221567</v>
+        <v>227127</v>
       </c>
     </row>
     <row outlineLevel="0" r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2020-10</t>
+          <t>2020-11</t>
         </is>
       </c>
       <c r="B72" s="5">
-        <v>659313</v>
+        <v>722118</v>
       </c>
       <c r="C72" s="5">
-        <v>193293</v>
+        <v>200723</v>
       </c>
       <c r="D72" s="5">
-        <v>217739</v>
+        <v>221567</v>
       </c>
     </row>
     <row outlineLevel="0" r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2020-09</t>
+          <t>2020-10</t>
         </is>
       </c>
       <c r="B73" s="5">
-        <v>654324</v>
+        <v>659313</v>
       </c>
       <c r="C73" s="5">
-        <v>189462</v>
+        <v>193293</v>
       </c>
       <c r="D73" s="5">
-        <v>211547</v>
+        <v>217739</v>
       </c>
     </row>
     <row outlineLevel="0" r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2020-08</t>
+          <t>2020-09</t>
         </is>
       </c>
       <c r="B74" s="5">
-        <v>645547</v>
+        <v>654324</v>
       </c>
       <c r="C74" s="5">
-        <v>185113</v>
+        <v>189462</v>
       </c>
       <c r="D74" s="5">
-        <v>215042</v>
+        <v>211547</v>
       </c>
     </row>
     <row outlineLevel="0" r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2020-07</t>
+          <t>2020-08</t>
         </is>
       </c>
       <c r="B75" s="5">
-        <v>613830</v>
+        <v>645547</v>
       </c>
       <c r="C75" s="5">
-        <v>181420</v>
+        <v>185113</v>
       </c>
       <c r="D75" s="5">
-        <v>223768</v>
+        <v>215042</v>
       </c>
     </row>
     <row outlineLevel="0" r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2020-06</t>
+          <t>2020-07</t>
         </is>
       </c>
       <c r="B76" s="5">
-        <v>584676</v>
+        <v>613830</v>
       </c>
       <c r="C76" s="5">
-        <v>185497</v>
+        <v>181420</v>
       </c>
       <c r="D76" s="5">
-        <v>229078</v>
+        <v>223768</v>
       </c>
     </row>
     <row outlineLevel="0" r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2020-05</t>
+          <t>2020-06</t>
         </is>
       </c>
       <c r="B77" s="5">
-        <v>552543</v>
+        <v>584676</v>
       </c>
       <c r="C77" s="5">
-        <v>175794</v>
+        <v>185497</v>
       </c>
       <c r="D77" s="5">
-        <v>210935</v>
+        <v>229078</v>
       </c>
     </row>
     <row outlineLevel="0" r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2020-04</t>
+          <t>2020-05</t>
         </is>
       </c>
       <c r="B78" s="5">
-        <v>524696</v>
+        <v>552543</v>
       </c>
       <c r="C78" s="5">
-        <v>180942</v>
+        <v>175794</v>
       </c>
       <c r="D78" s="5">
-        <v>217187</v>
+        <v>210935</v>
       </c>
     </row>
     <row outlineLevel="0" r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2020-03</t>
+          <t>2020-04</t>
         </is>
       </c>
       <c r="B79" s="5">
-        <v>479291</v>
+        <v>524696</v>
       </c>
       <c r="C79" s="5">
-        <v>191046</v>
+        <v>180942</v>
       </c>
       <c r="D79" s="5">
-        <v>226202</v>
+        <v>217187</v>
       </c>
     </row>
     <row outlineLevel="0" r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2020-02</t>
+          <t>2020-03</t>
         </is>
       </c>
       <c r="B80" s="5">
-        <v>545127</v>
+        <v>479291</v>
       </c>
       <c r="C80" s="5">
-        <v>163001</v>
+        <v>191046</v>
       </c>
       <c r="D80" s="5">
-        <v>197716</v>
+        <v>226202</v>
       </c>
     </row>
     <row outlineLevel="0" r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2020-01</t>
+          <t>2020-02</t>
         </is>
       </c>
       <c r="B81" s="5">
-        <v>561812</v>
+        <v>545127</v>
       </c>
       <c r="C81" s="5">
-        <v>152854</v>
+        <v>163001</v>
       </c>
       <c r="D81" s="5">
-        <v>186847</v>
+        <v>197716</v>
       </c>
     </row>
     <row outlineLevel="0" r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2019-12</t>
+          <t>2020-01</t>
         </is>
       </c>
       <c r="B82" s="5">
-        <v>579221</v>
+        <v>561812</v>
       </c>
       <c r="C82" s="5">
-        <v>151543</v>
+        <v>152854</v>
       </c>
       <c r="D82" s="5">
-        <v>186315</v>
+        <v>186847</v>
       </c>
     </row>
     <row outlineLevel="0" r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2019-11</t>
+          <t>2019-12</t>
         </is>
       </c>
       <c r="B83" s="5">
-        <v>563482</v>
+        <v>579221</v>
       </c>
       <c r="C83" s="5">
-        <v>146935</v>
+        <v>151543</v>
       </c>
       <c r="D83" s="5">
-        <v>186866</v>
+        <v>186315</v>
       </c>
     </row>
     <row outlineLevel="0" r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2019-10</t>
+          <t>2019-11</t>
         </is>
       </c>
       <c r="B84" s="5">
-        <v>554604</v>
+        <v>563482</v>
       </c>
       <c r="C84" s="5">
-        <v>145650</v>
+        <v>146935</v>
       </c>
       <c r="D84" s="5">
-        <v>183966</v>
+        <v>186866</v>
       </c>
     </row>
     <row outlineLevel="0" r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2019-09</t>
+          <t>2019-10</t>
         </is>
       </c>
       <c r="B85" s="5">
-        <v>555910</v>
+        <v>554604</v>
       </c>
       <c r="C85" s="5">
-        <v>150648</v>
+        <v>145650</v>
       </c>
       <c r="D85" s="5">
-        <v>187887</v>
+        <v>183966</v>
       </c>
     </row>
     <row outlineLevel="0" r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2019-08</t>
+          <t>2019-09</t>
         </is>
       </c>
       <c r="B86" s="5">
-        <v>564894</v>
+        <v>555910</v>
       </c>
       <c r="C86" s="5">
-        <v>135567</v>
+        <v>150648</v>
       </c>
       <c r="D86" s="5">
-        <v>181451</v>
+        <v>187887</v>
       </c>
     </row>
     <row outlineLevel="0" r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2019-07</t>
+          <t>2019-08</t>
         </is>
       </c>
       <c r="B87" s="5">
-        <v>602139</v>
+        <v>564894</v>
       </c>
       <c r="C87" s="5">
-        <v>138703</v>
+        <v>135567</v>
       </c>
       <c r="D87" s="5">
-        <v>182613</v>
+        <v>181451</v>
       </c>
     </row>
     <row outlineLevel="0" r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2019-06</t>
+          <t>2019-07</t>
         </is>
       </c>
       <c r="B88" s="5">
-        <v>596304</v>
+        <v>602139</v>
       </c>
       <c r="C88" s="5">
-        <v>139826</v>
+        <v>138703</v>
       </c>
       <c r="D88" s="5">
-        <v>179542</v>
+        <v>182613</v>
       </c>
     </row>
     <row outlineLevel="0" r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2019-05</t>
+          <t>2019-06</t>
         </is>
       </c>
       <c r="B89" s="5">
-        <v>568751</v>
+        <v>596304</v>
       </c>
       <c r="C89" s="5">
-        <v>137489</v>
+        <v>139826</v>
       </c>
       <c r="D89" s="5">
-        <v>179019</v>
+        <v>179542</v>
       </c>
     </row>
     <row outlineLevel="0" r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2019-04</t>
+          <t>2019-05</t>
         </is>
       </c>
       <c r="B90" s="5">
-        <v>588721</v>
+        <v>568751</v>
       </c>
       <c r="C90" s="5">
-        <v>143802</v>
+        <v>137489</v>
       </c>
       <c r="D90" s="5">
-        <v>178523</v>
+        <v>179019</v>
       </c>
     </row>
     <row outlineLevel="0" r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2019-03</t>
+          <t>2019-04</t>
         </is>
       </c>
       <c r="B91" s="5">
-        <v>574013</v>
+        <v>588721</v>
       </c>
       <c r="C91" s="5">
-        <v>141074</v>
+        <v>143802</v>
       </c>
       <c r="D91" s="5">
-        <v>180765</v>
+        <v>178523</v>
       </c>
     </row>
     <row outlineLevel="0" r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2019-02</t>
+          <t>2019-03</t>
         </is>
       </c>
       <c r="B92" s="5">
-        <v>581205</v>
+        <v>574013</v>
       </c>
       <c r="C92" s="5">
-        <v>149686</v>
+        <v>141074</v>
       </c>
       <c r="D92" s="5">
-        <v>181955</v>
+        <v>180765</v>
       </c>
     </row>
     <row outlineLevel="0" r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2019-01</t>
+          <t>2019-02</t>
         </is>
       </c>
       <c r="B93" s="5">
-        <v>568433</v>
+        <v>581205</v>
       </c>
       <c r="C93" s="5">
-        <v>151804</v>
+        <v>149686</v>
       </c>
       <c r="D93" s="5">
-        <v>186050</v>
+        <v>181955</v>
       </c>
     </row>
     <row outlineLevel="0" r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2018-12</t>
+          <t>2019-01</t>
         </is>
       </c>
       <c r="B94" s="5">
-        <v>554285</v>
+        <v>568433</v>
       </c>
       <c r="C94" s="5">
-        <v>159572</v>
+        <v>151804</v>
       </c>
       <c r="D94" s="5">
-        <v>190743</v>
+        <v>186050</v>
       </c>
     </row>
     <row outlineLevel="0" r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2018-11</t>
+          <t>2018-12</t>
         </is>
       </c>
       <c r="B95" s="5">
-        <v>592593</v>
+        <v>554285</v>
       </c>
       <c r="C95" s="5">
-        <v>146452</v>
+        <v>159572</v>
       </c>
       <c r="D95" s="5">
-        <v>178810</v>
+        <v>190743</v>
       </c>
     </row>
     <row outlineLevel="0" r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>2018-10</t>
+          <t>2018-11</t>
         </is>
       </c>
       <c r="B96" s="5">
-        <v>607645</v>
+        <v>592593</v>
       </c>
       <c r="C96" s="5">
-        <v>148037</v>
+        <v>146452</v>
       </c>
       <c r="D96" s="5">
-        <v>183432</v>
+        <v>178810</v>
       </c>
     </row>
     <row outlineLevel="0" r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>2018-09</t>
+          <t>2018-10</t>
         </is>
       </c>
       <c r="B97" s="5">
-        <v>648126</v>
+        <v>607645</v>
       </c>
       <c r="C97" s="5">
-        <v>151384</v>
+        <v>148037</v>
       </c>
       <c r="D97" s="5">
-        <v>188152</v>
+        <v>183432</v>
       </c>
     </row>
     <row outlineLevel="0" r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>2018-08</t>
+          <t>2018-09</t>
         </is>
       </c>
       <c r="B98" s="5">
-        <v>652395</v>
+        <v>648126</v>
       </c>
       <c r="C98" s="5">
-        <v>148873</v>
+        <v>151384</v>
       </c>
       <c r="D98" s="5">
-        <v>178601</v>
+        <v>188152</v>
       </c>
     </row>
     <row outlineLevel="0" r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2018-07</t>
+          <t>2018-08</t>
         </is>
       </c>
       <c r="B99" s="5">
-        <v>652790</v>
+        <v>652395</v>
       </c>
       <c r="C99" s="5">
-        <v>148947</v>
+        <v>148873</v>
       </c>
       <c r="D99" s="5">
-        <v>178299</v>
+        <v>178601</v>
       </c>
     </row>
     <row outlineLevel="0" r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>2018-06</t>
+          <t>2018-07</t>
         </is>
       </c>
       <c r="B100" s="5">
-        <v>646931</v>
+        <v>652790</v>
       </c>
       <c r="C100" s="5">
-        <v>157150</v>
+        <v>148947</v>
       </c>
       <c r="D100" s="5">
-        <v>179399</v>
+        <v>178299</v>
       </c>
     </row>
     <row outlineLevel="0" r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2018-05</t>
+          <t>2018-06</t>
         </is>
       </c>
       <c r="B101" s="5">
-        <v>668940</v>
+        <v>646931</v>
       </c>
       <c r="C101" s="5">
-        <v>155344</v>
+        <v>157150</v>
       </c>
       <c r="D101" s="5">
-        <v>181890</v>
+        <v>179399</v>
       </c>
     </row>
     <row outlineLevel="0" r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2018-04</t>
+          <t>2018-05</t>
         </is>
       </c>
       <c r="B102" s="5">
-        <v>652303</v>
+        <v>668940</v>
       </c>
       <c r="C102" s="5">
-        <v>155989</v>
+        <v>155344</v>
       </c>
       <c r="D102" s="5">
-        <v>179410</v>
+        <v>181890</v>
       </c>
     </row>
     <row outlineLevel="0" r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2018-03</t>
+          <t>2018-04</t>
         </is>
       </c>
       <c r="B103" s="5">
-        <v>645235</v>
+        <v>652303</v>
       </c>
       <c r="C103" s="5">
-        <v>166148</v>
+        <v>155989</v>
       </c>
       <c r="D103" s="5">
-        <v>180751</v>
+        <v>179410</v>
       </c>
     </row>
     <row outlineLevel="0" r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2018-02</t>
+          <t>2018-03</t>
         </is>
       </c>
       <c r="B104" s="5">
-        <v>645064</v>
+        <v>645235</v>
       </c>
       <c r="C104" s="5">
-        <v>164657</v>
+        <v>166148</v>
       </c>
       <c r="D104" s="5">
-        <v>183267</v>
+        <v>180751</v>
       </c>
     </row>
     <row outlineLevel="0" r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2018-01</t>
+          <t>2018-02</t>
         </is>
       </c>
       <c r="B105" s="5">
-        <v>665716</v>
+        <v>645064</v>
       </c>
       <c r="C105" s="5">
-        <v>168450</v>
+        <v>164657</v>
       </c>
       <c r="D105" s="5">
-        <v>181763</v>
+        <v>183267</v>
       </c>
     </row>
     <row outlineLevel="0" r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>2017-12</t>
+          <t>2018-01</t>
         </is>
       </c>
       <c r="B106" s="5">
-        <v>642798</v>
+        <v>665716</v>
       </c>
       <c r="C106" s="5">
-        <v>172999</v>
+        <v>168450</v>
       </c>
       <c r="D106" s="5">
-        <v>182773</v>
+        <v>181763</v>
       </c>
     </row>
     <row outlineLevel="0" r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2017-11</t>
+          <t>2017-12</t>
         </is>
       </c>
       <c r="B107" s="5">
-        <v>627422</v>
+        <v>642798</v>
       </c>
       <c r="C107" s="5">
-        <v>170948</v>
+        <v>172999</v>
       </c>
       <c r="D107" s="5">
-        <v>185312</v>
+        <v>182773</v>
       </c>
     </row>
     <row outlineLevel="0" r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>2017-10</t>
+          <t>2017-11</t>
         </is>
       </c>
       <c r="B108" s="5">
-        <v>607838</v>
+        <v>627422</v>
       </c>
       <c r="C108" s="5">
-        <v>169368</v>
+        <v>170948</v>
       </c>
       <c r="D108" s="5">
-        <v>184047</v>
+        <v>185312</v>
       </c>
     </row>
     <row outlineLevel="0" r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2017-09</t>
+          <t>2017-10</t>
         </is>
       </c>
       <c r="B109" s="5">
-        <v>606334</v>
+        <v>607838</v>
       </c>
       <c r="C109" s="5">
-        <v>172872</v>
+        <v>169368</v>
       </c>
       <c r="D109" s="5">
-        <v>183599</v>
+        <v>184047</v>
       </c>
     </row>
     <row outlineLevel="0" r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>2017-08</t>
+          <t>2017-09</t>
         </is>
       </c>
       <c r="B110" s="5">
-        <v>596567</v>
+        <v>606334</v>
       </c>
       <c r="C110" s="5">
-        <v>170524</v>
+        <v>172872</v>
       </c>
       <c r="D110" s="5">
-        <v>183744</v>
+        <v>183599</v>
       </c>
     </row>
     <row outlineLevel="0" r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2017-07</t>
+          <t>2017-08</t>
         </is>
       </c>
       <c r="B111" s="5">
-        <v>594414</v>
+        <v>596567</v>
       </c>
       <c r="C111" s="5">
-        <v>173195</v>
+        <v>170524</v>
       </c>
       <c r="D111" s="5">
-        <v>184246</v>
+        <v>183744</v>
       </c>
     </row>
     <row outlineLevel="0" r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>2017-06</t>
+          <t>2017-07</t>
         </is>
       </c>
       <c r="B112" s="5">
-        <v>584258</v>
+        <v>594414</v>
       </c>
       <c r="C112" s="5">
-        <v>176707</v>
+        <v>173195</v>
       </c>
       <c r="D112" s="5">
-        <v>187500</v>
+        <v>184246</v>
       </c>
     </row>
     <row outlineLevel="0" r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>2017-05</t>
+          <t>2017-06</t>
         </is>
       </c>
       <c r="B113" s="5">
-        <v>582764</v>
+        <v>584258</v>
       </c>
       <c r="C113" s="5">
-        <v>176970</v>
+        <v>176707</v>
       </c>
       <c r="D113" s="5">
-        <v>185463</v>
+        <v>187500</v>
       </c>
     </row>
     <row outlineLevel="0" r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>2017-04</t>
+          <t>2017-05</t>
         </is>
       </c>
       <c r="B114" s="5">
-        <v>590797</v>
+        <v>582764</v>
       </c>
       <c r="C114" s="5">
-        <v>180908</v>
+        <v>176970</v>
       </c>
       <c r="D114" s="5">
-        <v>184930</v>
+        <v>185463</v>
       </c>
     </row>
     <row outlineLevel="0" r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>2017-03</t>
+          <t>2017-04</t>
         </is>
       </c>
       <c r="B115" s="5">
-        <v>577674</v>
+        <v>590797</v>
       </c>
       <c r="C115" s="5">
-        <v>186892</v>
+        <v>180908</v>
       </c>
       <c r="D115" s="5">
-        <v>184977</v>
+        <v>184930</v>
       </c>
     </row>
     <row outlineLevel="0" r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>2017-02</t>
+          <t>2017-03</t>
         </is>
       </c>
       <c r="B116" s="5">
-        <v>568637</v>
+        <v>577674</v>
       </c>
       <c r="C116" s="5">
-        <v>185720</v>
+        <v>186892</v>
       </c>
       <c r="D116" s="5">
-        <v>184598</v>
+        <v>184977</v>
       </c>
     </row>
     <row outlineLevel="0" r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>2017-01</t>
+          <t>2017-02</t>
         </is>
       </c>
       <c r="B117" s="5">
-        <v>553557</v>
+        <v>568637</v>
       </c>
       <c r="C117" s="5">
-        <v>186301</v>
+        <v>185720</v>
       </c>
       <c r="D117" s="5">
-        <v>186029</v>
+        <v>184598</v>
       </c>
     </row>
     <row outlineLevel="0" r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>2016-12</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="B118" s="5">
-        <v>529372</v>
+        <v>553557</v>
       </c>
       <c r="C118" s="5">
-        <v>188062</v>
+        <v>186301</v>
       </c>
       <c r="D118" s="5">
-        <v>189979</v>
+        <v>186029</v>
       </c>
     </row>
     <row outlineLevel="0" r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>2016-11</t>
+          <t>2016-12</t>
         </is>
       </c>
       <c r="B119" s="5">
-        <v>539972</v>
+        <v>529372</v>
       </c>
       <c r="C119" s="5">
-        <v>179598</v>
+        <v>188062</v>
       </c>
       <c r="D119" s="5">
-        <v>187085</v>
+        <v>189979</v>
       </c>
     </row>
     <row outlineLevel="0" r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>2016-10</t>
+          <t>2016-11</t>
         </is>
       </c>
       <c r="B120" s="5">
-        <v>523760</v>
+        <v>539972</v>
       </c>
       <c r="C120" s="5">
-        <v>182051</v>
+        <v>179598</v>
       </c>
       <c r="D120" s="5">
-        <v>182986</v>
+        <v>187085</v>
       </c>
     </row>
     <row outlineLevel="0" r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>2016-09</t>
+          <t>2016-10</t>
         </is>
       </c>
       <c r="B121" s="5">
-        <v>540615</v>
+        <v>523760</v>
       </c>
       <c r="C121" s="5">
-        <v>184757</v>
+        <v>182051</v>
       </c>
       <c r="D121" s="5">
-        <v>182833</v>
+        <v>182986</v>
       </c>
     </row>
     <row outlineLevel="0" r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>2016-08</t>
+          <t>2016-09</t>
         </is>
       </c>
       <c r="B122" s="5">
-        <v>510157</v>
+        <v>540615</v>
       </c>
       <c r="C122" s="5">
-        <v>177764</v>
+        <v>184757</v>
       </c>
       <c r="D122" s="5">
-        <v>185695</v>
+        <v>182833</v>
       </c>
     </row>
     <row outlineLevel="0" r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>2016-07</t>
+          <t>2016-08</t>
         </is>
       </c>
       <c r="B123" s="5">
-        <v>513221</v>
+        <v>510157</v>
       </c>
       <c r="C123" s="5">
-        <v>183435</v>
+        <v>177764</v>
       </c>
       <c r="D123" s="5">
-        <v>188155</v>
+        <v>185695</v>
       </c>
     </row>
     <row outlineLevel="0" r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>2016-06</t>
+          <t>2016-07</t>
         </is>
       </c>
       <c r="B124" s="5">
-        <v>487636</v>
+        <v>513221</v>
       </c>
       <c r="C124" s="5">
-        <v>186233</v>
+        <v>183435</v>
       </c>
       <c r="D124" s="5">
-        <v>189585</v>
+        <v>188155</v>
       </c>
     </row>
     <row outlineLevel="0" r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>2016-05</t>
+          <t>2016-06</t>
         </is>
       </c>
       <c r="B125" s="5">
-        <v>489867</v>
+        <v>487636</v>
       </c>
       <c r="C125" s="5">
-        <v>177161</v>
+        <v>186233</v>
       </c>
       <c r="D125" s="5">
-        <v>187495</v>
+        <v>189585</v>
       </c>
     </row>
     <row outlineLevel="0" r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>2016-04</t>
+          <t>2016-05</t>
         </is>
       </c>
       <c r="B126" s="5">
-        <v>495178</v>
+        <v>489867</v>
       </c>
       <c r="C126" s="5">
-        <v>176016</v>
+        <v>177161</v>
       </c>
       <c r="D126" s="5">
-        <v>187000</v>
+        <v>187495</v>
       </c>
     </row>
     <row outlineLevel="0" r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>2016-03</t>
+          <t>2016-04</t>
         </is>
       </c>
       <c r="B127" s="5">
-        <v>483909</v>
+        <v>495178</v>
       </c>
       <c r="C127" s="5">
-        <v>182673</v>
+        <v>176016</v>
       </c>
       <c r="D127" s="5">
-        <v>172525</v>
+        <v>187000</v>
       </c>
     </row>
     <row outlineLevel="0" r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>2016-02</t>
+          <t>2016-03</t>
         </is>
       </c>
       <c r="B128" s="5">
-        <v>474156</v>
+        <v>483909</v>
       </c>
       <c r="C128" s="5">
-        <v>178989</v>
+        <v>182673</v>
       </c>
       <c r="D128" s="5">
-        <v>168308</v>
+        <v>172525</v>
       </c>
     </row>
     <row outlineLevel="0" r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>2016-01</t>
+          <t>2016-02</t>
         </is>
       </c>
       <c r="B129" s="5">
-        <v>487200</v>
+        <v>474156</v>
       </c>
       <c r="C129" s="5">
-        <v>180616</v>
+        <v>178989</v>
       </c>
       <c r="D129" s="5">
-        <v>162825</v>
+        <v>168308</v>
       </c>
     </row>
     <row outlineLevel="0" r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>2015-12</t>
+          <t>2016-01</t>
         </is>
       </c>
       <c r="B130" s="5">
-        <v>503444</v>
+        <v>487200</v>
       </c>
       <c r="C130" s="5">
-        <v>181812</v>
+        <v>180616</v>
       </c>
       <c r="D130" s="5">
-        <v>159677</v>
+        <v>162825</v>
       </c>
     </row>
     <row outlineLevel="0" r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>2015-11</t>
+          <t>2015-12</t>
         </is>
       </c>
       <c r="B131" s="5">
-        <v>515410</v>
+        <v>503444</v>
       </c>
       <c r="C131" s="5">
-        <v>174607</v>
+        <v>181812</v>
       </c>
       <c r="D131" s="5">
-        <v>165584</v>
+        <v>159677</v>
       </c>
     </row>
     <row outlineLevel="0" r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>2015-10</t>
+          <t>2015-11</t>
         </is>
       </c>
       <c r="B132" s="5">
-        <v>513941</v>
+        <v>515410</v>
       </c>
       <c r="C132" s="5">
-        <v>174437</v>
+        <v>174607</v>
       </c>
       <c r="D132" s="5">
-        <v>163210</v>
+        <v>165584</v>
       </c>
     </row>
     <row outlineLevel="0" r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>2015-09</t>
+          <t>2015-10</t>
         </is>
       </c>
       <c r="B133" s="5">
-        <v>497279</v>
+        <v>513941</v>
       </c>
       <c r="C133" s="5">
-        <v>173760</v>
+        <v>174437</v>
       </c>
       <c r="D133" s="5">
-        <v>167132</v>
+        <v>163210</v>
       </c>
     </row>
     <row outlineLevel="0" r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2015-09</t>
         </is>
       </c>
       <c r="B134" s="5">
-        <v>515960</v>
+        <v>497279</v>
       </c>
       <c r="C134" s="5">
-        <v>175647</v>
+        <v>173760</v>
       </c>
       <c r="D134" s="5">
-        <v>168692</v>
+        <v>167132</v>
       </c>
     </row>
     <row outlineLevel="0" r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>2015-07</t>
+          <t>2015-08</t>
         </is>
       </c>
       <c r="B135" s="5">
-        <v>530744</v>
+        <v>515960</v>
       </c>
       <c r="C135" s="5">
-        <v>168659</v>
+        <v>175647</v>
       </c>
       <c r="D135" s="5">
-        <v>169132</v>
+        <v>168692</v>
       </c>
     </row>
     <row outlineLevel="0" r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>2015-06</t>
+          <t>2015-07</t>
         </is>
       </c>
       <c r="B136" s="5">
-        <v>547957</v>
+        <v>530744</v>
       </c>
       <c r="C136" s="5">
-        <v>170614</v>
+        <v>168659</v>
       </c>
       <c r="D136" s="5">
-        <v>168441</v>
+        <v>169132</v>
       </c>
     </row>
     <row outlineLevel="0" r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>2015-05</t>
+          <t>2015-06</t>
         </is>
       </c>
       <c r="B137" s="5">
-        <v>541671</v>
+        <v>547957</v>
       </c>
       <c r="C137" s="5">
-        <v>166334</v>
+        <v>170614</v>
       </c>
       <c r="D137" s="5">
-        <v>169076</v>
+        <v>168441</v>
       </c>
     </row>
     <row outlineLevel="0" r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>2015-04</t>
+          <t>2015-05</t>
         </is>
       </c>
       <c r="B138" s="5">
-        <v>549964</v>
+        <v>541671</v>
       </c>
       <c r="C138" s="5">
-        <v>168430</v>
+        <v>166334</v>
       </c>
       <c r="D138" s="5">
-        <v>167073</v>
+        <v>169076</v>
       </c>
     </row>
     <row outlineLevel="0" r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>2015-03</t>
+          <t>2015-04</t>
         </is>
       </c>
       <c r="B139" s="5">
-        <v>518055</v>
+        <v>549964</v>
       </c>
       <c r="C139" s="5">
-        <v>171625</v>
+        <v>168430</v>
       </c>
       <c r="D139" s="5">
-        <v>170074</v>
+        <v>167073</v>
       </c>
     </row>
     <row outlineLevel="0" r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>2015-02</t>
+          <t>2015-03</t>
         </is>
       </c>
       <c r="B140" s="5">
-        <v>504923</v>
+        <v>518055</v>
       </c>
       <c r="C140" s="5">
-        <v>168371</v>
+        <v>171625</v>
       </c>
       <c r="D140" s="5">
-        <v>170930</v>
+        <v>170074</v>
       </c>
     </row>
     <row outlineLevel="0" r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2015-02</t>
         </is>
       </c>
       <c r="B141" s="5">
-        <v>485872</v>
+        <v>504923</v>
       </c>
       <c r="C141" s="5">
-        <v>163599</v>
+        <v>168371</v>
       </c>
       <c r="D141" s="5">
-        <v>178259</v>
+        <v>170930</v>
       </c>
     </row>
     <row outlineLevel="0" r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>2014-12</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="B142" s="5">
-        <v>495756</v>
+        <v>485872</v>
       </c>
       <c r="C142" s="5">
-        <v>169295</v>
+        <v>163599</v>
       </c>
       <c r="D142" s="5">
-        <v>181223</v>
+        <v>178259</v>
       </c>
     </row>
     <row outlineLevel="0" r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>2014-11</t>
+          <t>2014-12</t>
         </is>
       </c>
       <c r="B143" s="5">
-        <v>496341</v>
+        <v>495756</v>
       </c>
       <c r="C143" s="5">
-        <v>158420</v>
+        <v>169295</v>
       </c>
       <c r="D143" s="5">
-        <v>184227</v>
+        <v>181223</v>
       </c>
     </row>
     <row outlineLevel="0" r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>2014-10</t>
+          <t>2014-11</t>
         </is>
       </c>
       <c r="B144" s="5">
-        <v>492888</v>
+        <v>496341</v>
       </c>
       <c r="C144" s="5">
-        <v>158624</v>
+        <v>158420</v>
       </c>
       <c r="D144" s="5">
-        <v>185193</v>
+        <v>184227</v>
       </c>
     </row>
     <row outlineLevel="0" r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>2014-09</t>
+          <t>2014-10</t>
         </is>
       </c>
       <c r="B145" s="5">
-        <v>503901</v>
+        <v>492888</v>
       </c>
       <c r="C145" s="5">
-        <v>161621</v>
+        <v>158624</v>
       </c>
       <c r="D145" s="5">
-        <v>183243</v>
+        <v>185193</v>
       </c>
     </row>
     <row outlineLevel="0" r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2014-09</t>
         </is>
       </c>
       <c r="B146" s="5">
-        <v>501000</v>
+        <v>503901</v>
       </c>
       <c r="C146" s="5">
-        <v>155245</v>
+        <v>161621</v>
       </c>
       <c r="D146" s="5">
-        <v>180820</v>
+        <v>183243</v>
       </c>
     </row>
     <row outlineLevel="0" r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>2014-07</t>
+          <t>2014-08</t>
         </is>
       </c>
       <c r="B147" s="5">
-        <v>498671</v>
+        <v>501000</v>
       </c>
       <c r="C147" s="5">
-        <v>155931</v>
+        <v>155245</v>
       </c>
       <c r="D147" s="5">
-        <v>177981</v>
+        <v>180820</v>
       </c>
     </row>
     <row outlineLevel="0" r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>2014-06</t>
+          <t>2014-07</t>
         </is>
       </c>
       <c r="B148" s="5">
-        <v>502270</v>
+        <v>498671</v>
       </c>
       <c r="C148" s="5">
-        <v>160293</v>
+        <v>155931</v>
       </c>
       <c r="D148" s="5">
-        <v>184723</v>
+        <v>177981</v>
       </c>
     </row>
     <row outlineLevel="0" r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>2014-05</t>
+          <t>2014-06</t>
         </is>
       </c>
       <c r="B149" s="5">
-        <v>475362</v>
+        <v>502270</v>
       </c>
       <c r="C149" s="5">
-        <v>150474</v>
+        <v>160293</v>
       </c>
       <c r="D149" s="5">
-        <v>188551</v>
+        <v>184723</v>
       </c>
     </row>
     <row outlineLevel="0" r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>2014-04</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="B150" s="5">
-        <v>475195</v>
+        <v>475362</v>
       </c>
       <c r="C150" s="5">
-        <v>149801</v>
+        <v>150474</v>
       </c>
       <c r="D150" s="5">
-        <v>194679</v>
+        <v>188551</v>
       </c>
     </row>
     <row outlineLevel="0" r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>2014-03</t>
+          <t>2014-04</t>
         </is>
       </c>
       <c r="B151" s="5">
-        <v>487932</v>
+        <v>475195</v>
       </c>
       <c r="C151" s="5">
-        <v>156083</v>
+        <v>149801</v>
       </c>
       <c r="D151" s="5">
-        <v>194461</v>
+        <v>194679</v>
       </c>
     </row>
     <row outlineLevel="0" r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>2014-02</t>
+          <t>2014-03</t>
         </is>
       </c>
       <c r="B152" s="5">
-        <v>502093</v>
+        <v>487932</v>
       </c>
       <c r="C152" s="5">
-        <v>154049</v>
+        <v>156083</v>
       </c>
       <c r="D152" s="5">
-        <v>190312</v>
+        <v>194461</v>
       </c>
     </row>
     <row outlineLevel="0" r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>2014-01</t>
+          <t>2014-02</t>
         </is>
       </c>
       <c r="B153" s="5">
-        <v>487549</v>
+        <v>502093</v>
       </c>
       <c r="C153" s="5">
-        <v>151878</v>
+        <v>154049</v>
       </c>
       <c r="D153" s="5">
-        <v>195863</v>
+        <v>190312</v>
       </c>
     </row>
     <row outlineLevel="0" r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>2013-12</t>
+          <t>2014-01</t>
         </is>
       </c>
       <c r="B154" s="5">
-        <v>478502</v>
+        <v>487549</v>
       </c>
       <c r="C154" s="5">
-        <v>157000</v>
+        <v>151878</v>
       </c>
       <c r="D154" s="5">
-        <v>197521</v>
+        <v>195863</v>
       </c>
     </row>
     <row outlineLevel="0" r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>2013-11</t>
+          <t>2013-12</t>
         </is>
       </c>
       <c r="B155" s="5">
-        <v>456378</v>
+        <v>478502</v>
       </c>
       <c r="C155" s="5">
-        <v>150214</v>
+        <v>157000</v>
       </c>
       <c r="D155" s="5">
-        <v>199153</v>
+        <v>197521</v>
       </c>
     </row>
     <row outlineLevel="0" r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>2013-10</t>
+          <t>2013-11</t>
         </is>
       </c>
       <c r="B156" s="5">
-        <v>445022</v>
+        <v>456378</v>
       </c>
       <c r="C156" s="5">
-        <v>151494</v>
+        <v>150214</v>
       </c>
       <c r="D156" s="5">
-        <v>199889</v>
+        <v>199153</v>
       </c>
     </row>
     <row outlineLevel="0" r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>2013-09</t>
+          <t>2013-10</t>
         </is>
       </c>
       <c r="B157" s="5">
-        <v>432852</v>
+        <v>445022</v>
       </c>
       <c r="C157" s="5">
-        <v>149895</v>
+        <v>151494</v>
       </c>
       <c r="D157" s="5">
-        <v>197780</v>
+        <v>199889</v>
       </c>
     </row>
     <row outlineLevel="0" r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>2013-08</t>
+          <t>2013-09</t>
         </is>
       </c>
       <c r="B158" s="5">
-        <v>414442</v>
+        <v>432852</v>
       </c>
       <c r="C158" s="5">
-        <v>143808</v>
+        <v>149895</v>
       </c>
       <c r="D158" s="5">
-        <v>195181</v>
+        <v>197780</v>
       </c>
     </row>
     <row outlineLevel="0" r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>2013-07</t>
+          <t>2013-08</t>
         </is>
       </c>
       <c r="B159" s="5">
-        <v>412101</v>
+        <v>414442</v>
       </c>
       <c r="C159" s="5">
-        <v>144495</v>
+        <v>143808</v>
       </c>
       <c r="D159" s="5">
-        <v>194790</v>
+        <v>195181</v>
       </c>
     </row>
     <row outlineLevel="0" r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>2013-06</t>
+          <t>2013-07</t>
         </is>
       </c>
       <c r="B160" s="5">
-        <v>407681</v>
+        <v>412101</v>
       </c>
       <c r="C160" s="5">
-        <v>150093</v>
+        <v>144495</v>
       </c>
       <c r="D160" s="5">
-        <v>200308</v>
+        <v>194790</v>
       </c>
     </row>
     <row outlineLevel="0" r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>2013-05</t>
+          <t>2013-06</t>
         </is>
       </c>
       <c r="B161" s="5">
-        <v>401606</v>
+        <v>407681</v>
       </c>
       <c r="C161" s="5">
-        <v>146765</v>
+        <v>150093</v>
       </c>
       <c r="D161" s="5">
-        <v>199756</v>
+        <v>200308</v>
       </c>
     </row>
     <row outlineLevel="0" r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>2013-04</t>
+          <t>2013-05</t>
         </is>
       </c>
       <c r="B162" s="5">
-        <v>408677</v>
+        <v>401606</v>
       </c>
       <c r="C162" s="5">
-        <v>140706</v>
+        <v>146765</v>
       </c>
       <c r="D162" s="5">
-        <v>191719</v>
+        <v>199756</v>
       </c>
     </row>
     <row outlineLevel="0" r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>2013-03</t>
+          <t>2013-04</t>
         </is>
       </c>
       <c r="B163" s="5">
-        <v>403933</v>
+        <v>408677</v>
       </c>
       <c r="C163" s="5">
-        <v>144530</v>
+        <v>140706</v>
       </c>
       <c r="D163" s="5">
-        <v>197887</v>
+        <v>191719</v>
       </c>
     </row>
     <row outlineLevel="0" r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>2013-02</t>
+          <t>2013-03</t>
         </is>
       </c>
       <c r="B164" s="5">
-        <v>390351</v>
+        <v>403933</v>
       </c>
       <c r="C164" s="5">
-        <v>142123</v>
+        <v>144530</v>
       </c>
       <c r="D164" s="5">
-        <v>208682</v>
+        <v>197887</v>
       </c>
     </row>
     <row outlineLevel="0" r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>2013-01</t>
+          <t>2013-02</t>
         </is>
       </c>
       <c r="B165" s="5">
-        <v>388123</v>
+        <v>390351</v>
       </c>
       <c r="C165" s="5">
-        <v>142856</v>
+        <v>142123</v>
       </c>
       <c r="D165" s="5">
-        <v>199709</v>
+        <v>208682</v>
       </c>
     </row>
     <row outlineLevel="0" r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>2012-12</t>
+          <t>2013-01</t>
         </is>
       </c>
       <c r="B166" s="5">
-        <v>355009</v>
+        <v>388123</v>
       </c>
       <c r="C166" s="5">
-        <v>162206</v>
+        <v>142856</v>
       </c>
       <c r="D166" s="5">
-        <v>211576</v>
+        <v>199709</v>
       </c>
     </row>
     <row outlineLevel="0" r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>2012-11</t>
+          <t>2012-12</t>
         </is>
       </c>
       <c r="B167" s="5">
-        <v>351441</v>
+        <v>355009</v>
       </c>
       <c r="C167" s="5">
-        <v>135650</v>
+        <v>162206</v>
       </c>
       <c r="D167" s="5">
-        <v>202425</v>
+        <v>211576</v>
       </c>
     </row>
     <row outlineLevel="0" r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>2012-10</t>
+          <t>2012-11</t>
         </is>
       </c>
       <c r="B168" s="5">
-        <v>342325</v>
+        <v>351441</v>
       </c>
       <c r="C168" s="5">
-        <v>124800</v>
+        <v>135650</v>
       </c>
       <c r="D168" s="5">
-        <v>200406</v>
+        <v>202425</v>
       </c>
     </row>
     <row outlineLevel="0" r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>2012-09</t>
+          <t>2012-10</t>
         </is>
       </c>
       <c r="B169" s="5">
-        <v>339159</v>
+        <v>342325</v>
       </c>
       <c r="C169" s="5">
-        <v>129389</v>
+        <v>124800</v>
       </c>
       <c r="D169" s="5">
-        <v>205176</v>
+        <v>200406</v>
       </c>
     </row>
     <row outlineLevel="0" r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>2012-08</t>
+          <t>2012-09</t>
         </is>
       </c>
       <c r="B170" s="5">
-        <v>320395</v>
+        <v>339159</v>
       </c>
       <c r="C170" s="5">
-        <v>124276</v>
+        <v>129389</v>
       </c>
       <c r="D170" s="5">
-        <v>196786</v>
+        <v>205176</v>
       </c>
     </row>
     <row outlineLevel="0" r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>2012-07</t>
+          <t>2012-08</t>
         </is>
       </c>
       <c r="B171" s="5">
-        <v>313525</v>
+        <v>320395</v>
       </c>
       <c r="C171" s="5">
-        <v>124330</v>
+        <v>124276</v>
       </c>
       <c r="D171" s="5">
-        <v>194741</v>
+        <v>196786</v>
       </c>
     </row>
     <row outlineLevel="0" r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>2012-06</t>
+          <t>2012-07</t>
         </is>
       </c>
       <c r="B172" s="5">
-        <v>320952</v>
+        <v>313525</v>
       </c>
       <c r="C172" s="5">
-        <v>138937</v>
+        <v>124330</v>
       </c>
       <c r="D172" s="5">
-        <v>192149</v>
+        <v>194741</v>
       </c>
     </row>
     <row outlineLevel="0" r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>2012-05</t>
+          <t>2012-06</t>
         </is>
       </c>
       <c r="B173" s="5">
-        <v>315147</v>
+        <v>320952</v>
       </c>
       <c r="C173" s="5">
-        <v>139111</v>
+        <v>138937</v>
       </c>
       <c r="D173" s="5">
-        <v>187938</v>
+        <v>192149</v>
       </c>
     </row>
     <row outlineLevel="0" r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>2012-04</t>
+          <t>2012-05</t>
         </is>
       </c>
       <c r="B174" s="5">
-        <v>335154</v>
+        <v>315147</v>
       </c>
       <c r="C174" s="5">
-        <v>138909</v>
+        <v>139111</v>
       </c>
       <c r="D174" s="5">
-        <v>182021</v>
+        <v>187938</v>
       </c>
     </row>
     <row outlineLevel="0" r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>2012-03</t>
+          <t>2012-04</t>
         </is>
       </c>
       <c r="B175" s="5">
-        <v>330815</v>
+        <v>335154</v>
       </c>
       <c r="C175" s="5">
-        <v>142297</v>
+        <v>138909</v>
       </c>
       <c r="D175" s="5">
-        <v>182814</v>
+        <v>182021</v>
       </c>
     </row>
     <row outlineLevel="0" r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>2012-02</t>
+          <t>2012-03</t>
         </is>
       </c>
       <c r="B176" s="5">
-        <v>323021</v>
+        <v>330815</v>
       </c>
       <c r="C176" s="5">
-        <v>139609</v>
+        <v>142297</v>
       </c>
       <c r="D176" s="5">
-        <v>177639</v>
+        <v>182814</v>
       </c>
     </row>
     <row outlineLevel="0" r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>2012-01</t>
+          <t>2012-02</t>
         </is>
       </c>
       <c r="B177" s="5">
-        <v>309844</v>
+        <v>323021</v>
       </c>
       <c r="C177" s="5">
-        <v>137309</v>
+        <v>139609</v>
       </c>
       <c r="D177" s="5">
-        <v>174889</v>
+        <v>177639</v>
       </c>
     </row>
     <row outlineLevel="0" r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>2011-12</t>
+          <t>2012-01</t>
         </is>
       </c>
       <c r="B178" s="5">
-        <v>301616</v>
+        <v>309844</v>
       </c>
       <c r="C178" s="5">
-        <v>142533</v>
+        <v>137309</v>
       </c>
       <c r="D178" s="5">
-        <v>189143</v>
+        <v>174889</v>
       </c>
     </row>
     <row outlineLevel="0" r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>2011-11</t>
+          <t>2011-12</t>
         </is>
       </c>
       <c r="B179" s="5">
-        <v>303930</v>
+        <v>301616</v>
       </c>
       <c r="C179" s="5">
-        <v>132934</v>
+        <v>142533</v>
       </c>
       <c r="D179" s="5">
-        <v>188259</v>
+        <v>189143</v>
       </c>
     </row>
     <row outlineLevel="0" r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>2011-10</t>
+          <t>2011-11</t>
         </is>
       </c>
       <c r="B180" s="5">
-        <v>317028</v>
+        <v>303930</v>
       </c>
       <c r="C180" s="5">
-        <v>133639</v>
+        <v>132934</v>
       </c>
       <c r="D180" s="5">
-        <v>188141</v>
+        <v>188259</v>
       </c>
     </row>
     <row outlineLevel="0" r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>2011-09</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="B181" s="5">
-        <v>298277</v>
+        <v>317028</v>
       </c>
       <c r="C181" s="5">
-        <v>141806</v>
+        <v>133639</v>
       </c>
       <c r="D181" s="5">
-        <v>204307</v>
+        <v>188141</v>
       </c>
     </row>
     <row outlineLevel="0" r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>2011-08</t>
+          <t>2011-09</t>
         </is>
       </c>
       <c r="B182" s="5">
-        <v>308866</v>
+        <v>298277</v>
       </c>
       <c r="C182" s="5">
-        <v>135508</v>
+        <v>141806</v>
       </c>
       <c r="D182" s="5">
-        <v>193533</v>
+        <v>204307</v>
       </c>
     </row>
     <row outlineLevel="0" r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>2011-07</t>
+          <t>2011-08</t>
         </is>
       </c>
       <c r="B183" s="5">
-        <v>344572</v>
+        <v>308866</v>
       </c>
       <c r="C183" s="5">
-        <v>138316</v>
+        <v>135508</v>
       </c>
       <c r="D183" s="5">
-        <v>182957</v>
+        <v>193533</v>
       </c>
     </row>
     <row outlineLevel="0" r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>2011-06</t>
+          <t>2011-07</t>
         </is>
       </c>
       <c r="B184" s="5">
-        <v>345273</v>
+        <v>344572</v>
       </c>
       <c r="C184" s="5">
-        <v>139575</v>
+        <v>138316</v>
       </c>
       <c r="D184" s="5">
-        <v>183547</v>
+        <v>182957</v>
       </c>
     </row>
     <row outlineLevel="0" r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>2011-05</t>
+          <t>2011-06</t>
         </is>
       </c>
       <c r="B185" s="5">
-        <v>355736</v>
+        <v>345273</v>
       </c>
       <c r="C185" s="5">
-        <v>133727</v>
+        <v>139575</v>
       </c>
       <c r="D185" s="5">
-        <v>175508</v>
+        <v>183547</v>
       </c>
     </row>
     <row outlineLevel="0" r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>2011-04</t>
+          <t>2011-05</t>
         </is>
       </c>
       <c r="B186" s="5">
-        <v>360883</v>
+        <v>355736</v>
       </c>
       <c r="C186" s="5">
-        <v>133131</v>
+        <v>133727</v>
       </c>
       <c r="D186" s="5">
-        <v>175399</v>
+        <v>175508</v>
       </c>
     </row>
     <row outlineLevel="0" r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>2011-03</t>
+          <t>2011-04</t>
         </is>
       </c>
       <c r="B187" s="5">
-        <v>355413</v>
+        <v>360883</v>
       </c>
       <c r="C187" s="5">
-        <v>133386</v>
+        <v>133131</v>
       </c>
       <c r="D187" s="5">
-        <v>170139</v>
+        <v>175399</v>
       </c>
     </row>
     <row outlineLevel="0" r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>2011-02</t>
+          <t>2011-03</t>
         </is>
       </c>
       <c r="B188" s="5">
-        <v>348979</v>
+        <v>355413</v>
       </c>
       <c r="C188" s="5">
-        <v>135760</v>
+        <v>133386</v>
       </c>
       <c r="D188" s="5">
-        <v>179102</v>
+        <v>170139</v>
       </c>
     </row>
     <row outlineLevel="0" r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>2011-01</t>
+          <t>2011-02</t>
         </is>
       </c>
       <c r="B189" s="5">
-        <v>326868</v>
+        <v>348979</v>
       </c>
       <c r="C189" s="5">
-        <v>130894</v>
+        <v>135760</v>
       </c>
       <c r="D189" s="5">
-        <v>173545</v>
+        <v>179102</v>
       </c>
     </row>
     <row outlineLevel="0" r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>2010-12</t>
+          <t>2011-01</t>
         </is>
       </c>
       <c r="B190" s="5">
-        <v>313678</v>
+        <v>326868</v>
       </c>
       <c r="C190" s="5">
-        <v>126098</v>
+        <v>130894</v>
       </c>
       <c r="D190" s="5">
-        <v>182426</v>
+        <v>173545</v>
       </c>
     </row>
     <row outlineLevel="0" r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>2010-11</t>
+          <t>2010-12</t>
         </is>
       </c>
       <c r="B191" s="5">
-        <v>309340</v>
+        <v>313678</v>
       </c>
       <c r="C191" s="5">
-        <v>119305</v>
+        <v>126098</v>
       </c>
       <c r="D191" s="5">
-        <v>176805</v>
+        <v>182426</v>
       </c>
     </row>
     <row outlineLevel="0" r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>2010-10</t>
+          <t>2010-11</t>
         </is>
       </c>
       <c r="B192" s="5">
-        <v>303428</v>
+        <v>309340</v>
       </c>
       <c r="C192" s="5">
-        <v>114784</v>
+        <v>119305</v>
       </c>
       <c r="D192" s="5">
-        <v>176588</v>
+        <v>176805</v>
       </c>
     </row>
     <row outlineLevel="0" r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>2010-09</t>
+          <t>2010-10</t>
         </is>
       </c>
       <c r="B193" s="5">
-        <v>288540</v>
+        <v>303428</v>
       </c>
       <c r="C193" s="5">
-        <v>114321</v>
+        <v>114784</v>
       </c>
       <c r="D193" s="5">
-        <v>173544</v>
+        <v>176588</v>
       </c>
     </row>
     <row outlineLevel="0" r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>2010-08</t>
+          <t>2010-09</t>
         </is>
       </c>
       <c r="B194" s="5">
-        <v>268371</v>
+        <v>288540</v>
       </c>
       <c r="C194" s="5">
-        <v>106870</v>
+        <v>114321</v>
       </c>
       <c r="D194" s="5">
-        <v>174209</v>
+        <v>173544</v>
       </c>
     </row>
     <row outlineLevel="0" r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>2010-07</t>
+          <t>2010-08</t>
         </is>
       </c>
       <c r="B195" s="5">
-        <v>267468</v>
+        <v>268371</v>
       </c>
       <c r="C195" s="5">
-        <v>106290</v>
+        <v>106870</v>
       </c>
       <c r="D195" s="5">
-        <v>172179</v>
+        <v>174209</v>
       </c>
     </row>
     <row outlineLevel="0" r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>2010-06</t>
+          <t>2010-07</t>
         </is>
       </c>
       <c r="B196" s="5">
-        <v>263202</v>
+        <v>267468</v>
       </c>
       <c r="C196" s="5">
-        <v>114265</v>
+        <v>106290</v>
       </c>
       <c r="D196" s="5">
-        <v>172908</v>
+        <v>172179</v>
       </c>
     </row>
     <row outlineLevel="0" r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>2010-05</t>
+          <t>2010-06</t>
         </is>
       </c>
       <c r="B197" s="5">
-        <v>268566</v>
+        <v>263202</v>
       </c>
       <c r="C197" s="5">
-        <v>114051</v>
+        <v>114265</v>
       </c>
       <c r="D197" s="5">
-        <v>166706</v>
+        <v>172908</v>
       </c>
     </row>
     <row outlineLevel="0" r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>2010-04</t>
+          <t>2010-05</t>
         </is>
       </c>
       <c r="B198" s="5">
-        <v>295550</v>
+        <v>268566</v>
       </c>
       <c r="C198" s="5">
-        <v>111217</v>
+        <v>114051</v>
       </c>
       <c r="D198" s="5">
-        <v>160630</v>
+        <v>166706</v>
       </c>
     </row>
     <row outlineLevel="0" r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>2010-03</t>
+          <t>2010-04</t>
         </is>
       </c>
       <c r="B199" s="5">
-        <v>277798</v>
+        <v>295550</v>
       </c>
       <c r="C199" s="5">
-        <v>108908</v>
+        <v>111217</v>
       </c>
       <c r="D199" s="5">
-        <v>162169</v>
+        <v>160630</v>
       </c>
     </row>
     <row outlineLevel="0" r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>2010-02</t>
+          <t>2010-03</t>
         </is>
       </c>
       <c r="B200" s="5">
-        <v>263657</v>
+        <v>277798</v>
       </c>
       <c r="C200" s="5">
-        <v>106131</v>
+        <v>108908</v>
       </c>
       <c r="D200" s="5">
-        <v>164624</v>
+        <v>162169</v>
       </c>
     </row>
     <row outlineLevel="0" r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>2010-01</t>
+          <t>2010-02</t>
         </is>
       </c>
       <c r="B201" s="5">
-        <v>266455</v>
+        <v>263657</v>
       </c>
       <c r="C201" s="5">
-        <v>281035</v>
+        <v>106131</v>
+      </c>
+      <c r="D201" s="5">
+        <v>164624</v>
       </c>
     </row>
     <row outlineLevel="0" r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2010-01</t>
         </is>
       </c>
       <c r="B202" s="5">
-        <v>262399</v>
+        <v>266455</v>
       </c>
       <c r="C202" s="5">
-        <v>281043</v>
+        <v>281035</v>
       </c>
     </row>
     <row outlineLevel="0" r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-12</t>
         </is>
       </c>
       <c r="B203" s="5">
-        <v>250988</v>
+        <v>262399</v>
       </c>
       <c r="C203" s="5">
-        <v>284071</v>
+        <v>281043</v>
       </c>
     </row>
     <row outlineLevel="0" r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-11</t>
         </is>
       </c>
       <c r="B204" s="5">
-        <v>265404</v>
+        <v>250988</v>
       </c>
       <c r="C204" s="5">
-        <v>299858</v>
+        <v>284071</v>
       </c>
     </row>
     <row outlineLevel="0" r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-10</t>
         </is>
       </c>
       <c r="B205" s="5">
-        <v>254107</v>
+        <v>265404</v>
       </c>
       <c r="C205" s="5">
-        <v>287196</v>
+        <v>299858</v>
       </c>
     </row>
     <row outlineLevel="0" r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-09</t>
         </is>
       </c>
       <c r="B206" s="5">
-        <v>236251</v>
+        <v>254107</v>
       </c>
       <c r="C206" s="5">
-        <v>281989</v>
+        <v>287196</v>
       </c>
     </row>
     <row outlineLevel="0" r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-08</t>
         </is>
       </c>
       <c r="B207" s="5">
-        <v>228734</v>
+        <v>236251</v>
       </c>
       <c r="C207" s="5">
-        <v>277082</v>
+        <v>281989</v>
       </c>
     </row>
     <row outlineLevel="0" r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="B208" s="5">
-        <v>217140</v>
+        <v>228734</v>
       </c>
       <c r="C208" s="5">
-        <v>283874</v>
+        <v>277082</v>
       </c>
     </row>
     <row outlineLevel="0" r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="B209" s="5">
-        <v>214401</v>
+        <v>217140</v>
       </c>
       <c r="C209" s="5">
-        <v>275313</v>
+        <v>283874</v>
       </c>
     </row>
     <row outlineLevel="0" r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="B210" s="5">
-        <v>208010</v>
+        <v>214401</v>
       </c>
       <c r="C210" s="5">
-        <v>285658</v>
+        <v>275313</v>
       </c>
     </row>
     <row outlineLevel="0" r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="B211" s="5">
-        <v>203967</v>
+        <v>208010</v>
       </c>
       <c r="C211" s="5">
-        <v>291927</v>
+        <v>285658</v>
       </c>
     </row>
     <row outlineLevel="0" r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="B212" s="5">
-        <v>199655</v>
+        <v>203967</v>
       </c>
       <c r="C212" s="5">
-        <v>310503</v>
+        <v>291927</v>
       </c>
     </row>
     <row outlineLevel="0" r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="B213" s="5">
-        <v>205007</v>
+        <v>199655</v>
       </c>
       <c r="C213" s="5">
-        <v>316763</v>
+        <v>310503</v>
       </c>
     </row>
     <row outlineLevel="0" r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="B214" s="5">
-        <v>210185</v>
+        <v>205007</v>
       </c>
       <c r="C214" s="5">
-        <v>345713</v>
+        <v>316763</v>
       </c>
     </row>
     <row outlineLevel="0" r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="B215" s="5">
-        <v>227334</v>
+        <v>210185</v>
       </c>
       <c r="C215" s="5">
-        <v>364232</v>
+        <v>345713</v>
       </c>
     </row>
     <row outlineLevel="0" r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="B216" s="5">
-        <v>277568</v>
+        <v>227334</v>
       </c>
       <c r="C216" s="5">
-        <v>383429</v>
+        <v>364232</v>
       </c>
     </row>
     <row outlineLevel="0" r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="B217" s="5">
-        <v>345745</v>
+        <v>277568</v>
       </c>
       <c r="C217" s="5">
-        <v>381702</v>
+        <v>383429</v>
       </c>
     </row>
     <row outlineLevel="0" r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="B218" s="5">
-        <v>324814</v>
+        <v>345745</v>
       </c>
       <c r="C218" s="5">
-        <v>530042</v>
+        <v>381702</v>
       </c>
     </row>
     <row outlineLevel="0" r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="B219" s="5">
-        <v>343297</v>
+        <v>324814</v>
       </c>
       <c r="C219" s="5">
-        <v>519226</v>
+        <v>530042</v>
       </c>
     </row>
     <row outlineLevel="0" r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>2008-06</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="B220" s="5">
-        <v>346892</v>
+        <v>343297</v>
       </c>
       <c r="C220" s="5">
-        <v>499634</v>
+        <v>519226</v>
       </c>
     </row>
     <row outlineLevel="0" r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>2008-05</t>
+          <t>2008-06</t>
         </is>
       </c>
       <c r="B221" s="5">
-        <v>341610</v>
+        <v>346892</v>
       </c>
       <c r="C221" s="5">
-        <v>470188</v>
+        <v>499634</v>
       </c>
     </row>
     <row outlineLevel="0" r="222">
       <c r="A222" s="4" t="inlineStr">
         <is>
-          <t>2008-04</t>
+          <t>2008-05</t>
         </is>
       </c>
       <c r="B222" s="5">
-        <v>332303</v>
+        <v>341610</v>
       </c>
       <c r="C222" s="5">
-        <v>472371</v>
+        <v>470188</v>
       </c>
     </row>
     <row outlineLevel="0" r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>2008-03</t>
+          <t>2008-04</t>
         </is>
       </c>
       <c r="B223" s="5">
-        <v>349419</v>
+        <v>332303</v>
       </c>
       <c r="C223" s="5">
-        <v>488831</v>
+        <v>472371</v>
       </c>
     </row>
     <row outlineLevel="0" r="224">
       <c r="A224" s="4" t="inlineStr">
         <is>
-          <t>2008-02</t>
+          <t>2008-03</t>
         </is>
       </c>
       <c r="B224" s="5">
-        <v>377088</v>
+        <v>349419</v>
       </c>
       <c r="C224" s="5">
-        <v>454785</v>
+        <v>488831</v>
       </c>
     </row>
     <row outlineLevel="0" r="225">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2008-02</t>
         </is>
       </c>
       <c r="B225" s="5">
-        <v>365592</v>
+        <v>377088</v>
       </c>
       <c r="C225" s="5">
-        <v>474496</v>
+        <v>454785</v>
       </c>
     </row>
     <row outlineLevel="0" r="226">
       <c r="A226" s="4" t="inlineStr">
         <is>
-          <t>2007-12</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="B226" s="5">
-        <v>355292</v>
+        <v>365592</v>
       </c>
       <c r="C226" s="5">
-        <v>456353</v>
+        <v>474496</v>
       </c>
     </row>
     <row outlineLevel="0" r="227">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>2007-11</t>
+          <t>2007-12</t>
         </is>
       </c>
       <c r="B227" s="5">
-        <v>379593</v>
+        <v>355292</v>
       </c>
       <c r="C227" s="5">
-        <v>426721</v>
+        <v>456353</v>
       </c>
     </row>
     <row outlineLevel="0" r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
-          <t>2007-10</t>
+          <t>2007-11</t>
         </is>
       </c>
       <c r="B228" s="5">
-        <v>376979</v>
+        <v>379593</v>
       </c>
       <c r="C228" s="5">
-        <v>392543</v>
+        <v>426721</v>
       </c>
     </row>
     <row outlineLevel="0" r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>2007-09</t>
+          <t>2007-10</t>
         </is>
       </c>
       <c r="B229" s="5">
-        <v>359104</v>
+        <v>376979</v>
       </c>
       <c r="C229" s="5">
-        <v>377364</v>
+        <v>392543</v>
       </c>
     </row>
     <row outlineLevel="0" r="230">
       <c r="A230" s="4" t="inlineStr">
         <is>
-          <t>2007-08</t>
+          <t>2007-09</t>
         </is>
       </c>
       <c r="B230" s="5">
-        <v>362475</v>
+        <v>359104</v>
       </c>
       <c r="C230" s="5">
-        <v>381550</v>
+        <v>377364</v>
       </c>
     </row>
     <row outlineLevel="0" r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>2007-07</t>
+          <t>2007-08</t>
         </is>
       </c>
       <c r="B231" s="5">
-        <v>416403</v>
+        <v>362475</v>
       </c>
       <c r="C231" s="5">
-        <v>380971</v>
+        <v>381550</v>
       </c>
     </row>
     <row outlineLevel="0" r="232">
       <c r="A232" s="4" t="inlineStr">
         <is>
-          <t>2007-06</t>
+          <t>2007-07</t>
         </is>
       </c>
       <c r="B232" s="5">
-        <v>408444</v>
+        <v>416403</v>
       </c>
       <c r="C232" s="5">
-        <v>347617</v>
+        <v>380971</v>
       </c>
     </row>
     <row outlineLevel="0" r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>2007-05</t>
+          <t>2007-06</t>
         </is>
       </c>
       <c r="B233" s="5">
-        <v>382312</v>
+        <v>408444</v>
       </c>
       <c r="C233" s="5">
-        <v>334359</v>
+        <v>347617</v>
       </c>
     </row>
     <row outlineLevel="0" r="234">
       <c r="A234" s="4" t="inlineStr">
         <is>
-          <t>2007-04</t>
+          <t>2007-05</t>
         </is>
       </c>
       <c r="B234" s="5">
-        <v>342084</v>
+        <v>382312</v>
       </c>
       <c r="C234" s="5">
-        <v>314744</v>
+        <v>334359</v>
       </c>
     </row>
     <row outlineLevel="0" r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>2007-03</t>
+          <t>2007-04</t>
         </is>
       </c>
       <c r="B235" s="5">
-        <v>317737</v>
+        <v>342084</v>
       </c>
       <c r="C235" s="5">
-        <v>305479</v>
+        <v>314744</v>
       </c>
     </row>
     <row outlineLevel="0" r="236">
       <c r="A236" s="4" t="inlineStr">
         <is>
-          <t>2007-02</t>
+          <t>2007-03</t>
         </is>
       </c>
       <c r="B236" s="5">
-        <v>321171</v>
+        <v>317737</v>
       </c>
       <c r="C236" s="5">
-        <v>300072</v>
+        <v>305479</v>
       </c>
     </row>
     <row outlineLevel="0" r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>2007-01</t>
+          <t>2007-02</t>
         </is>
       </c>
       <c r="B237" s="5">
-        <v>311506</v>
+        <v>321171</v>
       </c>
       <c r="C237" s="5">
-        <v>292521</v>
+        <v>300072</v>
       </c>
     </row>
     <row outlineLevel="0" r="238">
       <c r="A238" s="4" t="inlineStr">
         <is>
-          <t>2006-12</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="B238" s="5">
-        <v>303288</v>
+        <v>311506</v>
       </c>
       <c r="C238" s="5">
-        <v>299023</v>
+        <v>292521</v>
       </c>
     </row>
     <row outlineLevel="0" r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>2006-11</t>
+          <t>2006-12</t>
         </is>
       </c>
       <c r="B239" s="5">
-        <v>294899</v>
+        <v>303288</v>
       </c>
       <c r="C239" s="5">
-        <v>290910</v>
+        <v>299023</v>
       </c>
     </row>
     <row outlineLevel="0" r="240">
       <c r="A240" s="4" t="inlineStr">
         <is>
-          <t>2006-10</t>
+          <t>2006-11</t>
         </is>
       </c>
       <c r="B240" s="5">
-        <v>267710</v>
+        <v>294899</v>
       </c>
       <c r="C240" s="5">
-        <v>267462</v>
+        <v>290910</v>
       </c>
     </row>
     <row outlineLevel="0" r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>2006-09</t>
+          <t>2006-10</t>
         </is>
       </c>
       <c r="B241" s="5">
-        <v>261769</v>
+        <v>267710</v>
       </c>
       <c r="C241" s="5">
-        <v>268612</v>
+        <v>267462</v>
       </c>
     </row>
     <row outlineLevel="0" r="242">
       <c r="A242" s="4" t="inlineStr">
         <is>
-          <t>2006-08</t>
+          <t>2006-09</t>
         </is>
       </c>
       <c r="B242" s="5">
-        <v>249368</v>
+        <v>261769</v>
       </c>
       <c r="C242" s="5">
-        <v>269423</v>
+        <v>268612</v>
       </c>
     </row>
     <row outlineLevel="0" r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>2006-07</t>
+          <t>2006-08</t>
         </is>
       </c>
       <c r="B243" s="5">
-        <v>256016</v>
+        <v>249368</v>
       </c>
       <c r="C243" s="5">
-        <v>269376</v>
+        <v>269423</v>
       </c>
     </row>
     <row outlineLevel="0" r="244">
       <c r="A244" s="4" t="inlineStr">
         <is>
-          <t>2006-06</t>
+          <t>2006-07</t>
         </is>
       </c>
       <c r="B244" s="5">
-        <v>251495</v>
+        <v>256016</v>
       </c>
       <c r="C244" s="5">
-        <v>280275</v>
+        <v>269376</v>
       </c>
     </row>
     <row outlineLevel="0" r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>2006-05</t>
+          <t>2006-06</t>
         </is>
       </c>
       <c r="B245" s="5">
-        <v>255608</v>
+        <v>251495</v>
       </c>
       <c r="C245" s="5">
-        <v>264307</v>
+        <v>280275</v>
       </c>
     </row>
     <row outlineLevel="0" r="246">
       <c r="A246" s="4" t="inlineStr">
         <is>
-          <t>2006-04</t>
+          <t>2006-05</t>
         </is>
       </c>
       <c r="B246" s="5">
-        <v>265164</v>
+        <v>255608</v>
       </c>
       <c r="C246" s="5">
-        <v>259342</v>
+        <v>264307</v>
       </c>
     </row>
     <row outlineLevel="0" r="247">
       <c r="A247" s="4" t="inlineStr">
         <is>
-          <t>2006-03</t>
+          <t>2006-04</t>
         </is>
       </c>
       <c r="B247" s="5">
-        <v>259370</v>
+        <v>265164</v>
       </c>
       <c r="C247" s="5">
-        <v>258928</v>
+        <v>259342</v>
       </c>
     </row>
     <row outlineLevel="0" r="248">
       <c r="A248" s="4" t="inlineStr">
         <is>
-          <t>2006-02</t>
+          <t>2006-03</t>
         </is>
       </c>
       <c r="B248" s="5">
-        <v>249609</v>
+        <v>259370</v>
       </c>
       <c r="C248" s="5">
-        <v>257573</v>
+        <v>258928</v>
       </c>
     </row>
     <row outlineLevel="0" r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>2006-01</t>
+          <t>2006-02</t>
         </is>
       </c>
       <c r="B249" s="5">
-        <v>255795</v>
+        <v>249609</v>
       </c>
       <c r="C249" s="5">
-        <v>255819</v>
+        <v>257573</v>
       </c>
     </row>
     <row outlineLevel="0" r="250">
       <c r="A250" s="4" t="inlineStr">
         <is>
-          <t>2005-12</t>
+          <t>2006-01</t>
         </is>
       </c>
       <c r="B250" s="5">
-        <v>244098</v>
+        <v>255795</v>
       </c>
       <c r="C250" s="5">
-        <v>263205</v>
+        <v>255819</v>
       </c>
     </row>
     <row outlineLevel="0" r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>2005-11</t>
+          <t>2005-12</t>
         </is>
       </c>
       <c r="B251" s="5">
-        <v>242904</v>
+        <v>244098</v>
       </c>
       <c r="C251" s="5">
-        <v>241695</v>
+        <v>263205</v>
       </c>
     </row>
     <row outlineLevel="0" r="252">
       <c r="A252" s="4" t="inlineStr">
         <is>
-          <t>2005-10</t>
+          <t>2005-11</t>
         </is>
       </c>
       <c r="B252" s="5">
-        <v>239868</v>
+        <v>242904</v>
       </c>
       <c r="C252" s="5">
-        <v>243174</v>
+        <v>241695</v>
       </c>
     </row>
     <row outlineLevel="0" r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>2005-09</t>
+          <t>2005-10</t>
         </is>
       </c>
       <c r="B253" s="5">
-        <v>244669</v>
+        <v>239868</v>
       </c>
       <c r="C253" s="5">
-        <v>238929</v>
+        <v>243174</v>
       </c>
     </row>
     <row outlineLevel="0" r="254">
       <c r="A254" s="4" t="inlineStr">
         <is>
-          <t>2005-08</t>
+          <t>2005-09</t>
         </is>
       </c>
       <c r="B254" s="5">
-        <v>231400</v>
+        <v>244669</v>
       </c>
       <c r="C254" s="5">
-        <v>225410</v>
+        <v>238929</v>
       </c>
     </row>
     <row outlineLevel="0" r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>2005-07</t>
+          <t>2005-08</t>
         </is>
       </c>
       <c r="B255" s="5">
-        <v>233585</v>
+        <v>231400</v>
       </c>
       <c r="C255" s="5">
-        <v>224242</v>
+        <v>225410</v>
       </c>
     </row>
     <row outlineLevel="0" r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>2005-06</t>
+          <t>2005-07</t>
         </is>
       </c>
       <c r="B256" s="5">
-        <v>224153</v>
+        <v>233585</v>
       </c>
       <c r="C256" s="5">
-        <v>234352</v>
+        <v>224242</v>
       </c>
     </row>
     <row outlineLevel="0" r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>2005-05</t>
+          <t>2005-06</t>
         </is>
       </c>
       <c r="B257" s="5">
-        <v>219404</v>
+        <v>224153</v>
       </c>
       <c r="C257" s="5">
-        <v>224933</v>
+        <v>234352</v>
       </c>
     </row>
     <row outlineLevel="0" r="258">
       <c r="A258" s="4" t="inlineStr">
         <is>
-          <t>2005-04</t>
+          <t>2005-05</t>
         </is>
       </c>
       <c r="B258" s="5">
-        <v>217447</v>
+        <v>219404</v>
       </c>
       <c r="C258" s="5">
-        <v>223839</v>
+        <v>224933</v>
       </c>
     </row>
     <row outlineLevel="0" r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>2005-03</t>
+          <t>2005-04</t>
         </is>
       </c>
       <c r="B259" s="5">
-        <v>226876</v>
+        <v>217447</v>
       </c>
       <c r="C259" s="5">
-        <v>234533</v>
+        <v>223839</v>
       </c>
     </row>
     <row outlineLevel="0" r="260">
       <c r="A260" s="4" t="inlineStr">
         <is>
-          <t>2005-02</t>
+          <t>2005-03</t>
         </is>
       </c>
       <c r="B260" s="5">
-        <v>223155</v>
+        <v>226876</v>
       </c>
       <c r="C260" s="5">
-        <v>224392</v>
+        <v>234533</v>
       </c>
     </row>
     <row outlineLevel="0" r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>2005-01</t>
+          <t>2005-02</t>
         </is>
       </c>
       <c r="B261" s="5">
-        <v>220122</v>
+        <v>223155</v>
       </c>
       <c r="C261" s="5">
-        <v>230624</v>
+        <v>224392</v>
       </c>
     </row>
     <row outlineLevel="0" r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2005-01</t>
         </is>
       </c>
       <c r="B262" s="5">
-        <v>217573</v>
+        <v>220122</v>
       </c>
       <c r="C262" s="5">
-        <v>238192</v>
+        <v>230624</v>
       </c>
     </row>
     <row outlineLevel="0" r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>2004-11</t>
+          <t>2004-12</t>
         </is>
       </c>
       <c r="B263" s="5">
-        <v>211012</v>
+        <v>217573</v>
       </c>
       <c r="C263" s="5">
-        <v>223928</v>
+        <v>238192</v>
       </c>
     </row>
     <row outlineLevel="0" r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>2004-10</t>
+          <t>2004-11</t>
         </is>
       </c>
       <c r="B264" s="5">
-        <v>197999</v>
+        <v>211012</v>
       </c>
       <c r="C264" s="5">
-        <v>218090</v>
+        <v>223928</v>
       </c>
     </row>
     <row outlineLevel="0" r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>2004-09</t>
+          <t>2004-10</t>
         </is>
       </c>
       <c r="B265" s="5">
-        <v>193668</v>
+        <v>197999</v>
       </c>
       <c r="C265" s="5">
-        <v>220860</v>
+        <v>218090</v>
       </c>
     </row>
     <row outlineLevel="0" r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>2004-08</t>
+          <t>2004-09</t>
         </is>
       </c>
       <c r="B266" s="5">
-        <v>187828</v>
+        <v>193668</v>
       </c>
       <c r="C266" s="5">
-        <v>217945</v>
+        <v>220860</v>
       </c>
     </row>
     <row outlineLevel="0" r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>2004-07</t>
+          <t>2004-08</t>
         </is>
       </c>
       <c r="B267" s="5">
-        <v>187844</v>
+        <v>187828</v>
       </c>
       <c r="C267" s="5">
-        <v>220196</v>
+        <v>217945</v>
       </c>
     </row>
     <row outlineLevel="0" r="268">
       <c r="A268" s="4" t="inlineStr">
         <is>
-          <t>2004-06</t>
+          <t>2004-07</t>
         </is>
       </c>
       <c r="B268" s="5">
-        <v>193993</v>
+        <v>187844</v>
       </c>
       <c r="C268" s="5">
-        <v>220781</v>
+        <v>220196</v>
       </c>
     </row>
     <row outlineLevel="0" r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="B269" s="5">
-        <v>193843</v>
+        <v>193993</v>
       </c>
       <c r="C269" s="5">
-        <v>219640</v>
+        <v>220781</v>
       </c>
     </row>
     <row outlineLevel="0" r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>2004-04</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="B270" s="5">
-        <v>198778</v>
+        <v>193843</v>
       </c>
       <c r="C270" s="5">
-        <v>217992</v>
+        <v>219640</v>
       </c>
     </row>
     <row outlineLevel="0" r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>2004-03</t>
+          <t>2004-04</t>
         </is>
       </c>
       <c r="B271" s="5">
-        <v>191451</v>
+        <v>198778</v>
       </c>
       <c r="C271" s="5">
-        <v>203953</v>
+        <v>217992</v>
       </c>
     </row>
     <row outlineLevel="0" r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>2004-02</t>
+          <t>2004-03</t>
         </is>
       </c>
       <c r="B272" s="5">
-        <v>190448</v>
+        <v>191451</v>
       </c>
       <c r="C272" s="5">
-        <v>200323</v>
+        <v>203953</v>
       </c>
     </row>
     <row outlineLevel="0" r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2004-02</t>
         </is>
       </c>
       <c r="B273" s="5">
-        <v>189429</v>
+        <v>190448</v>
       </c>
       <c r="C273" s="5">
-        <v>198628</v>
+        <v>200323</v>
       </c>
     </row>
     <row outlineLevel="0" r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>2003-12</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="B274" s="5">
-        <v>181459</v>
+        <v>189429</v>
       </c>
       <c r="C274" s="5">
-        <v>199297</v>
+        <v>198628</v>
       </c>
     </row>
     <row outlineLevel="0" r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>2003-11</t>
+          <t>2003-12</t>
         </is>
       </c>
       <c r="B275" s="5">
-        <v>182587</v>
+        <v>181459</v>
       </c>
       <c r="C275" s="5">
-        <v>184899</v>
+        <v>199297</v>
       </c>
     </row>
     <row outlineLevel="0" r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>2003-10</t>
+          <t>2003-11</t>
         </is>
       </c>
       <c r="B276" s="5">
-        <v>175428</v>
+        <v>182587</v>
       </c>
       <c r="C276" s="5">
-        <v>191554</v>
+        <v>184899</v>
       </c>
     </row>
     <row outlineLevel="0" r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>2003-09</t>
+          <t>2003-10</t>
         </is>
       </c>
       <c r="B277" s="5">
-        <v>171194</v>
+        <v>175428</v>
       </c>
       <c r="C277" s="5">
-        <v>189826</v>
+        <v>191554</v>
       </c>
     </row>
     <row outlineLevel="0" r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>2003-08</t>
+          <t>2003-09</t>
         </is>
       </c>
       <c r="B278" s="5">
-        <v>167200</v>
+        <v>171194</v>
       </c>
       <c r="C278" s="5">
-        <v>188112</v>
+        <v>189826</v>
       </c>
     </row>
     <row outlineLevel="0" r="279">
       <c r="A279" s="4" t="inlineStr">
         <is>
-          <t>2003-07</t>
+          <t>2003-08</t>
         </is>
       </c>
       <c r="B279" s="5">
-        <v>174427</v>
+        <v>167200</v>
       </c>
       <c r="C279" s="5">
-        <v>199973</v>
+        <v>188112</v>
       </c>
     </row>
     <row outlineLevel="0" r="280">
       <c r="A280" s="4" t="inlineStr">
         <is>
-          <t>2003-06</t>
+          <t>2003-07</t>
         </is>
       </c>
       <c r="B280" s="5">
-        <v>168281</v>
+        <v>174427</v>
       </c>
       <c r="C280" s="5">
-        <v>190026</v>
+        <v>199973</v>
       </c>
     </row>
     <row outlineLevel="0" r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>2003-05</t>
+          <t>2003-06</t>
         </is>
       </c>
       <c r="B281" s="5">
-        <v>153725</v>
+        <v>168281</v>
       </c>
       <c r="C281" s="5">
-        <v>178946</v>
+        <v>190026</v>
       </c>
     </row>
     <row outlineLevel="0" r="282">
       <c r="A282" s="4" t="inlineStr">
         <is>
-          <t>2003-04</t>
+          <t>2003-05</t>
         </is>
       </c>
       <c r="B282" s="5">
-        <v>143237</v>
+        <v>153725</v>
       </c>
       <c r="C282" s="5">
-        <v>168756</v>
+        <v>178946</v>
       </c>
     </row>
     <row outlineLevel="0" r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>2003-03</t>
+          <t>2003-04</t>
         </is>
       </c>
       <c r="B283" s="5">
-        <v>144267</v>
+        <v>143237</v>
       </c>
       <c r="C283" s="5">
-        <v>176955</v>
+        <v>168756</v>
       </c>
     </row>
     <row outlineLevel="0" r="284">
       <c r="A284" s="4" t="inlineStr">
         <is>
-          <t>2003-02</t>
+          <t>2003-03</t>
         </is>
       </c>
       <c r="B284" s="5">
-        <v>140516</v>
+        <v>144267</v>
       </c>
       <c r="C284" s="5">
-        <v>179925</v>
+        <v>176955</v>
       </c>
     </row>
     <row outlineLevel="0" r="285">
       <c r="A285" s="4" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2003-02</t>
         </is>
       </c>
       <c r="B285" s="5">
-        <v>141391</v>
+        <v>140516</v>
       </c>
       <c r="C285" s="5">
-        <v>179528</v>
+        <v>179925</v>
       </c>
     </row>
     <row outlineLevel="0" r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>2002-12</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="B286" s="5">
-        <v>139451</v>
+        <v>141391</v>
       </c>
       <c r="C286" s="5">
-        <v>184715</v>
+        <v>179528</v>
       </c>
     </row>
     <row outlineLevel="0" r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>2002-11</t>
+          <t>2002-12</t>
         </is>
       </c>
       <c r="B287" s="5">
-        <v>139472</v>
+        <v>139451</v>
       </c>
       <c r="C287" s="5">
-        <v>176062</v>
+        <v>184715</v>
       </c>
     </row>
     <row outlineLevel="0" r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>2002-10</t>
+          <t>2002-11</t>
         </is>
       </c>
       <c r="B288" s="5">
-        <v>138647</v>
+        <v>139472</v>
       </c>
       <c r="C288" s="5">
-        <v>181069</v>
+        <v>176062</v>
       </c>
     </row>
     <row outlineLevel="0" r="289">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>2002-09</t>
+          <t>2002-10</t>
         </is>
       </c>
       <c r="B289" s="5">
-        <v>136107</v>
+        <v>138647</v>
       </c>
       <c r="C289" s="5">
-        <v>180997</v>
+        <v>181069</v>
       </c>
     </row>
     <row outlineLevel="0" r="290">
       <c r="A290" s="4" t="inlineStr">
         <is>
-          <t>2002-08</t>
+          <t>2002-09</t>
         </is>
       </c>
       <c r="B290" s="5">
-        <v>139146</v>
+        <v>136107</v>
       </c>
       <c r="C290" s="5">
-        <v>174995</v>
+        <v>180997</v>
       </c>
     </row>
     <row outlineLevel="0" r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>2002-07</t>
+          <t>2002-08</t>
         </is>
       </c>
       <c r="B291" s="5">
-        <v>143905</v>
+        <v>139146</v>
       </c>
       <c r="C291" s="5">
-        <v>183326</v>
+        <v>174995</v>
       </c>
     </row>
     <row outlineLevel="0" r="292">
       <c r="A292" s="4" t="inlineStr">
         <is>
-          <t>2002-06</t>
+          <t>2002-07</t>
         </is>
       </c>
       <c r="B292" s="5">
-        <v>153972</v>
+        <v>143905</v>
       </c>
       <c r="C292" s="5">
-        <v>178744</v>
+        <v>183326</v>
       </c>
     </row>
     <row outlineLevel="0" r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>2002-05</t>
+          <t>2002-06</t>
         </is>
       </c>
       <c r="B293" s="5">
-        <v>157802</v>
+        <v>153972</v>
       </c>
       <c r="C293" s="5">
-        <v>173395</v>
+        <v>178744</v>
       </c>
     </row>
     <row outlineLevel="0" r="294">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>2002-04</t>
+          <t>2002-05</t>
         </is>
       </c>
       <c r="B294" s="5">
-        <v>159072</v>
+        <v>157802</v>
       </c>
       <c r="C294" s="5">
-        <v>175730</v>
+        <v>173395</v>
       </c>
     </row>
     <row outlineLevel="0" r="295">
       <c r="A295" s="4" t="inlineStr">
         <is>
-          <t>2002-03</t>
+          <t>2002-04</t>
         </is>
       </c>
       <c r="B295" s="5">
-        <v>160089</v>
+        <v>159072</v>
       </c>
       <c r="C295" s="5">
-        <v>180578</v>
+        <v>175730</v>
       </c>
     </row>
     <row outlineLevel="0" r="296">
       <c r="A296" s="4" t="inlineStr">
         <is>
-          <t>2002-02</t>
+          <t>2002-03</t>
         </is>
       </c>
       <c r="B296" s="5">
-        <v>154931</v>
+        <v>160089</v>
       </c>
       <c r="C296" s="5">
-        <v>186919</v>
+        <v>180578</v>
       </c>
     </row>
     <row outlineLevel="0" r="297">
       <c r="A297" s="4" t="inlineStr">
         <is>
-          <t>2002-01</t>
+          <t>2002-02</t>
         </is>
       </c>
       <c r="B297" s="5">
-        <v>160906</v>
+        <v>154931</v>
       </c>
       <c r="C297" s="5">
-        <v>189841</v>
+        <v>186919</v>
       </c>
     </row>
     <row outlineLevel="0" r="298">
       <c r="A298" s="4" t="inlineStr">
         <is>
-          <t>2001-12</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="B298" s="5">
-        <v>160473</v>
+        <v>160906</v>
       </c>
       <c r="C298" s="5">
-        <v>197424</v>
+        <v>189841</v>
       </c>
     </row>
     <row outlineLevel="0" r="299">
       <c r="A299" s="4" t="inlineStr">
         <is>
-          <t>2001-11</t>
+          <t>2001-12</t>
         </is>
       </c>
       <c r="B299" s="5">
-        <v>159440</v>
+        <v>160473</v>
       </c>
       <c r="C299" s="5">
-        <v>188441</v>
+        <v>197424</v>
       </c>
     </row>
     <row outlineLevel="0" r="300">
       <c r="A300" s="4" t="inlineStr">
         <is>
-          <t>2001-10</t>
+          <t>2001-11</t>
         </is>
       </c>
       <c r="B300" s="5">
-        <v>152367</v>
+        <v>159440</v>
       </c>
       <c r="C300" s="5">
-        <v>187012</v>
+        <v>188441</v>
       </c>
     </row>
     <row outlineLevel="0" r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>2001-09</t>
+          <t>2001-10</t>
         </is>
       </c>
       <c r="B301" s="5">
-        <v>157931</v>
+        <v>152367</v>
       </c>
       <c r="C301" s="5">
-        <v>211281</v>
+        <v>187012</v>
       </c>
     </row>
     <row outlineLevel="0" r="302">
       <c r="A302" s="4" t="inlineStr">
         <is>
-          <t>2001-08</t>
+          <t>2001-09</t>
         </is>
       </c>
       <c r="B302" s="5">
-        <v>169316</v>
+        <v>157931</v>
       </c>
       <c r="C302" s="5">
-        <v>191219</v>
+        <v>211281</v>
       </c>
     </row>
     <row outlineLevel="0" r="303">
       <c r="A303" s="4" t="inlineStr">
         <is>
-          <t>2001-07</t>
+          <t>2001-08</t>
         </is>
       </c>
       <c r="B303" s="5">
-        <v>173680</v>
+        <v>169316</v>
       </c>
       <c r="C303" s="5">
-        <v>185100</v>
+        <v>191219</v>
       </c>
     </row>
     <row outlineLevel="0" r="304">
       <c r="A304" s="4" t="inlineStr">
         <is>
-          <t>2001-06</t>
+          <t>2001-07</t>
         </is>
       </c>
       <c r="B304" s="5">
-        <v>179585</v>
+        <v>173680</v>
       </c>
       <c r="C304" s="5">
-        <v>187602</v>
+        <v>185100</v>
       </c>
     </row>
     <row outlineLevel="0" r="305">
       <c r="A305" s="4" t="inlineStr">
         <is>
-          <t>2001-05</t>
+          <t>2001-06</t>
         </is>
       </c>
       <c r="B305" s="5">
-        <v>183041</v>
+        <v>179585</v>
       </c>
       <c r="C305" s="5">
-        <v>183493</v>
+        <v>187602</v>
       </c>
     </row>
     <row outlineLevel="0" r="306">
       <c r="A306" s="4" t="inlineStr">
         <is>
-          <t>2001-04</t>
+          <t>2001-05</t>
         </is>
       </c>
       <c r="B306" s="5">
-        <v>176096</v>
+        <v>183041</v>
       </c>
       <c r="C306" s="5">
-        <v>191145</v>
+        <v>183493</v>
       </c>
     </row>
     <row outlineLevel="0" r="307">
       <c r="A307" s="4" t="inlineStr">
         <is>
-          <t>2001-03</t>
+          <t>2001-04</t>
         </is>
       </c>
       <c r="B307" s="5">
-        <v>174797</v>
+        <v>176096</v>
       </c>
       <c r="C307" s="5">
-        <v>198581</v>
+        <v>191145</v>
       </c>
     </row>
     <row outlineLevel="0" r="308">
       <c r="A308" s="4" t="inlineStr">
         <is>
-          <t>2001-02</t>
+          <t>2001-03</t>
         </is>
       </c>
       <c r="B308" s="5">
-        <v>198887</v>
+        <v>174797</v>
       </c>
       <c r="C308" s="5">
-        <v>193266</v>
+        <v>198581</v>
       </c>
     </row>
     <row outlineLevel="0" r="309">
       <c r="A309" s="4" t="inlineStr">
         <is>
-          <t>2001-01</t>
+          <t>2001-02</t>
         </is>
       </c>
       <c r="B309" s="5">
-        <v>208687</v>
+        <v>198887</v>
       </c>
       <c r="C309" s="5">
-        <v>187225</v>
+        <v>193266</v>
       </c>
     </row>
     <row outlineLevel="0" r="310">
       <c r="A310" s="4" t="inlineStr">
         <is>
-          <t>2000-12</t>
+          <t>2001-01</t>
         </is>
       </c>
       <c r="B310" s="5">
-        <v>210385</v>
+        <v>208687</v>
       </c>
       <c r="C310" s="5">
-        <v>198179</v>
+        <v>187225</v>
       </c>
     </row>
     <row outlineLevel="0" r="311">
       <c r="A311" s="4" t="inlineStr">
         <is>
-          <t>2000-11</t>
+          <t>2000-12</t>
         </is>
       </c>
       <c r="B311" s="5">
-        <v>237913</v>
+        <v>210385</v>
       </c>
       <c r="C311" s="5">
-        <v>186459</v>
+        <v>198179</v>
       </c>
     </row>
     <row outlineLevel="0" r="312">
       <c r="A312" s="4" t="inlineStr">
         <is>
-          <t>2000-10</t>
+          <t>2000-11</t>
         </is>
       </c>
       <c r="B312" s="5">
-        <v>250965</v>
+        <v>237913</v>
       </c>
       <c r="C312" s="5">
-        <v>172738</v>
+        <v>186459</v>
       </c>
     </row>
     <row outlineLevel="0" r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>2000-09</t>
+          <t>2000-10</t>
         </is>
       </c>
       <c r="B313" s="5">
-        <v>270208</v>
+        <v>250965</v>
       </c>
       <c r="C313" s="5">
-        <v>160964</v>
+        <v>172738</v>
       </c>
     </row>
     <row outlineLevel="0" r="314">
       <c r="A314" s="4" t="inlineStr">
         <is>
-          <t>2000-08</t>
+          <t>2000-09</t>
         </is>
       </c>
       <c r="B314" s="5">
-        <v>265166</v>
+        <v>270208</v>
       </c>
       <c r="C314" s="5">
-        <v>156775</v>
+        <v>160964</v>
       </c>
     </row>
     <row outlineLevel="0" r="315">
       <c r="A315" s="4" t="inlineStr">
         <is>
-          <t>2000-07</t>
+          <t>2000-08</t>
         </is>
       </c>
       <c r="B315" s="5">
-        <v>263729</v>
+        <v>265166</v>
       </c>
       <c r="C315" s="5">
-        <v>163050</v>
+        <v>156775</v>
       </c>
     </row>
     <row outlineLevel="0" r="316">
       <c r="A316" s="4" t="inlineStr">
         <is>
-          <t>2000-06</t>
+          <t>2000-07</t>
         </is>
       </c>
       <c r="B316" s="5">
-        <v>264471</v>
+        <v>263729</v>
       </c>
       <c r="C316" s="5">
-        <v>153050</v>
+        <v>163050</v>
       </c>
     </row>
     <row outlineLevel="0" r="317">
       <c r="A317" s="4" t="inlineStr">
         <is>
-          <t>2000-05</t>
+          <t>2000-06</t>
         </is>
       </c>
       <c r="B317" s="5">
-        <v>256862</v>
+        <v>264471</v>
       </c>
       <c r="C317" s="5">
-        <v>153843</v>
+        <v>153050</v>
       </c>
     </row>
     <row outlineLevel="0" r="318">
       <c r="A318" s="4" t="inlineStr">
         <is>
-          <t>2000-04</t>
+          <t>2000-05</t>
         </is>
       </c>
       <c r="B318" s="5">
-        <v>268716</v>
+        <v>256862</v>
       </c>
       <c r="C318" s="5">
-        <v>156868</v>
+        <v>153843</v>
       </c>
     </row>
     <row outlineLevel="0" r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>2000-03</t>
+          <t>2000-04</t>
         </is>
       </c>
       <c r="B319" s="5">
-        <v>299933</v>
+        <v>268716</v>
       </c>
       <c r="C319" s="5">
-        <v>168002</v>
+        <v>156868</v>
       </c>
     </row>
     <row outlineLevel="0" r="320">
       <c r="A320" s="4" t="inlineStr">
         <is>
-          <t>2000-02</t>
+          <t>2000-03</t>
         </is>
       </c>
       <c r="B320" s="5">
-        <v>284206</v>
+        <v>299933</v>
       </c>
       <c r="C320" s="5">
-        <v>153540</v>
+        <v>168002</v>
       </c>
     </row>
     <row outlineLevel="0" r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>2000-01</t>
+          <t>2000-02</t>
         </is>
       </c>
       <c r="B321" s="5">
-        <v>260409</v>
+        <v>284206</v>
       </c>
       <c r="C321" s="5">
-        <v>148567</v>
+        <v>153540</v>
       </c>
     </row>
     <row outlineLevel="0" r="322">
       <c r="A322" s="4" t="inlineStr">
         <is>
-          <t>1999-12</t>
+          <t>2000-01</t>
         </is>
       </c>
       <c r="B322" s="5">
-        <v>241967</v>
+        <v>260409</v>
       </c>
       <c r="C322" s="5">
-        <v>146582</v>
+        <v>148567</v>
       </c>
     </row>
     <row outlineLevel="0" r="323">
       <c r="A323" s="4" t="inlineStr">
         <is>
-          <t>1999-11</t>
+          <t>1999-12</t>
         </is>
       </c>
       <c r="B323" s="5">
-        <v>218304</v>
+        <v>241967</v>
       </c>
       <c r="C323" s="5">
-        <v>131786</v>
+        <v>146582</v>
       </c>
     </row>
     <row outlineLevel="0" r="324">
       <c r="A324" s="4" t="inlineStr">
         <is>
-          <t>1999-10</t>
+          <t>1999-11</t>
         </is>
       </c>
       <c r="B324" s="5">
-        <v>194259</v>
+        <v>218304</v>
       </c>
       <c r="C324" s="5">
-        <v>123457</v>
+        <v>131786</v>
       </c>
     </row>
     <row outlineLevel="0" r="325">
       <c r="A325" s="4" t="inlineStr">
         <is>
-          <t>1999-09</t>
+          <t>1999-10</t>
         </is>
       </c>
       <c r="B325" s="5">
-        <v>189741</v>
+        <v>194259</v>
       </c>
       <c r="C325" s="5">
-        <v>121207</v>
+        <v>123457</v>
       </c>
     </row>
     <row outlineLevel="0" r="326">
       <c r="A326" s="4" t="inlineStr">
         <is>
-          <t>1999-08</t>
+          <t>1999-09</t>
         </is>
       </c>
       <c r="B326" s="5">
-        <v>187616</v>
+        <v>189741</v>
       </c>
       <c r="C326" s="5">
-        <v>117149</v>
+        <v>121207</v>
       </c>
     </row>
     <row outlineLevel="0" r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>1999-07</t>
+          <t>1999-08</t>
         </is>
       </c>
       <c r="B327" s="5">
-        <v>189503</v>
+        <v>187616</v>
       </c>
       <c r="C327" s="5">
-        <v>115017</v>
+        <v>117149</v>
       </c>
     </row>
     <row outlineLevel="0" r="328">
       <c r="A328" s="4" t="inlineStr">
         <is>
-          <t>1999-06</t>
+          <t>1999-07</t>
         </is>
       </c>
       <c r="B328" s="5">
-        <v>187695</v>
+        <v>189503</v>
       </c>
       <c r="C328" s="5">
-        <v>116982</v>
+        <v>115017</v>
       </c>
     </row>
     <row outlineLevel="0" r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>1999-05</t>
+          <t>1999-06</t>
         </is>
       </c>
       <c r="B329" s="5">
-        <v>189950</v>
+        <v>187695</v>
       </c>
       <c r="C329" s="5">
-        <v>114271</v>
+        <v>116982</v>
       </c>
     </row>
     <row outlineLevel="0" r="330">
       <c r="A330" s="4" t="inlineStr">
         <is>
-          <t>1999-04</t>
+          <t>1999-05</t>
         </is>
       </c>
       <c r="B330" s="5">
-        <v>184329</v>
+        <v>189950</v>
       </c>
       <c r="C330" s="5">
-        <v>112290</v>
+        <v>114271</v>
       </c>
     </row>
     <row outlineLevel="0" r="331">
       <c r="A331" s="4" t="inlineStr">
         <is>
-          <t>1999-03</t>
+          <t>1999-04</t>
         </is>
       </c>
       <c r="B331" s="5">
-        <v>166212</v>
+        <v>184329</v>
       </c>
       <c r="C331" s="5">
-        <v>109941</v>
+        <v>112290</v>
       </c>
     </row>
     <row outlineLevel="0" r="332">
       <c r="A332" s="4" t="inlineStr">
         <is>
-          <t>1999-02</t>
+          <t>1999-03</t>
         </is>
       </c>
       <c r="B332" s="5">
-        <v>162909</v>
+        <v>166212</v>
       </c>
       <c r="C332" s="5">
-        <v>109523</v>
+        <v>109941</v>
       </c>
     </row>
     <row outlineLevel="0" r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1999-02</t>
         </is>
       </c>
       <c r="B333" s="5">
-        <v>162322</v>
+        <v>162909</v>
       </c>
       <c r="C333" s="5">
-        <v>107200</v>
+        <v>109523</v>
       </c>
     </row>
     <row outlineLevel="0" r="334">
       <c r="A334" s="4" t="inlineStr">
         <is>
-          <t>1998-12</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="B334" s="5">
-        <v>148674</v>
+        <v>162322</v>
       </c>
       <c r="C334" s="5">
-        <v>111507</v>
+        <v>107200</v>
       </c>
     </row>
     <row outlineLevel="0" r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>1998-11</t>
+          <t>1998-12</t>
         </is>
       </c>
       <c r="B335" s="5">
-        <v>148697</v>
+        <v>148674</v>
       </c>
       <c r="C335" s="5">
-        <v>108032</v>
+        <v>111507</v>
       </c>
     </row>
     <row outlineLevel="0" r="336">
       <c r="A336" s="4" t="inlineStr">
         <is>
-          <t>1998-10</t>
+          <t>1998-11</t>
         </is>
       </c>
       <c r="B336" s="5">
-        <v>138399</v>
+        <v>148697</v>
       </c>
       <c r="C336" s="5">
-        <v>108179</v>
+        <v>108032</v>
       </c>
     </row>
     <row outlineLevel="0" r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>1998-09</t>
+          <t>1998-10</t>
         </is>
       </c>
       <c r="B337" s="5">
-        <v>144541</v>
+        <v>138399</v>
       </c>
       <c r="C337" s="5">
-        <v>103879</v>
+        <v>108179</v>
       </c>
     </row>
     <row outlineLevel="0" r="338">
       <c r="A338" s="4" t="inlineStr">
         <is>
-          <t>1998-08</t>
+          <t>1998-09</t>
         </is>
       </c>
       <c r="B338" s="5">
-        <v>155879</v>
+        <v>144541</v>
       </c>
       <c r="C338" s="5">
-        <v>100093</v>
+        <v>103879</v>
       </c>
     </row>
     <row outlineLevel="0" r="339">
       <c r="A339" s="4" t="inlineStr">
         <is>
-          <t>1998-07</t>
+          <t>1998-08</t>
         </is>
       </c>
       <c r="B339" s="5">
-        <v>160980</v>
+        <v>155879</v>
       </c>
       <c r="C339" s="5">
-        <v>92687</v>
+        <v>100093</v>
       </c>
     </row>
     <row outlineLevel="0" r="340">
       <c r="A340" s="4" t="inlineStr">
         <is>
-          <t>1998-06</t>
+          <t>1998-07</t>
         </is>
       </c>
       <c r="B340" s="5">
-        <v>154357</v>
+        <v>160980</v>
       </c>
       <c r="C340" s="5">
-        <v>87891</v>
+        <v>92687</v>
       </c>
     </row>
     <row outlineLevel="0" r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>1998-05</t>
+          <t>1998-06</t>
         </is>
       </c>
       <c r="B341" s="5">
-        <v>150293</v>
+        <v>154357</v>
       </c>
       <c r="C341" s="5">
-        <v>80174</v>
+        <v>87891</v>
       </c>
     </row>
     <row outlineLevel="0" r="342">
       <c r="A342" s="4" t="inlineStr">
         <is>
-          <t>1998-04</t>
+          <t>1998-05</t>
         </is>
       </c>
       <c r="B342" s="5">
-        <v>146589</v>
+        <v>150293</v>
       </c>
       <c r="C342" s="5">
-        <v>85771</v>
+        <v>80174</v>
       </c>
     </row>
     <row outlineLevel="0" r="343">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>1998-03</t>
+          <t>1998-04</t>
         </is>
       </c>
       <c r="B343" s="5">
-        <v>146536</v>
+        <v>146589</v>
       </c>
       <c r="C343" s="5">
-        <v>85580</v>
+        <v>85771</v>
       </c>
     </row>
     <row outlineLevel="0" r="344">
       <c r="A344" s="4" t="inlineStr">
         <is>
-          <t>1998-02</t>
+          <t>1998-03</t>
         </is>
       </c>
       <c r="B344" s="5">
-        <v>141328</v>
+        <v>146536</v>
       </c>
       <c r="C344" s="5">
-        <v>81932</v>
+        <v>85580</v>
       </c>
     </row>
     <row outlineLevel="0" r="345">
       <c r="A345" s="4" t="inlineStr">
         <is>
-          <t>1998-01</t>
+          <t>1998-02</t>
         </is>
       </c>
       <c r="B345" s="5">
-        <v>132912</v>
+        <v>141328</v>
       </c>
       <c r="C345" s="5">
-        <v>83362</v>
+        <v>81932</v>
       </c>
     </row>
     <row outlineLevel="0" r="346">
       <c r="A346" s="4" t="inlineStr">
         <is>
-          <t>1997-12</t>
+          <t>1998-01</t>
         </is>
       </c>
       <c r="B346" s="5">
-        <v>131560</v>
+        <v>132912</v>
       </c>
       <c r="C346" s="5">
-        <v>88590</v>
+        <v>83362</v>
       </c>
     </row>
     <row outlineLevel="0" r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>1997-11</t>
+          <t>1997-12</t>
         </is>
       </c>
       <c r="B347" s="5">
-        <v>132741</v>
+        <v>131560</v>
       </c>
       <c r="C347" s="5">
-        <v>77259</v>
+        <v>88590</v>
       </c>
     </row>
     <row outlineLevel="0" r="348">
       <c r="A348" s="4" t="inlineStr">
         <is>
-          <t>1997-10</t>
+          <t>1997-11</t>
         </is>
       </c>
       <c r="B348" s="5">
-        <v>134491</v>
+        <v>132741</v>
       </c>
       <c r="C348" s="5">
-        <v>80287</v>
+        <v>77259</v>
       </c>
     </row>
     <row outlineLevel="0" r="349">
       <c r="A349" s="4" t="inlineStr">
         <is>
-          <t>1997-09</t>
+          <t>1997-10</t>
         </is>
       </c>
       <c r="B349" s="5">
-        <v>131962</v>
+        <v>134491</v>
       </c>
       <c r="C349" s="5">
-        <v>73087</v>
+        <v>80287</v>
       </c>
     </row>
     <row outlineLevel="0" r="350">
       <c r="A350" s="4" t="inlineStr">
         <is>
-          <t>1997-08</t>
+          <t>1997-09</t>
         </is>
       </c>
       <c r="B350" s="5">
-        <v>124404</v>
+        <v>131962</v>
       </c>
       <c r="C350" s="5">
-        <v>71211</v>
+        <v>73087</v>
       </c>
     </row>
     <row outlineLevel="0" r="351">
       <c r="A351" s="4" t="inlineStr">
         <is>
-          <t>1997-07</t>
+          <t>1997-08</t>
         </is>
       </c>
       <c r="B351" s="5">
-        <v>121090</v>
+        <v>124404</v>
       </c>
       <c r="C351" s="5">
-        <v>73714</v>
+        <v>71211</v>
       </c>
     </row>
     <row outlineLevel="0" r="352">
       <c r="A352" s="4" t="inlineStr">
         <is>
-          <t>1997-06</t>
+          <t>1997-07</t>
         </is>
       </c>
       <c r="B352" s="5">
-        <v>118843</v>
+        <v>121090</v>
       </c>
       <c r="C352" s="5">
-        <v>72422</v>
+        <v>73714</v>
       </c>
     </row>
     <row outlineLevel="0" r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>1997-05</t>
+          <t>1997-06</t>
         </is>
       </c>
       <c r="B353" s="5">
-        <v>111097</v>
+        <v>118843</v>
       </c>
       <c r="C353" s="5">
-        <v>66879</v>
+        <v>72422</v>
       </c>
     </row>
     <row outlineLevel="0" r="354">
       <c r="A354" s="4" t="inlineStr">
         <is>
-          <t>1997-04</t>
+          <t>1997-05</t>
         </is>
       </c>
       <c r="B354" s="5">
-        <v>102842</v>
+        <v>111097</v>
       </c>
       <c r="C354" s="5">
-        <v>64825</v>
+        <v>66879</v>
       </c>
     </row>
     <row outlineLevel="0" r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>1997-03</t>
+          <t>1997-04</t>
         </is>
       </c>
       <c r="B355" s="5">
-        <v>104835</v>
+        <v>102842</v>
       </c>
       <c r="C355" s="5">
-        <v>69553</v>
+        <v>64825</v>
       </c>
     </row>
     <row outlineLevel="0" r="356">
       <c r="A356" s="4" t="inlineStr">
         <is>
-          <t>1997-02</t>
+          <t>1997-03</t>
         </is>
       </c>
       <c r="B356" s="5">
-        <v>103886</v>
+        <v>104835</v>
       </c>
       <c r="C356" s="5">
-        <v>67058</v>
+        <v>69553</v>
       </c>
     </row>
     <row outlineLevel="0" r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
+          <t>1997-02</t>
+        </is>
+      </c>
+      <c r="B357" s="5">
+        <v>103886</v>
+      </c>
+      <c r="C357" s="5">
+        <v>67058</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="358">
+      <c r="A358" s="4" t="inlineStr">
+        <is>
           <t>1997-01</t>
         </is>
       </c>
-      <c r="B357" s="5">
+      <c r="B358" s="5">
         <v>103337</v>
       </c>
-      <c r="C357" s="5">
+      <c r="C358" s="5">
         <v>68856</v>
       </c>
     </row>
